--- a/plantillas/PLANTILLA_CARGA_ICA.xlsx
+++ b/plantillas/PLANTILLA_CARGA_ICA.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -510,6 +510,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -650,29 +651,41 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Opcional. Vacío = 15 (o el plazo configurado en la app).</t>
+          <t>Opcional. Días hábiles para responder el 1.er requerimiento (sin contar el día del envío). Vacío = 15.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Ejemplo de fila</t>
+          <t>DIAS HABILES 2 REQUERIMIENTO</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>00125 | JURIDICA | 5006003578 | COMERCIALIZADORA EJEMPLO S.A.S. | JUAN PÉREZ GÓMEZ | contabilidad@ejemplo.com | | CRA 8 # 12-30 | TOLIMA | FLANDES | 2023, 2024, 2025 | 15</t>
+          <t>Opcional. Días hábiles para responder el 2.º requerimiento (insistencia). Vacío = 15.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Ejemplo de fila</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>00125 | JURIDICA | 5006003578 | COMERCIALIZADORA EJEMPLO S.A.S. | JUAN PÉREZ GÓMEZ | contabilidad@ejemplo.com | | CRA 8 # 12-30 | TOLIMA | FLANDES | 2023, 2024, 2025 | 15 | 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Al subir</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>La app revisa cada fila antes de guardar y le muestra cuáles tienen errores y por qué. Solo se guardan las filas correctas.</t>
         </is>
@@ -689,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1001"/>
+  <dimension ref="A1:M1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -703,7 +716,8 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -765,6 +779,11 @@
       <c r="L1" s="5" t="inlineStr">
         <is>
           <t>DIAS HABILES</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>DIAS HABILES 2 REQUERIMIENTO</t>
         </is>
       </c>
     </row>
@@ -781,6 +800,7 @@
       <c r="J2" s="6" t="n"/>
       <c r="K2" s="6" t="n"/>
       <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -795,6 +815,7 @@
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
       <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n"/>
@@ -809,6 +830,7 @@
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -823,6 +845,7 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n"/>
@@ -837,6 +860,7 @@
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
@@ -851,6 +875,7 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
@@ -865,6 +890,7 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -879,6 +905,7 @@
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -893,6 +920,7 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
@@ -907,6 +935,7 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
@@ -921,6 +950,7 @@
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -935,6 +965,7 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -949,6 +980,7 @@
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
@@ -963,6 +995,7 @@
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
@@ -977,6 +1010,7 @@
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -991,6 +1025,7 @@
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -1005,6 +1040,7 @@
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
@@ -1019,6 +1055,7 @@
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
@@ -1033,6 +1070,7 @@
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -1047,6 +1085,7 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
@@ -1061,6 +1100,7 @@
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
@@ -1075,6 +1115,7 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
@@ -1089,6 +1130,7 @@
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -1103,6 +1145,7 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
@@ -1117,6 +1160,7 @@
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n"/>
@@ -1131,6 +1175,7 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n"/>
@@ -1145,6 +1190,7 @@
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -1159,6 +1205,7 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n"/>
@@ -1173,6 +1220,7 @@
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n"/>
@@ -1187,6 +1235,7 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -1201,6 +1250,7 @@
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
@@ -1215,6 +1265,7 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
@@ -1229,6 +1280,7 @@
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
@@ -1243,6 +1295,7 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -1257,6 +1310,7 @@
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
@@ -1271,6 +1325,7 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
@@ -1285,6 +1340,7 @@
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
@@ -1299,6 +1355,7 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -1313,6 +1370,7 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
@@ -1327,6 +1385,7 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
@@ -1341,6 +1400,7 @@
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
@@ -1355,6 +1415,7 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -1369,6 +1430,7 @@
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n"/>
@@ -1383,6 +1445,7 @@
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n"/>
@@ -1397,6 +1460,7 @@
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
@@ -1411,6 +1475,7 @@
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -1425,6 +1490,7 @@
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
@@ -1439,6 +1505,7 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n"/>
@@ -1453,6 +1520,7 @@
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n"/>
@@ -1467,6 +1535,7 @@
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -1481,6 +1550,7 @@
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n"/>
@@ -1495,6 +1565,7 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
       <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n"/>
@@ -1509,6 +1580,7 @@
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n"/>
+      <c r="M54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
@@ -1523,6 +1595,7 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="6" t="n"/>
+      <c r="M55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -1537,6 +1610,7 @@
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n"/>
+      <c r="M56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
@@ -1551,6 +1625,7 @@
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
       <c r="L57" s="6" t="n"/>
+      <c r="M57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n"/>
@@ -1565,6 +1640,7 @@
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n"/>
+      <c r="M58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n"/>
@@ -1579,6 +1655,7 @@
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
       <c r="L59" s="6" t="n"/>
+      <c r="M59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -1593,6 +1670,7 @@
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
       <c r="L60" s="6" t="n"/>
+      <c r="M60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
@@ -1607,6 +1685,7 @@
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="6" t="n"/>
       <c r="L61" s="6" t="n"/>
+      <c r="M61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="n"/>
@@ -1621,6 +1700,7 @@
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="6" t="n"/>
       <c r="L62" s="6" t="n"/>
+      <c r="M62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
@@ -1635,6 +1715,7 @@
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
       <c r="L63" s="6" t="n"/>
+      <c r="M63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -1649,6 +1730,7 @@
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="6" t="n"/>
+      <c r="M64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n"/>
@@ -1663,6 +1745,7 @@
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
       <c r="L65" s="6" t="n"/>
+      <c r="M65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n"/>
@@ -1677,6 +1760,7 @@
       <c r="J66" s="6" t="n"/>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="6" t="n"/>
+      <c r="M66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n"/>
@@ -1691,6 +1775,7 @@
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="6" t="n"/>
       <c r="L67" s="6" t="n"/>
+      <c r="M67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -1705,6 +1790,7 @@
       <c r="J68" s="6" t="n"/>
       <c r="K68" s="6" t="n"/>
       <c r="L68" s="6" t="n"/>
+      <c r="M68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n"/>
@@ -1719,6 +1805,7 @@
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="6" t="n"/>
       <c r="L69" s="6" t="n"/>
+      <c r="M69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
@@ -1733,6 +1820,7 @@
       <c r="J70" s="6" t="n"/>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="6" t="n"/>
+      <c r="M70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6" t="n"/>
@@ -1747,6 +1835,7 @@
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="6" t="n"/>
       <c r="L71" s="6" t="n"/>
+      <c r="M71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -1761,6 +1850,7 @@
       <c r="J72" s="6" t="n"/>
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="6" t="n"/>
+      <c r="M72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="n"/>
@@ -1775,6 +1865,7 @@
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="6" t="n"/>
       <c r="L73" s="6" t="n"/>
+      <c r="M73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
@@ -1789,6 +1880,7 @@
       <c r="J74" s="6" t="n"/>
       <c r="K74" s="6" t="n"/>
       <c r="L74" s="6" t="n"/>
+      <c r="M74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="n"/>
@@ -1803,6 +1895,7 @@
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="6" t="n"/>
       <c r="L75" s="6" t="n"/>
+      <c r="M75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -1817,6 +1910,7 @@
       <c r="J76" s="6" t="n"/>
       <c r="K76" s="6" t="n"/>
       <c r="L76" s="6" t="n"/>
+      <c r="M76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="n"/>
@@ -1831,6 +1925,7 @@
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="6" t="n"/>
       <c r="L77" s="6" t="n"/>
+      <c r="M77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="n"/>
@@ -1845,6 +1940,7 @@
       <c r="J78" s="6" t="n"/>
       <c r="K78" s="6" t="n"/>
       <c r="L78" s="6" t="n"/>
+      <c r="M78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="n"/>
@@ -1859,6 +1955,7 @@
       <c r="J79" s="6" t="n"/>
       <c r="K79" s="6" t="n"/>
       <c r="L79" s="6" t="n"/>
+      <c r="M79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -1873,6 +1970,7 @@
       <c r="J80" s="6" t="n"/>
       <c r="K80" s="6" t="n"/>
       <c r="L80" s="6" t="n"/>
+      <c r="M80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="6" t="n"/>
@@ -1887,6 +1985,7 @@
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="6" t="n"/>
       <c r="L81" s="6" t="n"/>
+      <c r="M81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
@@ -1901,6 +2000,7 @@
       <c r="J82" s="6" t="n"/>
       <c r="K82" s="6" t="n"/>
       <c r="L82" s="6" t="n"/>
+      <c r="M82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="n"/>
@@ -1915,6 +2015,7 @@
       <c r="J83" s="6" t="n"/>
       <c r="K83" s="6" t="n"/>
       <c r="L83" s="6" t="n"/>
+      <c r="M83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -1929,6 +2030,7 @@
       <c r="J84" s="6" t="n"/>
       <c r="K84" s="6" t="n"/>
       <c r="L84" s="6" t="n"/>
+      <c r="M84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="n"/>
@@ -1943,6 +2045,7 @@
       <c r="J85" s="6" t="n"/>
       <c r="K85" s="6" t="n"/>
       <c r="L85" s="6" t="n"/>
+      <c r="M85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
@@ -1957,6 +2060,7 @@
       <c r="J86" s="6" t="n"/>
       <c r="K86" s="6" t="n"/>
       <c r="L86" s="6" t="n"/>
+      <c r="M86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="n"/>
@@ -1971,6 +2075,7 @@
       <c r="J87" s="6" t="n"/>
       <c r="K87" s="6" t="n"/>
       <c r="L87" s="6" t="n"/>
+      <c r="M87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
@@ -1985,6 +2090,7 @@
       <c r="J88" s="6" t="n"/>
       <c r="K88" s="6" t="n"/>
       <c r="L88" s="6" t="n"/>
+      <c r="M88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="6" t="n"/>
@@ -1999,6 +2105,7 @@
       <c r="J89" s="6" t="n"/>
       <c r="K89" s="6" t="n"/>
       <c r="L89" s="6" t="n"/>
+      <c r="M89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="n"/>
@@ -2013,6 +2120,7 @@
       <c r="J90" s="6" t="n"/>
       <c r="K90" s="6" t="n"/>
       <c r="L90" s="6" t="n"/>
+      <c r="M90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
@@ -2027,6 +2135,7 @@
       <c r="J91" s="6" t="n"/>
       <c r="K91" s="6" t="n"/>
       <c r="L91" s="6" t="n"/>
+      <c r="M91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="n"/>
@@ -2041,6 +2150,7 @@
       <c r="J92" s="6" t="n"/>
       <c r="K92" s="6" t="n"/>
       <c r="L92" s="6" t="n"/>
+      <c r="M92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="6" t="n"/>
@@ -2055,6 +2165,7 @@
       <c r="J93" s="6" t="n"/>
       <c r="K93" s="6" t="n"/>
       <c r="L93" s="6" t="n"/>
+      <c r="M93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
@@ -2069,6 +2180,7 @@
       <c r="J94" s="6" t="n"/>
       <c r="K94" s="6" t="n"/>
       <c r="L94" s="6" t="n"/>
+      <c r="M94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="n"/>
@@ -2083,6 +2195,7 @@
       <c r="J95" s="6" t="n"/>
       <c r="K95" s="6" t="n"/>
       <c r="L95" s="6" t="n"/>
+      <c r="M95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="n"/>
@@ -2097,6 +2210,7 @@
       <c r="J96" s="6" t="n"/>
       <c r="K96" s="6" t="n"/>
       <c r="L96" s="6" t="n"/>
+      <c r="M96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="n"/>
@@ -2111,6 +2225,7 @@
       <c r="J97" s="6" t="n"/>
       <c r="K97" s="6" t="n"/>
       <c r="L97" s="6" t="n"/>
+      <c r="M97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="n"/>
@@ -2125,6 +2240,7 @@
       <c r="J98" s="6" t="n"/>
       <c r="K98" s="6" t="n"/>
       <c r="L98" s="6" t="n"/>
+      <c r="M98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
@@ -2139,6 +2255,7 @@
       <c r="J99" s="6" t="n"/>
       <c r="K99" s="6" t="n"/>
       <c r="L99" s="6" t="n"/>
+      <c r="M99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="n"/>
@@ -2153,6 +2270,7 @@
       <c r="J100" s="6" t="n"/>
       <c r="K100" s="6" t="n"/>
       <c r="L100" s="6" t="n"/>
+      <c r="M100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="n"/>
@@ -2167,6 +2285,7 @@
       <c r="J101" s="6" t="n"/>
       <c r="K101" s="6" t="n"/>
       <c r="L101" s="6" t="n"/>
+      <c r="M101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="n"/>
@@ -2181,6 +2300,7 @@
       <c r="J102" s="6" t="n"/>
       <c r="K102" s="6" t="n"/>
       <c r="L102" s="6" t="n"/>
+      <c r="M102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="n"/>
@@ -2195,6 +2315,7 @@
       <c r="J103" s="6" t="n"/>
       <c r="K103" s="6" t="n"/>
       <c r="L103" s="6" t="n"/>
+      <c r="M103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="n"/>
@@ -2209,6 +2330,7 @@
       <c r="J104" s="6" t="n"/>
       <c r="K104" s="6" t="n"/>
       <c r="L104" s="6" t="n"/>
+      <c r="M104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="6" t="n"/>
@@ -2223,6 +2345,7 @@
       <c r="J105" s="6" t="n"/>
       <c r="K105" s="6" t="n"/>
       <c r="L105" s="6" t="n"/>
+      <c r="M105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="n"/>
@@ -2237,6 +2360,7 @@
       <c r="J106" s="6" t="n"/>
       <c r="K106" s="6" t="n"/>
       <c r="L106" s="6" t="n"/>
+      <c r="M106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="n"/>
@@ -2251,6 +2375,7 @@
       <c r="J107" s="6" t="n"/>
       <c r="K107" s="6" t="n"/>
       <c r="L107" s="6" t="n"/>
+      <c r="M107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="n"/>
@@ -2265,6 +2390,7 @@
       <c r="J108" s="6" t="n"/>
       <c r="K108" s="6" t="n"/>
       <c r="L108" s="6" t="n"/>
+      <c r="M108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="n"/>
@@ -2279,6 +2405,7 @@
       <c r="J109" s="6" t="n"/>
       <c r="K109" s="6" t="n"/>
       <c r="L109" s="6" t="n"/>
+      <c r="M109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="n"/>
@@ -2293,6 +2420,7 @@
       <c r="J110" s="6" t="n"/>
       <c r="K110" s="6" t="n"/>
       <c r="L110" s="6" t="n"/>
+      <c r="M110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="n"/>
@@ -2307,6 +2435,7 @@
       <c r="J111" s="6" t="n"/>
       <c r="K111" s="6" t="n"/>
       <c r="L111" s="6" t="n"/>
+      <c r="M111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="n"/>
@@ -2321,6 +2450,7 @@
       <c r="J112" s="6" t="n"/>
       <c r="K112" s="6" t="n"/>
       <c r="L112" s="6" t="n"/>
+      <c r="M112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="n"/>
@@ -2335,6 +2465,7 @@
       <c r="J113" s="6" t="n"/>
       <c r="K113" s="6" t="n"/>
       <c r="L113" s="6" t="n"/>
+      <c r="M113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="n"/>
@@ -2349,6 +2480,7 @@
       <c r="J114" s="6" t="n"/>
       <c r="K114" s="6" t="n"/>
       <c r="L114" s="6" t="n"/>
+      <c r="M114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="6" t="n"/>
@@ -2363,6 +2495,7 @@
       <c r="J115" s="6" t="n"/>
       <c r="K115" s="6" t="n"/>
       <c r="L115" s="6" t="n"/>
+      <c r="M115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="n"/>
@@ -2377,6 +2510,7 @@
       <c r="J116" s="6" t="n"/>
       <c r="K116" s="6" t="n"/>
       <c r="L116" s="6" t="n"/>
+      <c r="M116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="6" t="n"/>
@@ -2391,6 +2525,7 @@
       <c r="J117" s="6" t="n"/>
       <c r="K117" s="6" t="n"/>
       <c r="L117" s="6" t="n"/>
+      <c r="M117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="n"/>
@@ -2405,6 +2540,7 @@
       <c r="J118" s="6" t="n"/>
       <c r="K118" s="6" t="n"/>
       <c r="L118" s="6" t="n"/>
+      <c r="M118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="6" t="n"/>
@@ -2419,6 +2555,7 @@
       <c r="J119" s="6" t="n"/>
       <c r="K119" s="6" t="n"/>
       <c r="L119" s="6" t="n"/>
+      <c r="M119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="n"/>
@@ -2433,6 +2570,7 @@
       <c r="J120" s="6" t="n"/>
       <c r="K120" s="6" t="n"/>
       <c r="L120" s="6" t="n"/>
+      <c r="M120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="6" t="n"/>
@@ -2447,6 +2585,7 @@
       <c r="J121" s="6" t="n"/>
       <c r="K121" s="6" t="n"/>
       <c r="L121" s="6" t="n"/>
+      <c r="M121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="n"/>
@@ -2461,6 +2600,7 @@
       <c r="J122" s="6" t="n"/>
       <c r="K122" s="6" t="n"/>
       <c r="L122" s="6" t="n"/>
+      <c r="M122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="6" t="n"/>
@@ -2475,6 +2615,7 @@
       <c r="J123" s="6" t="n"/>
       <c r="K123" s="6" t="n"/>
       <c r="L123" s="6" t="n"/>
+      <c r="M123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="n"/>
@@ -2489,6 +2630,7 @@
       <c r="J124" s="6" t="n"/>
       <c r="K124" s="6" t="n"/>
       <c r="L124" s="6" t="n"/>
+      <c r="M124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="6" t="n"/>
@@ -2503,6 +2645,7 @@
       <c r="J125" s="6" t="n"/>
       <c r="K125" s="6" t="n"/>
       <c r="L125" s="6" t="n"/>
+      <c r="M125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="n"/>
@@ -2517,6 +2660,7 @@
       <c r="J126" s="6" t="n"/>
       <c r="K126" s="6" t="n"/>
       <c r="L126" s="6" t="n"/>
+      <c r="M126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="n"/>
@@ -2531,6 +2675,7 @@
       <c r="J127" s="6" t="n"/>
       <c r="K127" s="6" t="n"/>
       <c r="L127" s="6" t="n"/>
+      <c r="M127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="n"/>
@@ -2545,6 +2690,7 @@
       <c r="J128" s="6" t="n"/>
       <c r="K128" s="6" t="n"/>
       <c r="L128" s="6" t="n"/>
+      <c r="M128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="6" t="n"/>
@@ -2559,6 +2705,7 @@
       <c r="J129" s="6" t="n"/>
       <c r="K129" s="6" t="n"/>
       <c r="L129" s="6" t="n"/>
+      <c r="M129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="n"/>
@@ -2573,6 +2720,7 @@
       <c r="J130" s="6" t="n"/>
       <c r="K130" s="6" t="n"/>
       <c r="L130" s="6" t="n"/>
+      <c r="M130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="6" t="n"/>
@@ -2587,6 +2735,7 @@
       <c r="J131" s="6" t="n"/>
       <c r="K131" s="6" t="n"/>
       <c r="L131" s="6" t="n"/>
+      <c r="M131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="n"/>
@@ -2601,6 +2750,7 @@
       <c r="J132" s="6" t="n"/>
       <c r="K132" s="6" t="n"/>
       <c r="L132" s="6" t="n"/>
+      <c r="M132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="6" t="n"/>
@@ -2615,6 +2765,7 @@
       <c r="J133" s="6" t="n"/>
       <c r="K133" s="6" t="n"/>
       <c r="L133" s="6" t="n"/>
+      <c r="M133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="n"/>
@@ -2629,6 +2780,7 @@
       <c r="J134" s="6" t="n"/>
       <c r="K134" s="6" t="n"/>
       <c r="L134" s="6" t="n"/>
+      <c r="M134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="6" t="n"/>
@@ -2643,6 +2795,7 @@
       <c r="J135" s="6" t="n"/>
       <c r="K135" s="6" t="n"/>
       <c r="L135" s="6" t="n"/>
+      <c r="M135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="n"/>
@@ -2657,6 +2810,7 @@
       <c r="J136" s="6" t="n"/>
       <c r="K136" s="6" t="n"/>
       <c r="L136" s="6" t="n"/>
+      <c r="M136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="6" t="n"/>
@@ -2671,6 +2825,7 @@
       <c r="J137" s="6" t="n"/>
       <c r="K137" s="6" t="n"/>
       <c r="L137" s="6" t="n"/>
+      <c r="M137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="n"/>
@@ -2685,6 +2840,7 @@
       <c r="J138" s="6" t="n"/>
       <c r="K138" s="6" t="n"/>
       <c r="L138" s="6" t="n"/>
+      <c r="M138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="n"/>
@@ -2699,6 +2855,7 @@
       <c r="J139" s="6" t="n"/>
       <c r="K139" s="6" t="n"/>
       <c r="L139" s="6" t="n"/>
+      <c r="M139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="n"/>
@@ -2713,6 +2870,7 @@
       <c r="J140" s="6" t="n"/>
       <c r="K140" s="6" t="n"/>
       <c r="L140" s="6" t="n"/>
+      <c r="M140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="n"/>
@@ -2727,6 +2885,7 @@
       <c r="J141" s="6" t="n"/>
       <c r="K141" s="6" t="n"/>
       <c r="L141" s="6" t="n"/>
+      <c r="M141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="n"/>
@@ -2741,6 +2900,7 @@
       <c r="J142" s="6" t="n"/>
       <c r="K142" s="6" t="n"/>
       <c r="L142" s="6" t="n"/>
+      <c r="M142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="6" t="n"/>
@@ -2755,6 +2915,7 @@
       <c r="J143" s="6" t="n"/>
       <c r="K143" s="6" t="n"/>
       <c r="L143" s="6" t="n"/>
+      <c r="M143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="n"/>
@@ -2769,6 +2930,7 @@
       <c r="J144" s="6" t="n"/>
       <c r="K144" s="6" t="n"/>
       <c r="L144" s="6" t="n"/>
+      <c r="M144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="6" t="n"/>
@@ -2783,6 +2945,7 @@
       <c r="J145" s="6" t="n"/>
       <c r="K145" s="6" t="n"/>
       <c r="L145" s="6" t="n"/>
+      <c r="M145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="n"/>
@@ -2797,6 +2960,7 @@
       <c r="J146" s="6" t="n"/>
       <c r="K146" s="6" t="n"/>
       <c r="L146" s="6" t="n"/>
+      <c r="M146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="n"/>
@@ -2811,6 +2975,7 @@
       <c r="J147" s="6" t="n"/>
       <c r="K147" s="6" t="n"/>
       <c r="L147" s="6" t="n"/>
+      <c r="M147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="n"/>
@@ -2825,6 +2990,7 @@
       <c r="J148" s="6" t="n"/>
       <c r="K148" s="6" t="n"/>
       <c r="L148" s="6" t="n"/>
+      <c r="M148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="6" t="n"/>
@@ -2839,6 +3005,7 @@
       <c r="J149" s="6" t="n"/>
       <c r="K149" s="6" t="n"/>
       <c r="L149" s="6" t="n"/>
+      <c r="M149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="n"/>
@@ -2853,6 +3020,7 @@
       <c r="J150" s="6" t="n"/>
       <c r="K150" s="6" t="n"/>
       <c r="L150" s="6" t="n"/>
+      <c r="M150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="6" t="n"/>
@@ -2867,6 +3035,7 @@
       <c r="J151" s="6" t="n"/>
       <c r="K151" s="6" t="n"/>
       <c r="L151" s="6" t="n"/>
+      <c r="M151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="n"/>
@@ -2881,6 +3050,7 @@
       <c r="J152" s="6" t="n"/>
       <c r="K152" s="6" t="n"/>
       <c r="L152" s="6" t="n"/>
+      <c r="M152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="6" t="n"/>
@@ -2895,6 +3065,7 @@
       <c r="J153" s="6" t="n"/>
       <c r="K153" s="6" t="n"/>
       <c r="L153" s="6" t="n"/>
+      <c r="M153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="n"/>
@@ -2909,6 +3080,7 @@
       <c r="J154" s="6" t="n"/>
       <c r="K154" s="6" t="n"/>
       <c r="L154" s="6" t="n"/>
+      <c r="M154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="n"/>
@@ -2923,6 +3095,7 @@
       <c r="J155" s="6" t="n"/>
       <c r="K155" s="6" t="n"/>
       <c r="L155" s="6" t="n"/>
+      <c r="M155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="n"/>
@@ -2937,6 +3110,7 @@
       <c r="J156" s="6" t="n"/>
       <c r="K156" s="6" t="n"/>
       <c r="L156" s="6" t="n"/>
+      <c r="M156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="6" t="n"/>
@@ -2951,6 +3125,7 @@
       <c r="J157" s="6" t="n"/>
       <c r="K157" s="6" t="n"/>
       <c r="L157" s="6" t="n"/>
+      <c r="M157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="n"/>
@@ -2965,6 +3140,7 @@
       <c r="J158" s="6" t="n"/>
       <c r="K158" s="6" t="n"/>
       <c r="L158" s="6" t="n"/>
+      <c r="M158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="6" t="n"/>
@@ -2979,6 +3155,7 @@
       <c r="J159" s="6" t="n"/>
       <c r="K159" s="6" t="n"/>
       <c r="L159" s="6" t="n"/>
+      <c r="M159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="n"/>
@@ -2993,6 +3170,7 @@
       <c r="J160" s="6" t="n"/>
       <c r="K160" s="6" t="n"/>
       <c r="L160" s="6" t="n"/>
+      <c r="M160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="6" t="n"/>
@@ -3007,6 +3185,7 @@
       <c r="J161" s="6" t="n"/>
       <c r="K161" s="6" t="n"/>
       <c r="L161" s="6" t="n"/>
+      <c r="M161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="n"/>
@@ -3021,6 +3200,7 @@
       <c r="J162" s="6" t="n"/>
       <c r="K162" s="6" t="n"/>
       <c r="L162" s="6" t="n"/>
+      <c r="M162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="6" t="n"/>
@@ -3035,6 +3215,7 @@
       <c r="J163" s="6" t="n"/>
       <c r="K163" s="6" t="n"/>
       <c r="L163" s="6" t="n"/>
+      <c r="M163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="n"/>
@@ -3049,6 +3230,7 @@
       <c r="J164" s="6" t="n"/>
       <c r="K164" s="6" t="n"/>
       <c r="L164" s="6" t="n"/>
+      <c r="M164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="n"/>
@@ -3063,6 +3245,7 @@
       <c r="J165" s="6" t="n"/>
       <c r="K165" s="6" t="n"/>
       <c r="L165" s="6" t="n"/>
+      <c r="M165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="n"/>
@@ -3077,6 +3260,7 @@
       <c r="J166" s="6" t="n"/>
       <c r="K166" s="6" t="n"/>
       <c r="L166" s="6" t="n"/>
+      <c r="M166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="6" t="n"/>
@@ -3091,6 +3275,7 @@
       <c r="J167" s="6" t="n"/>
       <c r="K167" s="6" t="n"/>
       <c r="L167" s="6" t="n"/>
+      <c r="M167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="n"/>
@@ -3105,6 +3290,7 @@
       <c r="J168" s="6" t="n"/>
       <c r="K168" s="6" t="n"/>
       <c r="L168" s="6" t="n"/>
+      <c r="M168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="6" t="n"/>
@@ -3119,6 +3305,7 @@
       <c r="J169" s="6" t="n"/>
       <c r="K169" s="6" t="n"/>
       <c r="L169" s="6" t="n"/>
+      <c r="M169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="n"/>
@@ -3133,6 +3320,7 @@
       <c r="J170" s="6" t="n"/>
       <c r="K170" s="6" t="n"/>
       <c r="L170" s="6" t="n"/>
+      <c r="M170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="6" t="n"/>
@@ -3147,6 +3335,7 @@
       <c r="J171" s="6" t="n"/>
       <c r="K171" s="6" t="n"/>
       <c r="L171" s="6" t="n"/>
+      <c r="M171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="n"/>
@@ -3161,6 +3350,7 @@
       <c r="J172" s="6" t="n"/>
       <c r="K172" s="6" t="n"/>
       <c r="L172" s="6" t="n"/>
+      <c r="M172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="6" t="n"/>
@@ -3175,6 +3365,7 @@
       <c r="J173" s="6" t="n"/>
       <c r="K173" s="6" t="n"/>
       <c r="L173" s="6" t="n"/>
+      <c r="M173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="n"/>
@@ -3189,6 +3380,7 @@
       <c r="J174" s="6" t="n"/>
       <c r="K174" s="6" t="n"/>
       <c r="L174" s="6" t="n"/>
+      <c r="M174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="n"/>
@@ -3203,6 +3395,7 @@
       <c r="J175" s="6" t="n"/>
       <c r="K175" s="6" t="n"/>
       <c r="L175" s="6" t="n"/>
+      <c r="M175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="n"/>
@@ -3217,6 +3410,7 @@
       <c r="J176" s="6" t="n"/>
       <c r="K176" s="6" t="n"/>
       <c r="L176" s="6" t="n"/>
+      <c r="M176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="6" t="n"/>
@@ -3231,6 +3425,7 @@
       <c r="J177" s="6" t="n"/>
       <c r="K177" s="6" t="n"/>
       <c r="L177" s="6" t="n"/>
+      <c r="M177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="n"/>
@@ -3245,6 +3440,7 @@
       <c r="J178" s="6" t="n"/>
       <c r="K178" s="6" t="n"/>
       <c r="L178" s="6" t="n"/>
+      <c r="M178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="6" t="n"/>
@@ -3259,6 +3455,7 @@
       <c r="J179" s="6" t="n"/>
       <c r="K179" s="6" t="n"/>
       <c r="L179" s="6" t="n"/>
+      <c r="M179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="n"/>
@@ -3273,6 +3470,7 @@
       <c r="J180" s="6" t="n"/>
       <c r="K180" s="6" t="n"/>
       <c r="L180" s="6" t="n"/>
+      <c r="M180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="6" t="n"/>
@@ -3287,6 +3485,7 @@
       <c r="J181" s="6" t="n"/>
       <c r="K181" s="6" t="n"/>
       <c r="L181" s="6" t="n"/>
+      <c r="M181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="n"/>
@@ -3301,6 +3500,7 @@
       <c r="J182" s="6" t="n"/>
       <c r="K182" s="6" t="n"/>
       <c r="L182" s="6" t="n"/>
+      <c r="M182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="6" t="n"/>
@@ -3315,6 +3515,7 @@
       <c r="J183" s="6" t="n"/>
       <c r="K183" s="6" t="n"/>
       <c r="L183" s="6" t="n"/>
+      <c r="M183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="n"/>
@@ -3329,6 +3530,7 @@
       <c r="J184" s="6" t="n"/>
       <c r="K184" s="6" t="n"/>
       <c r="L184" s="6" t="n"/>
+      <c r="M184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="6" t="n"/>
@@ -3343,6 +3545,7 @@
       <c r="J185" s="6" t="n"/>
       <c r="K185" s="6" t="n"/>
       <c r="L185" s="6" t="n"/>
+      <c r="M185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="n"/>
@@ -3357,6 +3560,7 @@
       <c r="J186" s="6" t="n"/>
       <c r="K186" s="6" t="n"/>
       <c r="L186" s="6" t="n"/>
+      <c r="M186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="6" t="n"/>
@@ -3371,6 +3575,7 @@
       <c r="J187" s="6" t="n"/>
       <c r="K187" s="6" t="n"/>
       <c r="L187" s="6" t="n"/>
+      <c r="M187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="n"/>
@@ -3385,6 +3590,7 @@
       <c r="J188" s="6" t="n"/>
       <c r="K188" s="6" t="n"/>
       <c r="L188" s="6" t="n"/>
+      <c r="M188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="6" t="n"/>
@@ -3399,6 +3605,7 @@
       <c r="J189" s="6" t="n"/>
       <c r="K189" s="6" t="n"/>
       <c r="L189" s="6" t="n"/>
+      <c r="M189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="n"/>
@@ -3413,6 +3620,7 @@
       <c r="J190" s="6" t="n"/>
       <c r="K190" s="6" t="n"/>
       <c r="L190" s="6" t="n"/>
+      <c r="M190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="6" t="n"/>
@@ -3427,6 +3635,7 @@
       <c r="J191" s="6" t="n"/>
       <c r="K191" s="6" t="n"/>
       <c r="L191" s="6" t="n"/>
+      <c r="M191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="n"/>
@@ -3441,6 +3650,7 @@
       <c r="J192" s="6" t="n"/>
       <c r="K192" s="6" t="n"/>
       <c r="L192" s="6" t="n"/>
+      <c r="M192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="n"/>
@@ -3455,6 +3665,7 @@
       <c r="J193" s="6" t="n"/>
       <c r="K193" s="6" t="n"/>
       <c r="L193" s="6" t="n"/>
+      <c r="M193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="n"/>
@@ -3469,6 +3680,7 @@
       <c r="J194" s="6" t="n"/>
       <c r="K194" s="6" t="n"/>
       <c r="L194" s="6" t="n"/>
+      <c r="M194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="6" t="n"/>
@@ -3483,6 +3695,7 @@
       <c r="J195" s="6" t="n"/>
       <c r="K195" s="6" t="n"/>
       <c r="L195" s="6" t="n"/>
+      <c r="M195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="n"/>
@@ -3497,6 +3710,7 @@
       <c r="J196" s="6" t="n"/>
       <c r="K196" s="6" t="n"/>
       <c r="L196" s="6" t="n"/>
+      <c r="M196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="n"/>
@@ -3511,6 +3725,7 @@
       <c r="J197" s="6" t="n"/>
       <c r="K197" s="6" t="n"/>
       <c r="L197" s="6" t="n"/>
+      <c r="M197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="n"/>
@@ -3525,6 +3740,7 @@
       <c r="J198" s="6" t="n"/>
       <c r="K198" s="6" t="n"/>
       <c r="L198" s="6" t="n"/>
+      <c r="M198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="6" t="n"/>
@@ -3539,6 +3755,7 @@
       <c r="J199" s="6" t="n"/>
       <c r="K199" s="6" t="n"/>
       <c r="L199" s="6" t="n"/>
+      <c r="M199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="n"/>
@@ -3553,6 +3770,7 @@
       <c r="J200" s="6" t="n"/>
       <c r="K200" s="6" t="n"/>
       <c r="L200" s="6" t="n"/>
+      <c r="M200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="n"/>
@@ -3567,6 +3785,7 @@
       <c r="J201" s="6" t="n"/>
       <c r="K201" s="6" t="n"/>
       <c r="L201" s="6" t="n"/>
+      <c r="M201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="n"/>
@@ -3581,6 +3800,7 @@
       <c r="J202" s="6" t="n"/>
       <c r="K202" s="6" t="n"/>
       <c r="L202" s="6" t="n"/>
+      <c r="M202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="6" t="n"/>
@@ -3595,6 +3815,7 @@
       <c r="J203" s="6" t="n"/>
       <c r="K203" s="6" t="n"/>
       <c r="L203" s="6" t="n"/>
+      <c r="M203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="n"/>
@@ -3609,6 +3830,7 @@
       <c r="J204" s="6" t="n"/>
       <c r="K204" s="6" t="n"/>
       <c r="L204" s="6" t="n"/>
+      <c r="M204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="6" t="n"/>
@@ -3623,6 +3845,7 @@
       <c r="J205" s="6" t="n"/>
       <c r="K205" s="6" t="n"/>
       <c r="L205" s="6" t="n"/>
+      <c r="M205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="n"/>
@@ -3637,6 +3860,7 @@
       <c r="J206" s="6" t="n"/>
       <c r="K206" s="6" t="n"/>
       <c r="L206" s="6" t="n"/>
+      <c r="M206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="6" t="n"/>
@@ -3651,6 +3875,7 @@
       <c r="J207" s="6" t="n"/>
       <c r="K207" s="6" t="n"/>
       <c r="L207" s="6" t="n"/>
+      <c r="M207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="n"/>
@@ -3665,6 +3890,7 @@
       <c r="J208" s="6" t="n"/>
       <c r="K208" s="6" t="n"/>
       <c r="L208" s="6" t="n"/>
+      <c r="M208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="6" t="n"/>
@@ -3679,6 +3905,7 @@
       <c r="J209" s="6" t="n"/>
       <c r="K209" s="6" t="n"/>
       <c r="L209" s="6" t="n"/>
+      <c r="M209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="n"/>
@@ -3693,6 +3920,7 @@
       <c r="J210" s="6" t="n"/>
       <c r="K210" s="6" t="n"/>
       <c r="L210" s="6" t="n"/>
+      <c r="M210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="6" t="n"/>
@@ -3707,6 +3935,7 @@
       <c r="J211" s="6" t="n"/>
       <c r="K211" s="6" t="n"/>
       <c r="L211" s="6" t="n"/>
+      <c r="M211" s="6" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="n"/>
@@ -3721,6 +3950,7 @@
       <c r="J212" s="6" t="n"/>
       <c r="K212" s="6" t="n"/>
       <c r="L212" s="6" t="n"/>
+      <c r="M212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="n"/>
@@ -3735,6 +3965,7 @@
       <c r="J213" s="6" t="n"/>
       <c r="K213" s="6" t="n"/>
       <c r="L213" s="6" t="n"/>
+      <c r="M213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="n"/>
@@ -3749,6 +3980,7 @@
       <c r="J214" s="6" t="n"/>
       <c r="K214" s="6" t="n"/>
       <c r="L214" s="6" t="n"/>
+      <c r="M214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="6" t="n"/>
@@ -3763,6 +3995,7 @@
       <c r="J215" s="6" t="n"/>
       <c r="K215" s="6" t="n"/>
       <c r="L215" s="6" t="n"/>
+      <c r="M215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="n"/>
@@ -3777,6 +4010,7 @@
       <c r="J216" s="6" t="n"/>
       <c r="K216" s="6" t="n"/>
       <c r="L216" s="6" t="n"/>
+      <c r="M216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="6" t="n"/>
@@ -3791,6 +4025,7 @@
       <c r="J217" s="6" t="n"/>
       <c r="K217" s="6" t="n"/>
       <c r="L217" s="6" t="n"/>
+      <c r="M217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="n"/>
@@ -3805,6 +4040,7 @@
       <c r="J218" s="6" t="n"/>
       <c r="K218" s="6" t="n"/>
       <c r="L218" s="6" t="n"/>
+      <c r="M218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="n"/>
@@ -3819,6 +4055,7 @@
       <c r="J219" s="6" t="n"/>
       <c r="K219" s="6" t="n"/>
       <c r="L219" s="6" t="n"/>
+      <c r="M219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="n"/>
@@ -3833,6 +4070,7 @@
       <c r="J220" s="6" t="n"/>
       <c r="K220" s="6" t="n"/>
       <c r="L220" s="6" t="n"/>
+      <c r="M220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="6" t="n"/>
@@ -3847,6 +4085,7 @@
       <c r="J221" s="6" t="n"/>
       <c r="K221" s="6" t="n"/>
       <c r="L221" s="6" t="n"/>
+      <c r="M221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="n"/>
@@ -3861,6 +4100,7 @@
       <c r="J222" s="6" t="n"/>
       <c r="K222" s="6" t="n"/>
       <c r="L222" s="6" t="n"/>
+      <c r="M222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="6" t="n"/>
@@ -3875,6 +4115,7 @@
       <c r="J223" s="6" t="n"/>
       <c r="K223" s="6" t="n"/>
       <c r="L223" s="6" t="n"/>
+      <c r="M223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="n"/>
@@ -3889,6 +4130,7 @@
       <c r="J224" s="6" t="n"/>
       <c r="K224" s="6" t="n"/>
       <c r="L224" s="6" t="n"/>
+      <c r="M224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="6" t="n"/>
@@ -3903,6 +4145,7 @@
       <c r="J225" s="6" t="n"/>
       <c r="K225" s="6" t="n"/>
       <c r="L225" s="6" t="n"/>
+      <c r="M225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="n"/>
@@ -3917,6 +4160,7 @@
       <c r="J226" s="6" t="n"/>
       <c r="K226" s="6" t="n"/>
       <c r="L226" s="6" t="n"/>
+      <c r="M226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="6" t="n"/>
@@ -3931,6 +4175,7 @@
       <c r="J227" s="6" t="n"/>
       <c r="K227" s="6" t="n"/>
       <c r="L227" s="6" t="n"/>
+      <c r="M227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="n"/>
@@ -3945,6 +4190,7 @@
       <c r="J228" s="6" t="n"/>
       <c r="K228" s="6" t="n"/>
       <c r="L228" s="6" t="n"/>
+      <c r="M228" s="6" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="6" t="n"/>
@@ -3959,6 +4205,7 @@
       <c r="J229" s="6" t="n"/>
       <c r="K229" s="6" t="n"/>
       <c r="L229" s="6" t="n"/>
+      <c r="M229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="n"/>
@@ -3973,6 +4220,7 @@
       <c r="J230" s="6" t="n"/>
       <c r="K230" s="6" t="n"/>
       <c r="L230" s="6" t="n"/>
+      <c r="M230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="6" t="n"/>
@@ -3987,6 +4235,7 @@
       <c r="J231" s="6" t="n"/>
       <c r="K231" s="6" t="n"/>
       <c r="L231" s="6" t="n"/>
+      <c r="M231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="n"/>
@@ -4001,6 +4250,7 @@
       <c r="J232" s="6" t="n"/>
       <c r="K232" s="6" t="n"/>
       <c r="L232" s="6" t="n"/>
+      <c r="M232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="6" t="n"/>
@@ -4015,6 +4265,7 @@
       <c r="J233" s="6" t="n"/>
       <c r="K233" s="6" t="n"/>
       <c r="L233" s="6" t="n"/>
+      <c r="M233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="n"/>
@@ -4029,6 +4280,7 @@
       <c r="J234" s="6" t="n"/>
       <c r="K234" s="6" t="n"/>
       <c r="L234" s="6" t="n"/>
+      <c r="M234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="6" t="n"/>
@@ -4043,6 +4295,7 @@
       <c r="J235" s="6" t="n"/>
       <c r="K235" s="6" t="n"/>
       <c r="L235" s="6" t="n"/>
+      <c r="M235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="n"/>
@@ -4057,6 +4310,7 @@
       <c r="J236" s="6" t="n"/>
       <c r="K236" s="6" t="n"/>
       <c r="L236" s="6" t="n"/>
+      <c r="M236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="6" t="n"/>
@@ -4071,6 +4325,7 @@
       <c r="J237" s="6" t="n"/>
       <c r="K237" s="6" t="n"/>
       <c r="L237" s="6" t="n"/>
+      <c r="M237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="n"/>
@@ -4085,6 +4340,7 @@
       <c r="J238" s="6" t="n"/>
       <c r="K238" s="6" t="n"/>
       <c r="L238" s="6" t="n"/>
+      <c r="M238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="6" t="n"/>
@@ -4099,6 +4355,7 @@
       <c r="J239" s="6" t="n"/>
       <c r="K239" s="6" t="n"/>
       <c r="L239" s="6" t="n"/>
+      <c r="M239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="n"/>
@@ -4113,6 +4370,7 @@
       <c r="J240" s="6" t="n"/>
       <c r="K240" s="6" t="n"/>
       <c r="L240" s="6" t="n"/>
+      <c r="M240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="6" t="n"/>
@@ -4127,6 +4385,7 @@
       <c r="J241" s="6" t="n"/>
       <c r="K241" s="6" t="n"/>
       <c r="L241" s="6" t="n"/>
+      <c r="M241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="n"/>
@@ -4141,6 +4400,7 @@
       <c r="J242" s="6" t="n"/>
       <c r="K242" s="6" t="n"/>
       <c r="L242" s="6" t="n"/>
+      <c r="M242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="6" t="n"/>
@@ -4155,6 +4415,7 @@
       <c r="J243" s="6" t="n"/>
       <c r="K243" s="6" t="n"/>
       <c r="L243" s="6" t="n"/>
+      <c r="M243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="n"/>
@@ -4169,6 +4430,7 @@
       <c r="J244" s="6" t="n"/>
       <c r="K244" s="6" t="n"/>
       <c r="L244" s="6" t="n"/>
+      <c r="M244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="6" t="n"/>
@@ -4183,6 +4445,7 @@
       <c r="J245" s="6" t="n"/>
       <c r="K245" s="6" t="n"/>
       <c r="L245" s="6" t="n"/>
+      <c r="M245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="n"/>
@@ -4197,6 +4460,7 @@
       <c r="J246" s="6" t="n"/>
       <c r="K246" s="6" t="n"/>
       <c r="L246" s="6" t="n"/>
+      <c r="M246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="6" t="n"/>
@@ -4211,6 +4475,7 @@
       <c r="J247" s="6" t="n"/>
       <c r="K247" s="6" t="n"/>
       <c r="L247" s="6" t="n"/>
+      <c r="M247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="n"/>
@@ -4225,6 +4490,7 @@
       <c r="J248" s="6" t="n"/>
       <c r="K248" s="6" t="n"/>
       <c r="L248" s="6" t="n"/>
+      <c r="M248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="6" t="n"/>
@@ -4239,6 +4505,7 @@
       <c r="J249" s="6" t="n"/>
       <c r="K249" s="6" t="n"/>
       <c r="L249" s="6" t="n"/>
+      <c r="M249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="n"/>
@@ -4253,6 +4520,7 @@
       <c r="J250" s="6" t="n"/>
       <c r="K250" s="6" t="n"/>
       <c r="L250" s="6" t="n"/>
+      <c r="M250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="6" t="n"/>
@@ -4267,6 +4535,7 @@
       <c r="J251" s="6" t="n"/>
       <c r="K251" s="6" t="n"/>
       <c r="L251" s="6" t="n"/>
+      <c r="M251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="n"/>
@@ -4281,6 +4550,7 @@
       <c r="J252" s="6" t="n"/>
       <c r="K252" s="6" t="n"/>
       <c r="L252" s="6" t="n"/>
+      <c r="M252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="6" t="n"/>
@@ -4295,6 +4565,7 @@
       <c r="J253" s="6" t="n"/>
       <c r="K253" s="6" t="n"/>
       <c r="L253" s="6" t="n"/>
+      <c r="M253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="n"/>
@@ -4309,6 +4580,7 @@
       <c r="J254" s="6" t="n"/>
       <c r="K254" s="6" t="n"/>
       <c r="L254" s="6" t="n"/>
+      <c r="M254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="6" t="n"/>
@@ -4323,6 +4595,7 @@
       <c r="J255" s="6" t="n"/>
       <c r="K255" s="6" t="n"/>
       <c r="L255" s="6" t="n"/>
+      <c r="M255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="n"/>
@@ -4337,6 +4610,7 @@
       <c r="J256" s="6" t="n"/>
       <c r="K256" s="6" t="n"/>
       <c r="L256" s="6" t="n"/>
+      <c r="M256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="6" t="n"/>
@@ -4351,6 +4625,7 @@
       <c r="J257" s="6" t="n"/>
       <c r="K257" s="6" t="n"/>
       <c r="L257" s="6" t="n"/>
+      <c r="M257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="n"/>
@@ -4365,6 +4640,7 @@
       <c r="J258" s="6" t="n"/>
       <c r="K258" s="6" t="n"/>
       <c r="L258" s="6" t="n"/>
+      <c r="M258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="6" t="n"/>
@@ -4379,6 +4655,7 @@
       <c r="J259" s="6" t="n"/>
       <c r="K259" s="6" t="n"/>
       <c r="L259" s="6" t="n"/>
+      <c r="M259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="n"/>
@@ -4393,6 +4670,7 @@
       <c r="J260" s="6" t="n"/>
       <c r="K260" s="6" t="n"/>
       <c r="L260" s="6" t="n"/>
+      <c r="M260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="6" t="n"/>
@@ -4407,6 +4685,7 @@
       <c r="J261" s="6" t="n"/>
       <c r="K261" s="6" t="n"/>
       <c r="L261" s="6" t="n"/>
+      <c r="M261" s="6" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="n"/>
@@ -4421,6 +4700,7 @@
       <c r="J262" s="6" t="n"/>
       <c r="K262" s="6" t="n"/>
       <c r="L262" s="6" t="n"/>
+      <c r="M262" s="6" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="6" t="n"/>
@@ -4435,6 +4715,7 @@
       <c r="J263" s="6" t="n"/>
       <c r="K263" s="6" t="n"/>
       <c r="L263" s="6" t="n"/>
+      <c r="M263" s="6" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="6" t="n"/>
@@ -4449,6 +4730,7 @@
       <c r="J264" s="6" t="n"/>
       <c r="K264" s="6" t="n"/>
       <c r="L264" s="6" t="n"/>
+      <c r="M264" s="6" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="6" t="n"/>
@@ -4463,6 +4745,7 @@
       <c r="J265" s="6" t="n"/>
       <c r="K265" s="6" t="n"/>
       <c r="L265" s="6" t="n"/>
+      <c r="M265" s="6" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="6" t="n"/>
@@ -4477,6 +4760,7 @@
       <c r="J266" s="6" t="n"/>
       <c r="K266" s="6" t="n"/>
       <c r="L266" s="6" t="n"/>
+      <c r="M266" s="6" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="6" t="n"/>
@@ -4491,6 +4775,7 @@
       <c r="J267" s="6" t="n"/>
       <c r="K267" s="6" t="n"/>
       <c r="L267" s="6" t="n"/>
+      <c r="M267" s="6" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="6" t="n"/>
@@ -4505,6 +4790,7 @@
       <c r="J268" s="6" t="n"/>
       <c r="K268" s="6" t="n"/>
       <c r="L268" s="6" t="n"/>
+      <c r="M268" s="6" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="6" t="n"/>
@@ -4519,6 +4805,7 @@
       <c r="J269" s="6" t="n"/>
       <c r="K269" s="6" t="n"/>
       <c r="L269" s="6" t="n"/>
+      <c r="M269" s="6" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="6" t="n"/>
@@ -4533,6 +4820,7 @@
       <c r="J270" s="6" t="n"/>
       <c r="K270" s="6" t="n"/>
       <c r="L270" s="6" t="n"/>
+      <c r="M270" s="6" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="6" t="n"/>
@@ -4547,6 +4835,7 @@
       <c r="J271" s="6" t="n"/>
       <c r="K271" s="6" t="n"/>
       <c r="L271" s="6" t="n"/>
+      <c r="M271" s="6" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="6" t="n"/>
@@ -4561,6 +4850,7 @@
       <c r="J272" s="6" t="n"/>
       <c r="K272" s="6" t="n"/>
       <c r="L272" s="6" t="n"/>
+      <c r="M272" s="6" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="6" t="n"/>
@@ -4575,6 +4865,7 @@
       <c r="J273" s="6" t="n"/>
       <c r="K273" s="6" t="n"/>
       <c r="L273" s="6" t="n"/>
+      <c r="M273" s="6" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="6" t="n"/>
@@ -4589,6 +4880,7 @@
       <c r="J274" s="6" t="n"/>
       <c r="K274" s="6" t="n"/>
       <c r="L274" s="6" t="n"/>
+      <c r="M274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="6" t="n"/>
@@ -4603,6 +4895,7 @@
       <c r="J275" s="6" t="n"/>
       <c r="K275" s="6" t="n"/>
       <c r="L275" s="6" t="n"/>
+      <c r="M275" s="6" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="6" t="n"/>
@@ -4617,6 +4910,7 @@
       <c r="J276" s="6" t="n"/>
       <c r="K276" s="6" t="n"/>
       <c r="L276" s="6" t="n"/>
+      <c r="M276" s="6" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="6" t="n"/>
@@ -4631,6 +4925,7 @@
       <c r="J277" s="6" t="n"/>
       <c r="K277" s="6" t="n"/>
       <c r="L277" s="6" t="n"/>
+      <c r="M277" s="6" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="6" t="n"/>
@@ -4645,6 +4940,7 @@
       <c r="J278" s="6" t="n"/>
       <c r="K278" s="6" t="n"/>
       <c r="L278" s="6" t="n"/>
+      <c r="M278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="6" t="n"/>
@@ -4659,6 +4955,7 @@
       <c r="J279" s="6" t="n"/>
       <c r="K279" s="6" t="n"/>
       <c r="L279" s="6" t="n"/>
+      <c r="M279" s="6" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="6" t="n"/>
@@ -4673,6 +4970,7 @@
       <c r="J280" s="6" t="n"/>
       <c r="K280" s="6" t="n"/>
       <c r="L280" s="6" t="n"/>
+      <c r="M280" s="6" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="6" t="n"/>
@@ -4687,6 +4985,7 @@
       <c r="J281" s="6" t="n"/>
       <c r="K281" s="6" t="n"/>
       <c r="L281" s="6" t="n"/>
+      <c r="M281" s="6" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="6" t="n"/>
@@ -4701,6 +5000,7 @@
       <c r="J282" s="6" t="n"/>
       <c r="K282" s="6" t="n"/>
       <c r="L282" s="6" t="n"/>
+      <c r="M282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="6" t="n"/>
@@ -4715,6 +5015,7 @@
       <c r="J283" s="6" t="n"/>
       <c r="K283" s="6" t="n"/>
       <c r="L283" s="6" t="n"/>
+      <c r="M283" s="6" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="6" t="n"/>
@@ -4729,6 +5030,7 @@
       <c r="J284" s="6" t="n"/>
       <c r="K284" s="6" t="n"/>
       <c r="L284" s="6" t="n"/>
+      <c r="M284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="6" t="n"/>
@@ -4743,6 +5045,7 @@
       <c r="J285" s="6" t="n"/>
       <c r="K285" s="6" t="n"/>
       <c r="L285" s="6" t="n"/>
+      <c r="M285" s="6" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="6" t="n"/>
@@ -4757,6 +5060,7 @@
       <c r="J286" s="6" t="n"/>
       <c r="K286" s="6" t="n"/>
       <c r="L286" s="6" t="n"/>
+      <c r="M286" s="6" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="6" t="n"/>
@@ -4771,6 +5075,7 @@
       <c r="J287" s="6" t="n"/>
       <c r="K287" s="6" t="n"/>
       <c r="L287" s="6" t="n"/>
+      <c r="M287" s="6" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="6" t="n"/>
@@ -4785,6 +5090,7 @@
       <c r="J288" s="6" t="n"/>
       <c r="K288" s="6" t="n"/>
       <c r="L288" s="6" t="n"/>
+      <c r="M288" s="6" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="6" t="n"/>
@@ -4799,6 +5105,7 @@
       <c r="J289" s="6" t="n"/>
       <c r="K289" s="6" t="n"/>
       <c r="L289" s="6" t="n"/>
+      <c r="M289" s="6" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="6" t="n"/>
@@ -4813,6 +5120,7 @@
       <c r="J290" s="6" t="n"/>
       <c r="K290" s="6" t="n"/>
       <c r="L290" s="6" t="n"/>
+      <c r="M290" s="6" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="6" t="n"/>
@@ -4827,6 +5135,7 @@
       <c r="J291" s="6" t="n"/>
       <c r="K291" s="6" t="n"/>
       <c r="L291" s="6" t="n"/>
+      <c r="M291" s="6" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="6" t="n"/>
@@ -4841,6 +5150,7 @@
       <c r="J292" s="6" t="n"/>
       <c r="K292" s="6" t="n"/>
       <c r="L292" s="6" t="n"/>
+      <c r="M292" s="6" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="6" t="n"/>
@@ -4855,6 +5165,7 @@
       <c r="J293" s="6" t="n"/>
       <c r="K293" s="6" t="n"/>
       <c r="L293" s="6" t="n"/>
+      <c r="M293" s="6" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="6" t="n"/>
@@ -4869,6 +5180,7 @@
       <c r="J294" s="6" t="n"/>
       <c r="K294" s="6" t="n"/>
       <c r="L294" s="6" t="n"/>
+      <c r="M294" s="6" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="6" t="n"/>
@@ -4883,6 +5195,7 @@
       <c r="J295" s="6" t="n"/>
       <c r="K295" s="6" t="n"/>
       <c r="L295" s="6" t="n"/>
+      <c r="M295" s="6" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="6" t="n"/>
@@ -4897,6 +5210,7 @@
       <c r="J296" s="6" t="n"/>
       <c r="K296" s="6" t="n"/>
       <c r="L296" s="6" t="n"/>
+      <c r="M296" s="6" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="6" t="n"/>
@@ -4911,6 +5225,7 @@
       <c r="J297" s="6" t="n"/>
       <c r="K297" s="6" t="n"/>
       <c r="L297" s="6" t="n"/>
+      <c r="M297" s="6" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="6" t="n"/>
@@ -4925,6 +5240,7 @@
       <c r="J298" s="6" t="n"/>
       <c r="K298" s="6" t="n"/>
       <c r="L298" s="6" t="n"/>
+      <c r="M298" s="6" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="6" t="n"/>
@@ -4939,6 +5255,7 @@
       <c r="J299" s="6" t="n"/>
       <c r="K299" s="6" t="n"/>
       <c r="L299" s="6" t="n"/>
+      <c r="M299" s="6" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="6" t="n"/>
@@ -4953,6 +5270,7 @@
       <c r="J300" s="6" t="n"/>
       <c r="K300" s="6" t="n"/>
       <c r="L300" s="6" t="n"/>
+      <c r="M300" s="6" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="6" t="n"/>
@@ -4967,6 +5285,7 @@
       <c r="J301" s="6" t="n"/>
       <c r="K301" s="6" t="n"/>
       <c r="L301" s="6" t="n"/>
+      <c r="M301" s="6" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="6" t="n"/>
@@ -4981,6 +5300,7 @@
       <c r="J302" s="6" t="n"/>
       <c r="K302" s="6" t="n"/>
       <c r="L302" s="6" t="n"/>
+      <c r="M302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="6" t="n"/>
@@ -4995,6 +5315,7 @@
       <c r="J303" s="6" t="n"/>
       <c r="K303" s="6" t="n"/>
       <c r="L303" s="6" t="n"/>
+      <c r="M303" s="6" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="6" t="n"/>
@@ -5009,6 +5330,7 @@
       <c r="J304" s="6" t="n"/>
       <c r="K304" s="6" t="n"/>
       <c r="L304" s="6" t="n"/>
+      <c r="M304" s="6" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="6" t="n"/>
@@ -5023,6 +5345,7 @@
       <c r="J305" s="6" t="n"/>
       <c r="K305" s="6" t="n"/>
       <c r="L305" s="6" t="n"/>
+      <c r="M305" s="6" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="6" t="n"/>
@@ -5037,6 +5360,7 @@
       <c r="J306" s="6" t="n"/>
       <c r="K306" s="6" t="n"/>
       <c r="L306" s="6" t="n"/>
+      <c r="M306" s="6" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="6" t="n"/>
@@ -5051,6 +5375,7 @@
       <c r="J307" s="6" t="n"/>
       <c r="K307" s="6" t="n"/>
       <c r="L307" s="6" t="n"/>
+      <c r="M307" s="6" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="6" t="n"/>
@@ -5065,6 +5390,7 @@
       <c r="J308" s="6" t="n"/>
       <c r="K308" s="6" t="n"/>
       <c r="L308" s="6" t="n"/>
+      <c r="M308" s="6" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="6" t="n"/>
@@ -5079,6 +5405,7 @@
       <c r="J309" s="6" t="n"/>
       <c r="K309" s="6" t="n"/>
       <c r="L309" s="6" t="n"/>
+      <c r="M309" s="6" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="6" t="n"/>
@@ -5093,6 +5420,7 @@
       <c r="J310" s="6" t="n"/>
       <c r="K310" s="6" t="n"/>
       <c r="L310" s="6" t="n"/>
+      <c r="M310" s="6" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="6" t="n"/>
@@ -5107,6 +5435,7 @@
       <c r="J311" s="6" t="n"/>
       <c r="K311" s="6" t="n"/>
       <c r="L311" s="6" t="n"/>
+      <c r="M311" s="6" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="6" t="n"/>
@@ -5121,6 +5450,7 @@
       <c r="J312" s="6" t="n"/>
       <c r="K312" s="6" t="n"/>
       <c r="L312" s="6" t="n"/>
+      <c r="M312" s="6" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="6" t="n"/>
@@ -5135,6 +5465,7 @@
       <c r="J313" s="6" t="n"/>
       <c r="K313" s="6" t="n"/>
       <c r="L313" s="6" t="n"/>
+      <c r="M313" s="6" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="6" t="n"/>
@@ -5149,6 +5480,7 @@
       <c r="J314" s="6" t="n"/>
       <c r="K314" s="6" t="n"/>
       <c r="L314" s="6" t="n"/>
+      <c r="M314" s="6" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="6" t="n"/>
@@ -5163,6 +5495,7 @@
       <c r="J315" s="6" t="n"/>
       <c r="K315" s="6" t="n"/>
       <c r="L315" s="6" t="n"/>
+      <c r="M315" s="6" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="6" t="n"/>
@@ -5177,6 +5510,7 @@
       <c r="J316" s="6" t="n"/>
       <c r="K316" s="6" t="n"/>
       <c r="L316" s="6" t="n"/>
+      <c r="M316" s="6" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="6" t="n"/>
@@ -5191,6 +5525,7 @@
       <c r="J317" s="6" t="n"/>
       <c r="K317" s="6" t="n"/>
       <c r="L317" s="6" t="n"/>
+      <c r="M317" s="6" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="6" t="n"/>
@@ -5205,6 +5540,7 @@
       <c r="J318" s="6" t="n"/>
       <c r="K318" s="6" t="n"/>
       <c r="L318" s="6" t="n"/>
+      <c r="M318" s="6" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="6" t="n"/>
@@ -5219,6 +5555,7 @@
       <c r="J319" s="6" t="n"/>
       <c r="K319" s="6" t="n"/>
       <c r="L319" s="6" t="n"/>
+      <c r="M319" s="6" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="6" t="n"/>
@@ -5233,6 +5570,7 @@
       <c r="J320" s="6" t="n"/>
       <c r="K320" s="6" t="n"/>
       <c r="L320" s="6" t="n"/>
+      <c r="M320" s="6" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="6" t="n"/>
@@ -5247,6 +5585,7 @@
       <c r="J321" s="6" t="n"/>
       <c r="K321" s="6" t="n"/>
       <c r="L321" s="6" t="n"/>
+      <c r="M321" s="6" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="6" t="n"/>
@@ -5261,6 +5600,7 @@
       <c r="J322" s="6" t="n"/>
       <c r="K322" s="6" t="n"/>
       <c r="L322" s="6" t="n"/>
+      <c r="M322" s="6" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="6" t="n"/>
@@ -5275,6 +5615,7 @@
       <c r="J323" s="6" t="n"/>
       <c r="K323" s="6" t="n"/>
       <c r="L323" s="6" t="n"/>
+      <c r="M323" s="6" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="6" t="n"/>
@@ -5289,6 +5630,7 @@
       <c r="J324" s="6" t="n"/>
       <c r="K324" s="6" t="n"/>
       <c r="L324" s="6" t="n"/>
+      <c r="M324" s="6" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="6" t="n"/>
@@ -5303,6 +5645,7 @@
       <c r="J325" s="6" t="n"/>
       <c r="K325" s="6" t="n"/>
       <c r="L325" s="6" t="n"/>
+      <c r="M325" s="6" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="6" t="n"/>
@@ -5317,6 +5660,7 @@
       <c r="J326" s="6" t="n"/>
       <c r="K326" s="6" t="n"/>
       <c r="L326" s="6" t="n"/>
+      <c r="M326" s="6" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="6" t="n"/>
@@ -5331,6 +5675,7 @@
       <c r="J327" s="6" t="n"/>
       <c r="K327" s="6" t="n"/>
       <c r="L327" s="6" t="n"/>
+      <c r="M327" s="6" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="6" t="n"/>
@@ -5345,6 +5690,7 @@
       <c r="J328" s="6" t="n"/>
       <c r="K328" s="6" t="n"/>
       <c r="L328" s="6" t="n"/>
+      <c r="M328" s="6" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="6" t="n"/>
@@ -5359,6 +5705,7 @@
       <c r="J329" s="6" t="n"/>
       <c r="K329" s="6" t="n"/>
       <c r="L329" s="6" t="n"/>
+      <c r="M329" s="6" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="6" t="n"/>
@@ -5373,6 +5720,7 @@
       <c r="J330" s="6" t="n"/>
       <c r="K330" s="6" t="n"/>
       <c r="L330" s="6" t="n"/>
+      <c r="M330" s="6" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="6" t="n"/>
@@ -5387,6 +5735,7 @@
       <c r="J331" s="6" t="n"/>
       <c r="K331" s="6" t="n"/>
       <c r="L331" s="6" t="n"/>
+      <c r="M331" s="6" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="6" t="n"/>
@@ -5401,6 +5750,7 @@
       <c r="J332" s="6" t="n"/>
       <c r="K332" s="6" t="n"/>
       <c r="L332" s="6" t="n"/>
+      <c r="M332" s="6" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="6" t="n"/>
@@ -5415,6 +5765,7 @@
       <c r="J333" s="6" t="n"/>
       <c r="K333" s="6" t="n"/>
       <c r="L333" s="6" t="n"/>
+      <c r="M333" s="6" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="6" t="n"/>
@@ -5429,6 +5780,7 @@
       <c r="J334" s="6" t="n"/>
       <c r="K334" s="6" t="n"/>
       <c r="L334" s="6" t="n"/>
+      <c r="M334" s="6" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="6" t="n"/>
@@ -5443,6 +5795,7 @@
       <c r="J335" s="6" t="n"/>
       <c r="K335" s="6" t="n"/>
       <c r="L335" s="6" t="n"/>
+      <c r="M335" s="6" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="6" t="n"/>
@@ -5457,6 +5810,7 @@
       <c r="J336" s="6" t="n"/>
       <c r="K336" s="6" t="n"/>
       <c r="L336" s="6" t="n"/>
+      <c r="M336" s="6" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="6" t="n"/>
@@ -5471,6 +5825,7 @@
       <c r="J337" s="6" t="n"/>
       <c r="K337" s="6" t="n"/>
       <c r="L337" s="6" t="n"/>
+      <c r="M337" s="6" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="6" t="n"/>
@@ -5485,6 +5840,7 @@
       <c r="J338" s="6" t="n"/>
       <c r="K338" s="6" t="n"/>
       <c r="L338" s="6" t="n"/>
+      <c r="M338" s="6" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="6" t="n"/>
@@ -5499,6 +5855,7 @@
       <c r="J339" s="6" t="n"/>
       <c r="K339" s="6" t="n"/>
       <c r="L339" s="6" t="n"/>
+      <c r="M339" s="6" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="6" t="n"/>
@@ -5513,6 +5870,7 @@
       <c r="J340" s="6" t="n"/>
       <c r="K340" s="6" t="n"/>
       <c r="L340" s="6" t="n"/>
+      <c r="M340" s="6" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="6" t="n"/>
@@ -5527,6 +5885,7 @@
       <c r="J341" s="6" t="n"/>
       <c r="K341" s="6" t="n"/>
       <c r="L341" s="6" t="n"/>
+      <c r="M341" s="6" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="6" t="n"/>
@@ -5541,6 +5900,7 @@
       <c r="J342" s="6" t="n"/>
       <c r="K342" s="6" t="n"/>
       <c r="L342" s="6" t="n"/>
+      <c r="M342" s="6" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="6" t="n"/>
@@ -5555,6 +5915,7 @@
       <c r="J343" s="6" t="n"/>
       <c r="K343" s="6" t="n"/>
       <c r="L343" s="6" t="n"/>
+      <c r="M343" s="6" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="6" t="n"/>
@@ -5569,6 +5930,7 @@
       <c r="J344" s="6" t="n"/>
       <c r="K344" s="6" t="n"/>
       <c r="L344" s="6" t="n"/>
+      <c r="M344" s="6" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="6" t="n"/>
@@ -5583,6 +5945,7 @@
       <c r="J345" s="6" t="n"/>
       <c r="K345" s="6" t="n"/>
       <c r="L345" s="6" t="n"/>
+      <c r="M345" s="6" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="6" t="n"/>
@@ -5597,6 +5960,7 @@
       <c r="J346" s="6" t="n"/>
       <c r="K346" s="6" t="n"/>
       <c r="L346" s="6" t="n"/>
+      <c r="M346" s="6" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="6" t="n"/>
@@ -5611,6 +5975,7 @@
       <c r="J347" s="6" t="n"/>
       <c r="K347" s="6" t="n"/>
       <c r="L347" s="6" t="n"/>
+      <c r="M347" s="6" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="6" t="n"/>
@@ -5625,6 +5990,7 @@
       <c r="J348" s="6" t="n"/>
       <c r="K348" s="6" t="n"/>
       <c r="L348" s="6" t="n"/>
+      <c r="M348" s="6" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="6" t="n"/>
@@ -5639,6 +6005,7 @@
       <c r="J349" s="6" t="n"/>
       <c r="K349" s="6" t="n"/>
       <c r="L349" s="6" t="n"/>
+      <c r="M349" s="6" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="6" t="n"/>
@@ -5653,6 +6020,7 @@
       <c r="J350" s="6" t="n"/>
       <c r="K350" s="6" t="n"/>
       <c r="L350" s="6" t="n"/>
+      <c r="M350" s="6" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="6" t="n"/>
@@ -5667,6 +6035,7 @@
       <c r="J351" s="6" t="n"/>
       <c r="K351" s="6" t="n"/>
       <c r="L351" s="6" t="n"/>
+      <c r="M351" s="6" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="6" t="n"/>
@@ -5681,6 +6050,7 @@
       <c r="J352" s="6" t="n"/>
       <c r="K352" s="6" t="n"/>
       <c r="L352" s="6" t="n"/>
+      <c r="M352" s="6" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="6" t="n"/>
@@ -5695,6 +6065,7 @@
       <c r="J353" s="6" t="n"/>
       <c r="K353" s="6" t="n"/>
       <c r="L353" s="6" t="n"/>
+      <c r="M353" s="6" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="6" t="n"/>
@@ -5709,6 +6080,7 @@
       <c r="J354" s="6" t="n"/>
       <c r="K354" s="6" t="n"/>
       <c r="L354" s="6" t="n"/>
+      <c r="M354" s="6" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="6" t="n"/>
@@ -5723,6 +6095,7 @@
       <c r="J355" s="6" t="n"/>
       <c r="K355" s="6" t="n"/>
       <c r="L355" s="6" t="n"/>
+      <c r="M355" s="6" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="6" t="n"/>
@@ -5737,6 +6110,7 @@
       <c r="J356" s="6" t="n"/>
       <c r="K356" s="6" t="n"/>
       <c r="L356" s="6" t="n"/>
+      <c r="M356" s="6" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="6" t="n"/>
@@ -5751,6 +6125,7 @@
       <c r="J357" s="6" t="n"/>
       <c r="K357" s="6" t="n"/>
       <c r="L357" s="6" t="n"/>
+      <c r="M357" s="6" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="6" t="n"/>
@@ -5765,6 +6140,7 @@
       <c r="J358" s="6" t="n"/>
       <c r="K358" s="6" t="n"/>
       <c r="L358" s="6" t="n"/>
+      <c r="M358" s="6" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="6" t="n"/>
@@ -5779,6 +6155,7 @@
       <c r="J359" s="6" t="n"/>
       <c r="K359" s="6" t="n"/>
       <c r="L359" s="6" t="n"/>
+      <c r="M359" s="6" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="6" t="n"/>
@@ -5793,6 +6170,7 @@
       <c r="J360" s="6" t="n"/>
       <c r="K360" s="6" t="n"/>
       <c r="L360" s="6" t="n"/>
+      <c r="M360" s="6" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="6" t="n"/>
@@ -5807,6 +6185,7 @@
       <c r="J361" s="6" t="n"/>
       <c r="K361" s="6" t="n"/>
       <c r="L361" s="6" t="n"/>
+      <c r="M361" s="6" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="6" t="n"/>
@@ -5821,6 +6200,7 @@
       <c r="J362" s="6" t="n"/>
       <c r="K362" s="6" t="n"/>
       <c r="L362" s="6" t="n"/>
+      <c r="M362" s="6" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="6" t="n"/>
@@ -5835,6 +6215,7 @@
       <c r="J363" s="6" t="n"/>
       <c r="K363" s="6" t="n"/>
       <c r="L363" s="6" t="n"/>
+      <c r="M363" s="6" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="6" t="n"/>
@@ -5849,6 +6230,7 @@
       <c r="J364" s="6" t="n"/>
       <c r="K364" s="6" t="n"/>
       <c r="L364" s="6" t="n"/>
+      <c r="M364" s="6" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="6" t="n"/>
@@ -5863,6 +6245,7 @@
       <c r="J365" s="6" t="n"/>
       <c r="K365" s="6" t="n"/>
       <c r="L365" s="6" t="n"/>
+      <c r="M365" s="6" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="6" t="n"/>
@@ -5877,6 +6260,7 @@
       <c r="J366" s="6" t="n"/>
       <c r="K366" s="6" t="n"/>
       <c r="L366" s="6" t="n"/>
+      <c r="M366" s="6" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="6" t="n"/>
@@ -5891,6 +6275,7 @@
       <c r="J367" s="6" t="n"/>
       <c r="K367" s="6" t="n"/>
       <c r="L367" s="6" t="n"/>
+      <c r="M367" s="6" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="6" t="n"/>
@@ -5905,6 +6290,7 @@
       <c r="J368" s="6" t="n"/>
       <c r="K368" s="6" t="n"/>
       <c r="L368" s="6" t="n"/>
+      <c r="M368" s="6" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="6" t="n"/>
@@ -5919,6 +6305,7 @@
       <c r="J369" s="6" t="n"/>
       <c r="K369" s="6" t="n"/>
       <c r="L369" s="6" t="n"/>
+      <c r="M369" s="6" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="6" t="n"/>
@@ -5933,6 +6320,7 @@
       <c r="J370" s="6" t="n"/>
       <c r="K370" s="6" t="n"/>
       <c r="L370" s="6" t="n"/>
+      <c r="M370" s="6" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="6" t="n"/>
@@ -5947,6 +6335,7 @@
       <c r="J371" s="6" t="n"/>
       <c r="K371" s="6" t="n"/>
       <c r="L371" s="6" t="n"/>
+      <c r="M371" s="6" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="6" t="n"/>
@@ -5961,6 +6350,7 @@
       <c r="J372" s="6" t="n"/>
       <c r="K372" s="6" t="n"/>
       <c r="L372" s="6" t="n"/>
+      <c r="M372" s="6" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="6" t="n"/>
@@ -5975,6 +6365,7 @@
       <c r="J373" s="6" t="n"/>
       <c r="K373" s="6" t="n"/>
       <c r="L373" s="6" t="n"/>
+      <c r="M373" s="6" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="6" t="n"/>
@@ -5989,6 +6380,7 @@
       <c r="J374" s="6" t="n"/>
       <c r="K374" s="6" t="n"/>
       <c r="L374" s="6" t="n"/>
+      <c r="M374" s="6" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="6" t="n"/>
@@ -6003,6 +6395,7 @@
       <c r="J375" s="6" t="n"/>
       <c r="K375" s="6" t="n"/>
       <c r="L375" s="6" t="n"/>
+      <c r="M375" s="6" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="6" t="n"/>
@@ -6017,6 +6410,7 @@
       <c r="J376" s="6" t="n"/>
       <c r="K376" s="6" t="n"/>
       <c r="L376" s="6" t="n"/>
+      <c r="M376" s="6" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="6" t="n"/>
@@ -6031,6 +6425,7 @@
       <c r="J377" s="6" t="n"/>
       <c r="K377" s="6" t="n"/>
       <c r="L377" s="6" t="n"/>
+      <c r="M377" s="6" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="6" t="n"/>
@@ -6045,6 +6440,7 @@
       <c r="J378" s="6" t="n"/>
       <c r="K378" s="6" t="n"/>
       <c r="L378" s="6" t="n"/>
+      <c r="M378" s="6" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="6" t="n"/>
@@ -6059,6 +6455,7 @@
       <c r="J379" s="6" t="n"/>
       <c r="K379" s="6" t="n"/>
       <c r="L379" s="6" t="n"/>
+      <c r="M379" s="6" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="6" t="n"/>
@@ -6073,6 +6470,7 @@
       <c r="J380" s="6" t="n"/>
       <c r="K380" s="6" t="n"/>
       <c r="L380" s="6" t="n"/>
+      <c r="M380" s="6" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="6" t="n"/>
@@ -6087,6 +6485,7 @@
       <c r="J381" s="6" t="n"/>
       <c r="K381" s="6" t="n"/>
       <c r="L381" s="6" t="n"/>
+      <c r="M381" s="6" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="6" t="n"/>
@@ -6101,6 +6500,7 @@
       <c r="J382" s="6" t="n"/>
       <c r="K382" s="6" t="n"/>
       <c r="L382" s="6" t="n"/>
+      <c r="M382" s="6" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="6" t="n"/>
@@ -6115,6 +6515,7 @@
       <c r="J383" s="6" t="n"/>
       <c r="K383" s="6" t="n"/>
       <c r="L383" s="6" t="n"/>
+      <c r="M383" s="6" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="6" t="n"/>
@@ -6129,6 +6530,7 @@
       <c r="J384" s="6" t="n"/>
       <c r="K384" s="6" t="n"/>
       <c r="L384" s="6" t="n"/>
+      <c r="M384" s="6" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="6" t="n"/>
@@ -6143,6 +6545,7 @@
       <c r="J385" s="6" t="n"/>
       <c r="K385" s="6" t="n"/>
       <c r="L385" s="6" t="n"/>
+      <c r="M385" s="6" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="6" t="n"/>
@@ -6157,6 +6560,7 @@
       <c r="J386" s="6" t="n"/>
       <c r="K386" s="6" t="n"/>
       <c r="L386" s="6" t="n"/>
+      <c r="M386" s="6" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="6" t="n"/>
@@ -6171,6 +6575,7 @@
       <c r="J387" s="6" t="n"/>
       <c r="K387" s="6" t="n"/>
       <c r="L387" s="6" t="n"/>
+      <c r="M387" s="6" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="6" t="n"/>
@@ -6185,6 +6590,7 @@
       <c r="J388" s="6" t="n"/>
       <c r="K388" s="6" t="n"/>
       <c r="L388" s="6" t="n"/>
+      <c r="M388" s="6" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="6" t="n"/>
@@ -6199,6 +6605,7 @@
       <c r="J389" s="6" t="n"/>
       <c r="K389" s="6" t="n"/>
       <c r="L389" s="6" t="n"/>
+      <c r="M389" s="6" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="6" t="n"/>
@@ -6213,6 +6620,7 @@
       <c r="J390" s="6" t="n"/>
       <c r="K390" s="6" t="n"/>
       <c r="L390" s="6" t="n"/>
+      <c r="M390" s="6" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="6" t="n"/>
@@ -6227,6 +6635,7 @@
       <c r="J391" s="6" t="n"/>
       <c r="K391" s="6" t="n"/>
       <c r="L391" s="6" t="n"/>
+      <c r="M391" s="6" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="6" t="n"/>
@@ -6241,6 +6650,7 @@
       <c r="J392" s="6" t="n"/>
       <c r="K392" s="6" t="n"/>
       <c r="L392" s="6" t="n"/>
+      <c r="M392" s="6" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="6" t="n"/>
@@ -6255,6 +6665,7 @@
       <c r="J393" s="6" t="n"/>
       <c r="K393" s="6" t="n"/>
       <c r="L393" s="6" t="n"/>
+      <c r="M393" s="6" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="6" t="n"/>
@@ -6269,6 +6680,7 @@
       <c r="J394" s="6" t="n"/>
       <c r="K394" s="6" t="n"/>
       <c r="L394" s="6" t="n"/>
+      <c r="M394" s="6" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="6" t="n"/>
@@ -6283,6 +6695,7 @@
       <c r="J395" s="6" t="n"/>
       <c r="K395" s="6" t="n"/>
       <c r="L395" s="6" t="n"/>
+      <c r="M395" s="6" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="6" t="n"/>
@@ -6297,6 +6710,7 @@
       <c r="J396" s="6" t="n"/>
       <c r="K396" s="6" t="n"/>
       <c r="L396" s="6" t="n"/>
+      <c r="M396" s="6" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="6" t="n"/>
@@ -6311,6 +6725,7 @@
       <c r="J397" s="6" t="n"/>
       <c r="K397" s="6" t="n"/>
       <c r="L397" s="6" t="n"/>
+      <c r="M397" s="6" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="6" t="n"/>
@@ -6325,6 +6740,7 @@
       <c r="J398" s="6" t="n"/>
       <c r="K398" s="6" t="n"/>
       <c r="L398" s="6" t="n"/>
+      <c r="M398" s="6" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="6" t="n"/>
@@ -6339,6 +6755,7 @@
       <c r="J399" s="6" t="n"/>
       <c r="K399" s="6" t="n"/>
       <c r="L399" s="6" t="n"/>
+      <c r="M399" s="6" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="6" t="n"/>
@@ -6353,6 +6770,7 @@
       <c r="J400" s="6" t="n"/>
       <c r="K400" s="6" t="n"/>
       <c r="L400" s="6" t="n"/>
+      <c r="M400" s="6" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="6" t="n"/>
@@ -6367,6 +6785,7 @@
       <c r="J401" s="6" t="n"/>
       <c r="K401" s="6" t="n"/>
       <c r="L401" s="6" t="n"/>
+      <c r="M401" s="6" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="6" t="n"/>
@@ -6381,6 +6800,7 @@
       <c r="J402" s="6" t="n"/>
       <c r="K402" s="6" t="n"/>
       <c r="L402" s="6" t="n"/>
+      <c r="M402" s="6" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="6" t="n"/>
@@ -6395,6 +6815,7 @@
       <c r="J403" s="6" t="n"/>
       <c r="K403" s="6" t="n"/>
       <c r="L403" s="6" t="n"/>
+      <c r="M403" s="6" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="6" t="n"/>
@@ -6409,6 +6830,7 @@
       <c r="J404" s="6" t="n"/>
       <c r="K404" s="6" t="n"/>
       <c r="L404" s="6" t="n"/>
+      <c r="M404" s="6" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="6" t="n"/>
@@ -6423,6 +6845,7 @@
       <c r="J405" s="6" t="n"/>
       <c r="K405" s="6" t="n"/>
       <c r="L405" s="6" t="n"/>
+      <c r="M405" s="6" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="6" t="n"/>
@@ -6437,6 +6860,7 @@
       <c r="J406" s="6" t="n"/>
       <c r="K406" s="6" t="n"/>
       <c r="L406" s="6" t="n"/>
+      <c r="M406" s="6" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="6" t="n"/>
@@ -6451,6 +6875,7 @@
       <c r="J407" s="6" t="n"/>
       <c r="K407" s="6" t="n"/>
       <c r="L407" s="6" t="n"/>
+      <c r="M407" s="6" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="6" t="n"/>
@@ -6465,6 +6890,7 @@
       <c r="J408" s="6" t="n"/>
       <c r="K408" s="6" t="n"/>
       <c r="L408" s="6" t="n"/>
+      <c r="M408" s="6" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="6" t="n"/>
@@ -6479,6 +6905,7 @@
       <c r="J409" s="6" t="n"/>
       <c r="K409" s="6" t="n"/>
       <c r="L409" s="6" t="n"/>
+      <c r="M409" s="6" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="6" t="n"/>
@@ -6493,6 +6920,7 @@
       <c r="J410" s="6" t="n"/>
       <c r="K410" s="6" t="n"/>
       <c r="L410" s="6" t="n"/>
+      <c r="M410" s="6" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="6" t="n"/>
@@ -6507,6 +6935,7 @@
       <c r="J411" s="6" t="n"/>
       <c r="K411" s="6" t="n"/>
       <c r="L411" s="6" t="n"/>
+      <c r="M411" s="6" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="6" t="n"/>
@@ -6521,6 +6950,7 @@
       <c r="J412" s="6" t="n"/>
       <c r="K412" s="6" t="n"/>
       <c r="L412" s="6" t="n"/>
+      <c r="M412" s="6" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="6" t="n"/>
@@ -6535,6 +6965,7 @@
       <c r="J413" s="6" t="n"/>
       <c r="K413" s="6" t="n"/>
       <c r="L413" s="6" t="n"/>
+      <c r="M413" s="6" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="6" t="n"/>
@@ -6549,6 +6980,7 @@
       <c r="J414" s="6" t="n"/>
       <c r="K414" s="6" t="n"/>
       <c r="L414" s="6" t="n"/>
+      <c r="M414" s="6" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="6" t="n"/>
@@ -6563,6 +6995,7 @@
       <c r="J415" s="6" t="n"/>
       <c r="K415" s="6" t="n"/>
       <c r="L415" s="6" t="n"/>
+      <c r="M415" s="6" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="6" t="n"/>
@@ -6577,6 +7010,7 @@
       <c r="J416" s="6" t="n"/>
       <c r="K416" s="6" t="n"/>
       <c r="L416" s="6" t="n"/>
+      <c r="M416" s="6" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="6" t="n"/>
@@ -6591,6 +7025,7 @@
       <c r="J417" s="6" t="n"/>
       <c r="K417" s="6" t="n"/>
       <c r="L417" s="6" t="n"/>
+      <c r="M417" s="6" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="6" t="n"/>
@@ -6605,6 +7040,7 @@
       <c r="J418" s="6" t="n"/>
       <c r="K418" s="6" t="n"/>
       <c r="L418" s="6" t="n"/>
+      <c r="M418" s="6" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="6" t="n"/>
@@ -6619,6 +7055,7 @@
       <c r="J419" s="6" t="n"/>
       <c r="K419" s="6" t="n"/>
       <c r="L419" s="6" t="n"/>
+      <c r="M419" s="6" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="6" t="n"/>
@@ -6633,6 +7070,7 @@
       <c r="J420" s="6" t="n"/>
       <c r="K420" s="6" t="n"/>
       <c r="L420" s="6" t="n"/>
+      <c r="M420" s="6" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="6" t="n"/>
@@ -6647,6 +7085,7 @@
       <c r="J421" s="6" t="n"/>
       <c r="K421" s="6" t="n"/>
       <c r="L421" s="6" t="n"/>
+      <c r="M421" s="6" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="6" t="n"/>
@@ -6661,6 +7100,7 @@
       <c r="J422" s="6" t="n"/>
       <c r="K422" s="6" t="n"/>
       <c r="L422" s="6" t="n"/>
+      <c r="M422" s="6" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="6" t="n"/>
@@ -6675,6 +7115,7 @@
       <c r="J423" s="6" t="n"/>
       <c r="K423" s="6" t="n"/>
       <c r="L423" s="6" t="n"/>
+      <c r="M423" s="6" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="6" t="n"/>
@@ -6689,6 +7130,7 @@
       <c r="J424" s="6" t="n"/>
       <c r="K424" s="6" t="n"/>
       <c r="L424" s="6" t="n"/>
+      <c r="M424" s="6" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="6" t="n"/>
@@ -6703,6 +7145,7 @@
       <c r="J425" s="6" t="n"/>
       <c r="K425" s="6" t="n"/>
       <c r="L425" s="6" t="n"/>
+      <c r="M425" s="6" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="6" t="n"/>
@@ -6717,6 +7160,7 @@
       <c r="J426" s="6" t="n"/>
       <c r="K426" s="6" t="n"/>
       <c r="L426" s="6" t="n"/>
+      <c r="M426" s="6" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="6" t="n"/>
@@ -6731,6 +7175,7 @@
       <c r="J427" s="6" t="n"/>
       <c r="K427" s="6" t="n"/>
       <c r="L427" s="6" t="n"/>
+      <c r="M427" s="6" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="6" t="n"/>
@@ -6745,6 +7190,7 @@
       <c r="J428" s="6" t="n"/>
       <c r="K428" s="6" t="n"/>
       <c r="L428" s="6" t="n"/>
+      <c r="M428" s="6" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="6" t="n"/>
@@ -6759,6 +7205,7 @@
       <c r="J429" s="6" t="n"/>
       <c r="K429" s="6" t="n"/>
       <c r="L429" s="6" t="n"/>
+      <c r="M429" s="6" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="6" t="n"/>
@@ -6773,6 +7220,7 @@
       <c r="J430" s="6" t="n"/>
       <c r="K430" s="6" t="n"/>
       <c r="L430" s="6" t="n"/>
+      <c r="M430" s="6" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="6" t="n"/>
@@ -6787,6 +7235,7 @@
       <c r="J431" s="6" t="n"/>
       <c r="K431" s="6" t="n"/>
       <c r="L431" s="6" t="n"/>
+      <c r="M431" s="6" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="6" t="n"/>
@@ -6801,6 +7250,7 @@
       <c r="J432" s="6" t="n"/>
       <c r="K432" s="6" t="n"/>
       <c r="L432" s="6" t="n"/>
+      <c r="M432" s="6" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="6" t="n"/>
@@ -6815,6 +7265,7 @@
       <c r="J433" s="6" t="n"/>
       <c r="K433" s="6" t="n"/>
       <c r="L433" s="6" t="n"/>
+      <c r="M433" s="6" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="6" t="n"/>
@@ -6829,6 +7280,7 @@
       <c r="J434" s="6" t="n"/>
       <c r="K434" s="6" t="n"/>
       <c r="L434" s="6" t="n"/>
+      <c r="M434" s="6" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="6" t="n"/>
@@ -6843,6 +7295,7 @@
       <c r="J435" s="6" t="n"/>
       <c r="K435" s="6" t="n"/>
       <c r="L435" s="6" t="n"/>
+      <c r="M435" s="6" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="6" t="n"/>
@@ -6857,6 +7310,7 @@
       <c r="J436" s="6" t="n"/>
       <c r="K436" s="6" t="n"/>
       <c r="L436" s="6" t="n"/>
+      <c r="M436" s="6" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="6" t="n"/>
@@ -6871,6 +7325,7 @@
       <c r="J437" s="6" t="n"/>
       <c r="K437" s="6" t="n"/>
       <c r="L437" s="6" t="n"/>
+      <c r="M437" s="6" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="6" t="n"/>
@@ -6885,6 +7340,7 @@
       <c r="J438" s="6" t="n"/>
       <c r="K438" s="6" t="n"/>
       <c r="L438" s="6" t="n"/>
+      <c r="M438" s="6" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="6" t="n"/>
@@ -6899,6 +7355,7 @@
       <c r="J439" s="6" t="n"/>
       <c r="K439" s="6" t="n"/>
       <c r="L439" s="6" t="n"/>
+      <c r="M439" s="6" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="6" t="n"/>
@@ -6913,6 +7370,7 @@
       <c r="J440" s="6" t="n"/>
       <c r="K440" s="6" t="n"/>
       <c r="L440" s="6" t="n"/>
+      <c r="M440" s="6" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="6" t="n"/>
@@ -6927,6 +7385,7 @@
       <c r="J441" s="6" t="n"/>
       <c r="K441" s="6" t="n"/>
       <c r="L441" s="6" t="n"/>
+      <c r="M441" s="6" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="6" t="n"/>
@@ -6941,6 +7400,7 @@
       <c r="J442" s="6" t="n"/>
       <c r="K442" s="6" t="n"/>
       <c r="L442" s="6" t="n"/>
+      <c r="M442" s="6" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="6" t="n"/>
@@ -6955,6 +7415,7 @@
       <c r="J443" s="6" t="n"/>
       <c r="K443" s="6" t="n"/>
       <c r="L443" s="6" t="n"/>
+      <c r="M443" s="6" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="6" t="n"/>
@@ -6969,6 +7430,7 @@
       <c r="J444" s="6" t="n"/>
       <c r="K444" s="6" t="n"/>
       <c r="L444" s="6" t="n"/>
+      <c r="M444" s="6" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="6" t="n"/>
@@ -6983,6 +7445,7 @@
       <c r="J445" s="6" t="n"/>
       <c r="K445" s="6" t="n"/>
       <c r="L445" s="6" t="n"/>
+      <c r="M445" s="6" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="6" t="n"/>
@@ -6997,6 +7460,7 @@
       <c r="J446" s="6" t="n"/>
       <c r="K446" s="6" t="n"/>
       <c r="L446" s="6" t="n"/>
+      <c r="M446" s="6" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="6" t="n"/>
@@ -7011,6 +7475,7 @@
       <c r="J447" s="6" t="n"/>
       <c r="K447" s="6" t="n"/>
       <c r="L447" s="6" t="n"/>
+      <c r="M447" s="6" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="6" t="n"/>
@@ -7025,6 +7490,7 @@
       <c r="J448" s="6" t="n"/>
       <c r="K448" s="6" t="n"/>
       <c r="L448" s="6" t="n"/>
+      <c r="M448" s="6" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="6" t="n"/>
@@ -7039,6 +7505,7 @@
       <c r="J449" s="6" t="n"/>
       <c r="K449" s="6" t="n"/>
       <c r="L449" s="6" t="n"/>
+      <c r="M449" s="6" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="6" t="n"/>
@@ -7053,6 +7520,7 @@
       <c r="J450" s="6" t="n"/>
       <c r="K450" s="6" t="n"/>
       <c r="L450" s="6" t="n"/>
+      <c r="M450" s="6" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="6" t="n"/>
@@ -7067,6 +7535,7 @@
       <c r="J451" s="6" t="n"/>
       <c r="K451" s="6" t="n"/>
       <c r="L451" s="6" t="n"/>
+      <c r="M451" s="6" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="6" t="n"/>
@@ -7081,6 +7550,7 @@
       <c r="J452" s="6" t="n"/>
       <c r="K452" s="6" t="n"/>
       <c r="L452" s="6" t="n"/>
+      <c r="M452" s="6" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="6" t="n"/>
@@ -7095,6 +7565,7 @@
       <c r="J453" s="6" t="n"/>
       <c r="K453" s="6" t="n"/>
       <c r="L453" s="6" t="n"/>
+      <c r="M453" s="6" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="6" t="n"/>
@@ -7109,6 +7580,7 @@
       <c r="J454" s="6" t="n"/>
       <c r="K454" s="6" t="n"/>
       <c r="L454" s="6" t="n"/>
+      <c r="M454" s="6" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="6" t="n"/>
@@ -7123,6 +7595,7 @@
       <c r="J455" s="6" t="n"/>
       <c r="K455" s="6" t="n"/>
       <c r="L455" s="6" t="n"/>
+      <c r="M455" s="6" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="6" t="n"/>
@@ -7137,6 +7610,7 @@
       <c r="J456" s="6" t="n"/>
       <c r="K456" s="6" t="n"/>
       <c r="L456" s="6" t="n"/>
+      <c r="M456" s="6" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="6" t="n"/>
@@ -7151,6 +7625,7 @@
       <c r="J457" s="6" t="n"/>
       <c r="K457" s="6" t="n"/>
       <c r="L457" s="6" t="n"/>
+      <c r="M457" s="6" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="6" t="n"/>
@@ -7165,6 +7640,7 @@
       <c r="J458" s="6" t="n"/>
       <c r="K458" s="6" t="n"/>
       <c r="L458" s="6" t="n"/>
+      <c r="M458" s="6" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="6" t="n"/>
@@ -7179,6 +7655,7 @@
       <c r="J459" s="6" t="n"/>
       <c r="K459" s="6" t="n"/>
       <c r="L459" s="6" t="n"/>
+      <c r="M459" s="6" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="6" t="n"/>
@@ -7193,6 +7670,7 @@
       <c r="J460" s="6" t="n"/>
       <c r="K460" s="6" t="n"/>
       <c r="L460" s="6" t="n"/>
+      <c r="M460" s="6" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="6" t="n"/>
@@ -7207,6 +7685,7 @@
       <c r="J461" s="6" t="n"/>
       <c r="K461" s="6" t="n"/>
       <c r="L461" s="6" t="n"/>
+      <c r="M461" s="6" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="6" t="n"/>
@@ -7221,6 +7700,7 @@
       <c r="J462" s="6" t="n"/>
       <c r="K462" s="6" t="n"/>
       <c r="L462" s="6" t="n"/>
+      <c r="M462" s="6" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="6" t="n"/>
@@ -7235,6 +7715,7 @@
       <c r="J463" s="6" t="n"/>
       <c r="K463" s="6" t="n"/>
       <c r="L463" s="6" t="n"/>
+      <c r="M463" s="6" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="6" t="n"/>
@@ -7249,6 +7730,7 @@
       <c r="J464" s="6" t="n"/>
       <c r="K464" s="6" t="n"/>
       <c r="L464" s="6" t="n"/>
+      <c r="M464" s="6" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="6" t="n"/>
@@ -7263,6 +7745,7 @@
       <c r="J465" s="6" t="n"/>
       <c r="K465" s="6" t="n"/>
       <c r="L465" s="6" t="n"/>
+      <c r="M465" s="6" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="6" t="n"/>
@@ -7277,6 +7760,7 @@
       <c r="J466" s="6" t="n"/>
       <c r="K466" s="6" t="n"/>
       <c r="L466" s="6" t="n"/>
+      <c r="M466" s="6" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="6" t="n"/>
@@ -7291,6 +7775,7 @@
       <c r="J467" s="6" t="n"/>
       <c r="K467" s="6" t="n"/>
       <c r="L467" s="6" t="n"/>
+      <c r="M467" s="6" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="6" t="n"/>
@@ -7305,6 +7790,7 @@
       <c r="J468" s="6" t="n"/>
       <c r="K468" s="6" t="n"/>
       <c r="L468" s="6" t="n"/>
+      <c r="M468" s="6" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="6" t="n"/>
@@ -7319,6 +7805,7 @@
       <c r="J469" s="6" t="n"/>
       <c r="K469" s="6" t="n"/>
       <c r="L469" s="6" t="n"/>
+      <c r="M469" s="6" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="6" t="n"/>
@@ -7333,6 +7820,7 @@
       <c r="J470" s="6" t="n"/>
       <c r="K470" s="6" t="n"/>
       <c r="L470" s="6" t="n"/>
+      <c r="M470" s="6" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="6" t="n"/>
@@ -7347,6 +7835,7 @@
       <c r="J471" s="6" t="n"/>
       <c r="K471" s="6" t="n"/>
       <c r="L471" s="6" t="n"/>
+      <c r="M471" s="6" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="6" t="n"/>
@@ -7361,6 +7850,7 @@
       <c r="J472" s="6" t="n"/>
       <c r="K472" s="6" t="n"/>
       <c r="L472" s="6" t="n"/>
+      <c r="M472" s="6" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="6" t="n"/>
@@ -7375,6 +7865,7 @@
       <c r="J473" s="6" t="n"/>
       <c r="K473" s="6" t="n"/>
       <c r="L473" s="6" t="n"/>
+      <c r="M473" s="6" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="6" t="n"/>
@@ -7389,6 +7880,7 @@
       <c r="J474" s="6" t="n"/>
       <c r="K474" s="6" t="n"/>
       <c r="L474" s="6" t="n"/>
+      <c r="M474" s="6" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="6" t="n"/>
@@ -7403,6 +7895,7 @@
       <c r="J475" s="6" t="n"/>
       <c r="K475" s="6" t="n"/>
       <c r="L475" s="6" t="n"/>
+      <c r="M475" s="6" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="6" t="n"/>
@@ -7417,6 +7910,7 @@
       <c r="J476" s="6" t="n"/>
       <c r="K476" s="6" t="n"/>
       <c r="L476" s="6" t="n"/>
+      <c r="M476" s="6" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="6" t="n"/>
@@ -7431,6 +7925,7 @@
       <c r="J477" s="6" t="n"/>
       <c r="K477" s="6" t="n"/>
       <c r="L477" s="6" t="n"/>
+      <c r="M477" s="6" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="6" t="n"/>
@@ -7445,6 +7940,7 @@
       <c r="J478" s="6" t="n"/>
       <c r="K478" s="6" t="n"/>
       <c r="L478" s="6" t="n"/>
+      <c r="M478" s="6" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="6" t="n"/>
@@ -7459,6 +7955,7 @@
       <c r="J479" s="6" t="n"/>
       <c r="K479" s="6" t="n"/>
       <c r="L479" s="6" t="n"/>
+      <c r="M479" s="6" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="6" t="n"/>
@@ -7473,6 +7970,7 @@
       <c r="J480" s="6" t="n"/>
       <c r="K480" s="6" t="n"/>
       <c r="L480" s="6" t="n"/>
+      <c r="M480" s="6" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="6" t="n"/>
@@ -7487,6 +7985,7 @@
       <c r="J481" s="6" t="n"/>
       <c r="K481" s="6" t="n"/>
       <c r="L481" s="6" t="n"/>
+      <c r="M481" s="6" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="6" t="n"/>
@@ -7501,6 +8000,7 @@
       <c r="J482" s="6" t="n"/>
       <c r="K482" s="6" t="n"/>
       <c r="L482" s="6" t="n"/>
+      <c r="M482" s="6" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="6" t="n"/>
@@ -7515,6 +8015,7 @@
       <c r="J483" s="6" t="n"/>
       <c r="K483" s="6" t="n"/>
       <c r="L483" s="6" t="n"/>
+      <c r="M483" s="6" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="6" t="n"/>
@@ -7529,6 +8030,7 @@
       <c r="J484" s="6" t="n"/>
       <c r="K484" s="6" t="n"/>
       <c r="L484" s="6" t="n"/>
+      <c r="M484" s="6" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="6" t="n"/>
@@ -7543,6 +8045,7 @@
       <c r="J485" s="6" t="n"/>
       <c r="K485" s="6" t="n"/>
       <c r="L485" s="6" t="n"/>
+      <c r="M485" s="6" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="6" t="n"/>
@@ -7557,6 +8060,7 @@
       <c r="J486" s="6" t="n"/>
       <c r="K486" s="6" t="n"/>
       <c r="L486" s="6" t="n"/>
+      <c r="M486" s="6" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="6" t="n"/>
@@ -7571,6 +8075,7 @@
       <c r="J487" s="6" t="n"/>
       <c r="K487" s="6" t="n"/>
       <c r="L487" s="6" t="n"/>
+      <c r="M487" s="6" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="6" t="n"/>
@@ -7585,6 +8090,7 @@
       <c r="J488" s="6" t="n"/>
       <c r="K488" s="6" t="n"/>
       <c r="L488" s="6" t="n"/>
+      <c r="M488" s="6" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="6" t="n"/>
@@ -7599,6 +8105,7 @@
       <c r="J489" s="6" t="n"/>
       <c r="K489" s="6" t="n"/>
       <c r="L489" s="6" t="n"/>
+      <c r="M489" s="6" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="6" t="n"/>
@@ -7613,6 +8120,7 @@
       <c r="J490" s="6" t="n"/>
       <c r="K490" s="6" t="n"/>
       <c r="L490" s="6" t="n"/>
+      <c r="M490" s="6" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="6" t="n"/>
@@ -7627,6 +8135,7 @@
       <c r="J491" s="6" t="n"/>
       <c r="K491" s="6" t="n"/>
       <c r="L491" s="6" t="n"/>
+      <c r="M491" s="6" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="6" t="n"/>
@@ -7641,6 +8150,7 @@
       <c r="J492" s="6" t="n"/>
       <c r="K492" s="6" t="n"/>
       <c r="L492" s="6" t="n"/>
+      <c r="M492" s="6" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="6" t="n"/>
@@ -7655,6 +8165,7 @@
       <c r="J493" s="6" t="n"/>
       <c r="K493" s="6" t="n"/>
       <c r="L493" s="6" t="n"/>
+      <c r="M493" s="6" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="6" t="n"/>
@@ -7669,6 +8180,7 @@
       <c r="J494" s="6" t="n"/>
       <c r="K494" s="6" t="n"/>
       <c r="L494" s="6" t="n"/>
+      <c r="M494" s="6" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="6" t="n"/>
@@ -7683,6 +8195,7 @@
       <c r="J495" s="6" t="n"/>
       <c r="K495" s="6" t="n"/>
       <c r="L495" s="6" t="n"/>
+      <c r="M495" s="6" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="6" t="n"/>
@@ -7697,6 +8210,7 @@
       <c r="J496" s="6" t="n"/>
       <c r="K496" s="6" t="n"/>
       <c r="L496" s="6" t="n"/>
+      <c r="M496" s="6" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="6" t="n"/>
@@ -7711,6 +8225,7 @@
       <c r="J497" s="6" t="n"/>
       <c r="K497" s="6" t="n"/>
       <c r="L497" s="6" t="n"/>
+      <c r="M497" s="6" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="6" t="n"/>
@@ -7725,6 +8240,7 @@
       <c r="J498" s="6" t="n"/>
       <c r="K498" s="6" t="n"/>
       <c r="L498" s="6" t="n"/>
+      <c r="M498" s="6" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="6" t="n"/>
@@ -7739,6 +8255,7 @@
       <c r="J499" s="6" t="n"/>
       <c r="K499" s="6" t="n"/>
       <c r="L499" s="6" t="n"/>
+      <c r="M499" s="6" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="6" t="n"/>
@@ -7753,6 +8270,7 @@
       <c r="J500" s="6" t="n"/>
       <c r="K500" s="6" t="n"/>
       <c r="L500" s="6" t="n"/>
+      <c r="M500" s="6" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="6" t="n"/>
@@ -7767,6 +8285,7 @@
       <c r="J501" s="6" t="n"/>
       <c r="K501" s="6" t="n"/>
       <c r="L501" s="6" t="n"/>
+      <c r="M501" s="6" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="6" t="n"/>
@@ -7781,6 +8300,7 @@
       <c r="J502" s="6" t="n"/>
       <c r="K502" s="6" t="n"/>
       <c r="L502" s="6" t="n"/>
+      <c r="M502" s="6" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="6" t="n"/>
@@ -7795,6 +8315,7 @@
       <c r="J503" s="6" t="n"/>
       <c r="K503" s="6" t="n"/>
       <c r="L503" s="6" t="n"/>
+      <c r="M503" s="6" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="6" t="n"/>
@@ -7809,6 +8330,7 @@
       <c r="J504" s="6" t="n"/>
       <c r="K504" s="6" t="n"/>
       <c r="L504" s="6" t="n"/>
+      <c r="M504" s="6" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="6" t="n"/>
@@ -7823,6 +8345,7 @@
       <c r="J505" s="6" t="n"/>
       <c r="K505" s="6" t="n"/>
       <c r="L505" s="6" t="n"/>
+      <c r="M505" s="6" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="6" t="n"/>
@@ -7837,6 +8360,7 @@
       <c r="J506" s="6" t="n"/>
       <c r="K506" s="6" t="n"/>
       <c r="L506" s="6" t="n"/>
+      <c r="M506" s="6" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="6" t="n"/>
@@ -7851,6 +8375,7 @@
       <c r="J507" s="6" t="n"/>
       <c r="K507" s="6" t="n"/>
       <c r="L507" s="6" t="n"/>
+      <c r="M507" s="6" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="6" t="n"/>
@@ -7865,6 +8390,7 @@
       <c r="J508" s="6" t="n"/>
       <c r="K508" s="6" t="n"/>
       <c r="L508" s="6" t="n"/>
+      <c r="M508" s="6" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="6" t="n"/>
@@ -7879,6 +8405,7 @@
       <c r="J509" s="6" t="n"/>
       <c r="K509" s="6" t="n"/>
       <c r="L509" s="6" t="n"/>
+      <c r="M509" s="6" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="6" t="n"/>
@@ -7893,6 +8420,7 @@
       <c r="J510" s="6" t="n"/>
       <c r="K510" s="6" t="n"/>
       <c r="L510" s="6" t="n"/>
+      <c r="M510" s="6" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="6" t="n"/>
@@ -7907,6 +8435,7 @@
       <c r="J511" s="6" t="n"/>
       <c r="K511" s="6" t="n"/>
       <c r="L511" s="6" t="n"/>
+      <c r="M511" s="6" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="6" t="n"/>
@@ -7921,6 +8450,7 @@
       <c r="J512" s="6" t="n"/>
       <c r="K512" s="6" t="n"/>
       <c r="L512" s="6" t="n"/>
+      <c r="M512" s="6" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="6" t="n"/>
@@ -7935,6 +8465,7 @@
       <c r="J513" s="6" t="n"/>
       <c r="K513" s="6" t="n"/>
       <c r="L513" s="6" t="n"/>
+      <c r="M513" s="6" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="6" t="n"/>
@@ -7949,6 +8480,7 @@
       <c r="J514" s="6" t="n"/>
       <c r="K514" s="6" t="n"/>
       <c r="L514" s="6" t="n"/>
+      <c r="M514" s="6" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="6" t="n"/>
@@ -7963,6 +8495,7 @@
       <c r="J515" s="6" t="n"/>
       <c r="K515" s="6" t="n"/>
       <c r="L515" s="6" t="n"/>
+      <c r="M515" s="6" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="6" t="n"/>
@@ -7977,6 +8510,7 @@
       <c r="J516" s="6" t="n"/>
       <c r="K516" s="6" t="n"/>
       <c r="L516" s="6" t="n"/>
+      <c r="M516" s="6" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="6" t="n"/>
@@ -7991,6 +8525,7 @@
       <c r="J517" s="6" t="n"/>
       <c r="K517" s="6" t="n"/>
       <c r="L517" s="6" t="n"/>
+      <c r="M517" s="6" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="6" t="n"/>
@@ -8005,6 +8540,7 @@
       <c r="J518" s="6" t="n"/>
       <c r="K518" s="6" t="n"/>
       <c r="L518" s="6" t="n"/>
+      <c r="M518" s="6" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="6" t="n"/>
@@ -8019,6 +8555,7 @@
       <c r="J519" s="6" t="n"/>
       <c r="K519" s="6" t="n"/>
       <c r="L519" s="6" t="n"/>
+      <c r="M519" s="6" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="6" t="n"/>
@@ -8033,6 +8570,7 @@
       <c r="J520" s="6" t="n"/>
       <c r="K520" s="6" t="n"/>
       <c r="L520" s="6" t="n"/>
+      <c r="M520" s="6" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="6" t="n"/>
@@ -8047,6 +8585,7 @@
       <c r="J521" s="6" t="n"/>
       <c r="K521" s="6" t="n"/>
       <c r="L521" s="6" t="n"/>
+      <c r="M521" s="6" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="6" t="n"/>
@@ -8061,6 +8600,7 @@
       <c r="J522" s="6" t="n"/>
       <c r="K522" s="6" t="n"/>
       <c r="L522" s="6" t="n"/>
+      <c r="M522" s="6" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="6" t="n"/>
@@ -8075,6 +8615,7 @@
       <c r="J523" s="6" t="n"/>
       <c r="K523" s="6" t="n"/>
       <c r="L523" s="6" t="n"/>
+      <c r="M523" s="6" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="6" t="n"/>
@@ -8089,6 +8630,7 @@
       <c r="J524" s="6" t="n"/>
       <c r="K524" s="6" t="n"/>
       <c r="L524" s="6" t="n"/>
+      <c r="M524" s="6" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="6" t="n"/>
@@ -8103,6 +8645,7 @@
       <c r="J525" s="6" t="n"/>
       <c r="K525" s="6" t="n"/>
       <c r="L525" s="6" t="n"/>
+      <c r="M525" s="6" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="6" t="n"/>
@@ -8117,6 +8660,7 @@
       <c r="J526" s="6" t="n"/>
       <c r="K526" s="6" t="n"/>
       <c r="L526" s="6" t="n"/>
+      <c r="M526" s="6" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="6" t="n"/>
@@ -8131,6 +8675,7 @@
       <c r="J527" s="6" t="n"/>
       <c r="K527" s="6" t="n"/>
       <c r="L527" s="6" t="n"/>
+      <c r="M527" s="6" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="6" t="n"/>
@@ -8145,6 +8690,7 @@
       <c r="J528" s="6" t="n"/>
       <c r="K528" s="6" t="n"/>
       <c r="L528" s="6" t="n"/>
+      <c r="M528" s="6" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="6" t="n"/>
@@ -8159,6 +8705,7 @@
       <c r="J529" s="6" t="n"/>
       <c r="K529" s="6" t="n"/>
       <c r="L529" s="6" t="n"/>
+      <c r="M529" s="6" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="6" t="n"/>
@@ -8173,6 +8720,7 @@
       <c r="J530" s="6" t="n"/>
       <c r="K530" s="6" t="n"/>
       <c r="L530" s="6" t="n"/>
+      <c r="M530" s="6" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="6" t="n"/>
@@ -8187,6 +8735,7 @@
       <c r="J531" s="6" t="n"/>
       <c r="K531" s="6" t="n"/>
       <c r="L531" s="6" t="n"/>
+      <c r="M531" s="6" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="6" t="n"/>
@@ -8201,6 +8750,7 @@
       <c r="J532" s="6" t="n"/>
       <c r="K532" s="6" t="n"/>
       <c r="L532" s="6" t="n"/>
+      <c r="M532" s="6" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="6" t="n"/>
@@ -8215,6 +8765,7 @@
       <c r="J533" s="6" t="n"/>
       <c r="K533" s="6" t="n"/>
       <c r="L533" s="6" t="n"/>
+      <c r="M533" s="6" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="6" t="n"/>
@@ -8229,6 +8780,7 @@
       <c r="J534" s="6" t="n"/>
       <c r="K534" s="6" t="n"/>
       <c r="L534" s="6" t="n"/>
+      <c r="M534" s="6" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="6" t="n"/>
@@ -8243,6 +8795,7 @@
       <c r="J535" s="6" t="n"/>
       <c r="K535" s="6" t="n"/>
       <c r="L535" s="6" t="n"/>
+      <c r="M535" s="6" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="6" t="n"/>
@@ -8257,6 +8810,7 @@
       <c r="J536" s="6" t="n"/>
       <c r="K536" s="6" t="n"/>
       <c r="L536" s="6" t="n"/>
+      <c r="M536" s="6" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="6" t="n"/>
@@ -8271,6 +8825,7 @@
       <c r="J537" s="6" t="n"/>
       <c r="K537" s="6" t="n"/>
       <c r="L537" s="6" t="n"/>
+      <c r="M537" s="6" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="6" t="n"/>
@@ -8285,6 +8840,7 @@
       <c r="J538" s="6" t="n"/>
       <c r="K538" s="6" t="n"/>
       <c r="L538" s="6" t="n"/>
+      <c r="M538" s="6" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="6" t="n"/>
@@ -8299,6 +8855,7 @@
       <c r="J539" s="6" t="n"/>
       <c r="K539" s="6" t="n"/>
       <c r="L539" s="6" t="n"/>
+      <c r="M539" s="6" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="6" t="n"/>
@@ -8313,6 +8870,7 @@
       <c r="J540" s="6" t="n"/>
       <c r="K540" s="6" t="n"/>
       <c r="L540" s="6" t="n"/>
+      <c r="M540" s="6" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="6" t="n"/>
@@ -8327,6 +8885,7 @@
       <c r="J541" s="6" t="n"/>
       <c r="K541" s="6" t="n"/>
       <c r="L541" s="6" t="n"/>
+      <c r="M541" s="6" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="6" t="n"/>
@@ -8341,6 +8900,7 @@
       <c r="J542" s="6" t="n"/>
       <c r="K542" s="6" t="n"/>
       <c r="L542" s="6" t="n"/>
+      <c r="M542" s="6" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="6" t="n"/>
@@ -8355,6 +8915,7 @@
       <c r="J543" s="6" t="n"/>
       <c r="K543" s="6" t="n"/>
       <c r="L543" s="6" t="n"/>
+      <c r="M543" s="6" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="6" t="n"/>
@@ -8369,6 +8930,7 @@
       <c r="J544" s="6" t="n"/>
       <c r="K544" s="6" t="n"/>
       <c r="L544" s="6" t="n"/>
+      <c r="M544" s="6" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="6" t="n"/>
@@ -8383,6 +8945,7 @@
       <c r="J545" s="6" t="n"/>
       <c r="K545" s="6" t="n"/>
       <c r="L545" s="6" t="n"/>
+      <c r="M545" s="6" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="6" t="n"/>
@@ -8397,6 +8960,7 @@
       <c r="J546" s="6" t="n"/>
       <c r="K546" s="6" t="n"/>
       <c r="L546" s="6" t="n"/>
+      <c r="M546" s="6" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="6" t="n"/>
@@ -8411,6 +8975,7 @@
       <c r="J547" s="6" t="n"/>
       <c r="K547" s="6" t="n"/>
       <c r="L547" s="6" t="n"/>
+      <c r="M547" s="6" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="6" t="n"/>
@@ -8425,6 +8990,7 @@
       <c r="J548" s="6" t="n"/>
       <c r="K548" s="6" t="n"/>
       <c r="L548" s="6" t="n"/>
+      <c r="M548" s="6" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="6" t="n"/>
@@ -8439,6 +9005,7 @@
       <c r="J549" s="6" t="n"/>
       <c r="K549" s="6" t="n"/>
       <c r="L549" s="6" t="n"/>
+      <c r="M549" s="6" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="6" t="n"/>
@@ -8453,6 +9020,7 @@
       <c r="J550" s="6" t="n"/>
       <c r="K550" s="6" t="n"/>
       <c r="L550" s="6" t="n"/>
+      <c r="M550" s="6" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="6" t="n"/>
@@ -8467,6 +9035,7 @@
       <c r="J551" s="6" t="n"/>
       <c r="K551" s="6" t="n"/>
       <c r="L551" s="6" t="n"/>
+      <c r="M551" s="6" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="6" t="n"/>
@@ -8481,6 +9050,7 @@
       <c r="J552" s="6" t="n"/>
       <c r="K552" s="6" t="n"/>
       <c r="L552" s="6" t="n"/>
+      <c r="M552" s="6" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="6" t="n"/>
@@ -8495,6 +9065,7 @@
       <c r="J553" s="6" t="n"/>
       <c r="K553" s="6" t="n"/>
       <c r="L553" s="6" t="n"/>
+      <c r="M553" s="6" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="6" t="n"/>
@@ -8509,6 +9080,7 @@
       <c r="J554" s="6" t="n"/>
       <c r="K554" s="6" t="n"/>
       <c r="L554" s="6" t="n"/>
+      <c r="M554" s="6" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="6" t="n"/>
@@ -8523,6 +9095,7 @@
       <c r="J555" s="6" t="n"/>
       <c r="K555" s="6" t="n"/>
       <c r="L555" s="6" t="n"/>
+      <c r="M555" s="6" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="6" t="n"/>
@@ -8537,6 +9110,7 @@
       <c r="J556" s="6" t="n"/>
       <c r="K556" s="6" t="n"/>
       <c r="L556" s="6" t="n"/>
+      <c r="M556" s="6" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="6" t="n"/>
@@ -8551,6 +9125,7 @@
       <c r="J557" s="6" t="n"/>
       <c r="K557" s="6" t="n"/>
       <c r="L557" s="6" t="n"/>
+      <c r="M557" s="6" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="6" t="n"/>
@@ -8565,6 +9140,7 @@
       <c r="J558" s="6" t="n"/>
       <c r="K558" s="6" t="n"/>
       <c r="L558" s="6" t="n"/>
+      <c r="M558" s="6" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="6" t="n"/>
@@ -8579,6 +9155,7 @@
       <c r="J559" s="6" t="n"/>
       <c r="K559" s="6" t="n"/>
       <c r="L559" s="6" t="n"/>
+      <c r="M559" s="6" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="6" t="n"/>
@@ -8593,6 +9170,7 @@
       <c r="J560" s="6" t="n"/>
       <c r="K560" s="6" t="n"/>
       <c r="L560" s="6" t="n"/>
+      <c r="M560" s="6" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="6" t="n"/>
@@ -8607,6 +9185,7 @@
       <c r="J561" s="6" t="n"/>
       <c r="K561" s="6" t="n"/>
       <c r="L561" s="6" t="n"/>
+      <c r="M561" s="6" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="6" t="n"/>
@@ -8621,6 +9200,7 @@
       <c r="J562" s="6" t="n"/>
       <c r="K562" s="6" t="n"/>
       <c r="L562" s="6" t="n"/>
+      <c r="M562" s="6" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="6" t="n"/>
@@ -8635,6 +9215,7 @@
       <c r="J563" s="6" t="n"/>
       <c r="K563" s="6" t="n"/>
       <c r="L563" s="6" t="n"/>
+      <c r="M563" s="6" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="6" t="n"/>
@@ -8649,6 +9230,7 @@
       <c r="J564" s="6" t="n"/>
       <c r="K564" s="6" t="n"/>
       <c r="L564" s="6" t="n"/>
+      <c r="M564" s="6" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="6" t="n"/>
@@ -8663,6 +9245,7 @@
       <c r="J565" s="6" t="n"/>
       <c r="K565" s="6" t="n"/>
       <c r="L565" s="6" t="n"/>
+      <c r="M565" s="6" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="6" t="n"/>
@@ -8677,6 +9260,7 @@
       <c r="J566" s="6" t="n"/>
       <c r="K566" s="6" t="n"/>
       <c r="L566" s="6" t="n"/>
+      <c r="M566" s="6" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="6" t="n"/>
@@ -8691,6 +9275,7 @@
       <c r="J567" s="6" t="n"/>
       <c r="K567" s="6" t="n"/>
       <c r="L567" s="6" t="n"/>
+      <c r="M567" s="6" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="6" t="n"/>
@@ -8705,6 +9290,7 @@
       <c r="J568" s="6" t="n"/>
       <c r="K568" s="6" t="n"/>
       <c r="L568" s="6" t="n"/>
+      <c r="M568" s="6" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="6" t="n"/>
@@ -8719,6 +9305,7 @@
       <c r="J569" s="6" t="n"/>
       <c r="K569" s="6" t="n"/>
       <c r="L569" s="6" t="n"/>
+      <c r="M569" s="6" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="6" t="n"/>
@@ -8733,6 +9320,7 @@
       <c r="J570" s="6" t="n"/>
       <c r="K570" s="6" t="n"/>
       <c r="L570" s="6" t="n"/>
+      <c r="M570" s="6" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="6" t="n"/>
@@ -8747,6 +9335,7 @@
       <c r="J571" s="6" t="n"/>
       <c r="K571" s="6" t="n"/>
       <c r="L571" s="6" t="n"/>
+      <c r="M571" s="6" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="6" t="n"/>
@@ -8761,6 +9350,7 @@
       <c r="J572" s="6" t="n"/>
       <c r="K572" s="6" t="n"/>
       <c r="L572" s="6" t="n"/>
+      <c r="M572" s="6" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="6" t="n"/>
@@ -8775,6 +9365,7 @@
       <c r="J573" s="6" t="n"/>
       <c r="K573" s="6" t="n"/>
       <c r="L573" s="6" t="n"/>
+      <c r="M573" s="6" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="6" t="n"/>
@@ -8789,6 +9380,7 @@
       <c r="J574" s="6" t="n"/>
       <c r="K574" s="6" t="n"/>
       <c r="L574" s="6" t="n"/>
+      <c r="M574" s="6" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="6" t="n"/>
@@ -8803,6 +9395,7 @@
       <c r="J575" s="6" t="n"/>
       <c r="K575" s="6" t="n"/>
       <c r="L575" s="6" t="n"/>
+      <c r="M575" s="6" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="6" t="n"/>
@@ -8817,6 +9410,7 @@
       <c r="J576" s="6" t="n"/>
       <c r="K576" s="6" t="n"/>
       <c r="L576" s="6" t="n"/>
+      <c r="M576" s="6" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="6" t="n"/>
@@ -8831,6 +9425,7 @@
       <c r="J577" s="6" t="n"/>
       <c r="K577" s="6" t="n"/>
       <c r="L577" s="6" t="n"/>
+      <c r="M577" s="6" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="6" t="n"/>
@@ -8845,6 +9440,7 @@
       <c r="J578" s="6" t="n"/>
       <c r="K578" s="6" t="n"/>
       <c r="L578" s="6" t="n"/>
+      <c r="M578" s="6" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="6" t="n"/>
@@ -8859,6 +9455,7 @@
       <c r="J579" s="6" t="n"/>
       <c r="K579" s="6" t="n"/>
       <c r="L579" s="6" t="n"/>
+      <c r="M579" s="6" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="6" t="n"/>
@@ -8873,6 +9470,7 @@
       <c r="J580" s="6" t="n"/>
       <c r="K580" s="6" t="n"/>
       <c r="L580" s="6" t="n"/>
+      <c r="M580" s="6" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="6" t="n"/>
@@ -8887,6 +9485,7 @@
       <c r="J581" s="6" t="n"/>
       <c r="K581" s="6" t="n"/>
       <c r="L581" s="6" t="n"/>
+      <c r="M581" s="6" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="6" t="n"/>
@@ -8901,6 +9500,7 @@
       <c r="J582" s="6" t="n"/>
       <c r="K582" s="6" t="n"/>
       <c r="L582" s="6" t="n"/>
+      <c r="M582" s="6" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="6" t="n"/>
@@ -8915,6 +9515,7 @@
       <c r="J583" s="6" t="n"/>
       <c r="K583" s="6" t="n"/>
       <c r="L583" s="6" t="n"/>
+      <c r="M583" s="6" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="6" t="n"/>
@@ -8929,6 +9530,7 @@
       <c r="J584" s="6" t="n"/>
       <c r="K584" s="6" t="n"/>
       <c r="L584" s="6" t="n"/>
+      <c r="M584" s="6" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="6" t="n"/>
@@ -8943,6 +9545,7 @@
       <c r="J585" s="6" t="n"/>
       <c r="K585" s="6" t="n"/>
       <c r="L585" s="6" t="n"/>
+      <c r="M585" s="6" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="6" t="n"/>
@@ -8957,6 +9560,7 @@
       <c r="J586" s="6" t="n"/>
       <c r="K586" s="6" t="n"/>
       <c r="L586" s="6" t="n"/>
+      <c r="M586" s="6" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="n"/>
@@ -8971,6 +9575,7 @@
       <c r="J587" s="6" t="n"/>
       <c r="K587" s="6" t="n"/>
       <c r="L587" s="6" t="n"/>
+      <c r="M587" s="6" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="6" t="n"/>
@@ -8985,6 +9590,7 @@
       <c r="J588" s="6" t="n"/>
       <c r="K588" s="6" t="n"/>
       <c r="L588" s="6" t="n"/>
+      <c r="M588" s="6" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="n"/>
@@ -8999,6 +9605,7 @@
       <c r="J589" s="6" t="n"/>
       <c r="K589" s="6" t="n"/>
       <c r="L589" s="6" t="n"/>
+      <c r="M589" s="6" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="6" t="n"/>
@@ -9013,6 +9620,7 @@
       <c r="J590" s="6" t="n"/>
       <c r="K590" s="6" t="n"/>
       <c r="L590" s="6" t="n"/>
+      <c r="M590" s="6" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="6" t="n"/>
@@ -9027,6 +9635,7 @@
       <c r="J591" s="6" t="n"/>
       <c r="K591" s="6" t="n"/>
       <c r="L591" s="6" t="n"/>
+      <c r="M591" s="6" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="6" t="n"/>
@@ -9041,6 +9650,7 @@
       <c r="J592" s="6" t="n"/>
       <c r="K592" s="6" t="n"/>
       <c r="L592" s="6" t="n"/>
+      <c r="M592" s="6" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="6" t="n"/>
@@ -9055,6 +9665,7 @@
       <c r="J593" s="6" t="n"/>
       <c r="K593" s="6" t="n"/>
       <c r="L593" s="6" t="n"/>
+      <c r="M593" s="6" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="6" t="n"/>
@@ -9069,6 +9680,7 @@
       <c r="J594" s="6" t="n"/>
       <c r="K594" s="6" t="n"/>
       <c r="L594" s="6" t="n"/>
+      <c r="M594" s="6" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="n"/>
@@ -9083,6 +9695,7 @@
       <c r="J595" s="6" t="n"/>
       <c r="K595" s="6" t="n"/>
       <c r="L595" s="6" t="n"/>
+      <c r="M595" s="6" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="6" t="n"/>
@@ -9097,6 +9710,7 @@
       <c r="J596" s="6" t="n"/>
       <c r="K596" s="6" t="n"/>
       <c r="L596" s="6" t="n"/>
+      <c r="M596" s="6" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="n"/>
@@ -9111,6 +9725,7 @@
       <c r="J597" s="6" t="n"/>
       <c r="K597" s="6" t="n"/>
       <c r="L597" s="6" t="n"/>
+      <c r="M597" s="6" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="6" t="n"/>
@@ -9125,6 +9740,7 @@
       <c r="J598" s="6" t="n"/>
       <c r="K598" s="6" t="n"/>
       <c r="L598" s="6" t="n"/>
+      <c r="M598" s="6" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="n"/>
@@ -9139,6 +9755,7 @@
       <c r="J599" s="6" t="n"/>
       <c r="K599" s="6" t="n"/>
       <c r="L599" s="6" t="n"/>
+      <c r="M599" s="6" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="6" t="n"/>
@@ -9153,6 +9770,7 @@
       <c r="J600" s="6" t="n"/>
       <c r="K600" s="6" t="n"/>
       <c r="L600" s="6" t="n"/>
+      <c r="M600" s="6" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="6" t="n"/>
@@ -9167,6 +9785,7 @@
       <c r="J601" s="6" t="n"/>
       <c r="K601" s="6" t="n"/>
       <c r="L601" s="6" t="n"/>
+      <c r="M601" s="6" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="6" t="n"/>
@@ -9181,6 +9800,7 @@
       <c r="J602" s="6" t="n"/>
       <c r="K602" s="6" t="n"/>
       <c r="L602" s="6" t="n"/>
+      <c r="M602" s="6" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="n"/>
@@ -9195,6 +9815,7 @@
       <c r="J603" s="6" t="n"/>
       <c r="K603" s="6" t="n"/>
       <c r="L603" s="6" t="n"/>
+      <c r="M603" s="6" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="6" t="n"/>
@@ -9209,6 +9830,7 @@
       <c r="J604" s="6" t="n"/>
       <c r="K604" s="6" t="n"/>
       <c r="L604" s="6" t="n"/>
+      <c r="M604" s="6" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="n"/>
@@ -9223,6 +9845,7 @@
       <c r="J605" s="6" t="n"/>
       <c r="K605" s="6" t="n"/>
       <c r="L605" s="6" t="n"/>
+      <c r="M605" s="6" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="6" t="n"/>
@@ -9237,6 +9860,7 @@
       <c r="J606" s="6" t="n"/>
       <c r="K606" s="6" t="n"/>
       <c r="L606" s="6" t="n"/>
+      <c r="M606" s="6" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="6" t="n"/>
@@ -9251,6 +9875,7 @@
       <c r="J607" s="6" t="n"/>
       <c r="K607" s="6" t="n"/>
       <c r="L607" s="6" t="n"/>
+      <c r="M607" s="6" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="6" t="n"/>
@@ -9265,6 +9890,7 @@
       <c r="J608" s="6" t="n"/>
       <c r="K608" s="6" t="n"/>
       <c r="L608" s="6" t="n"/>
+      <c r="M608" s="6" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="6" t="n"/>
@@ -9279,6 +9905,7 @@
       <c r="J609" s="6" t="n"/>
       <c r="K609" s="6" t="n"/>
       <c r="L609" s="6" t="n"/>
+      <c r="M609" s="6" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="6" t="n"/>
@@ -9293,6 +9920,7 @@
       <c r="J610" s="6" t="n"/>
       <c r="K610" s="6" t="n"/>
       <c r="L610" s="6" t="n"/>
+      <c r="M610" s="6" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="6" t="n"/>
@@ -9307,6 +9935,7 @@
       <c r="J611" s="6" t="n"/>
       <c r="K611" s="6" t="n"/>
       <c r="L611" s="6" t="n"/>
+      <c r="M611" s="6" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="6" t="n"/>
@@ -9321,6 +9950,7 @@
       <c r="J612" s="6" t="n"/>
       <c r="K612" s="6" t="n"/>
       <c r="L612" s="6" t="n"/>
+      <c r="M612" s="6" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="6" t="n"/>
@@ -9335,6 +9965,7 @@
       <c r="J613" s="6" t="n"/>
       <c r="K613" s="6" t="n"/>
       <c r="L613" s="6" t="n"/>
+      <c r="M613" s="6" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="6" t="n"/>
@@ -9349,6 +9980,7 @@
       <c r="J614" s="6" t="n"/>
       <c r="K614" s="6" t="n"/>
       <c r="L614" s="6" t="n"/>
+      <c r="M614" s="6" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="6" t="n"/>
@@ -9363,6 +9995,7 @@
       <c r="J615" s="6" t="n"/>
       <c r="K615" s="6" t="n"/>
       <c r="L615" s="6" t="n"/>
+      <c r="M615" s="6" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="6" t="n"/>
@@ -9377,6 +10010,7 @@
       <c r="J616" s="6" t="n"/>
       <c r="K616" s="6" t="n"/>
       <c r="L616" s="6" t="n"/>
+      <c r="M616" s="6" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="6" t="n"/>
@@ -9391,6 +10025,7 @@
       <c r="J617" s="6" t="n"/>
       <c r="K617" s="6" t="n"/>
       <c r="L617" s="6" t="n"/>
+      <c r="M617" s="6" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="6" t="n"/>
@@ -9405,6 +10040,7 @@
       <c r="J618" s="6" t="n"/>
       <c r="K618" s="6" t="n"/>
       <c r="L618" s="6" t="n"/>
+      <c r="M618" s="6" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="6" t="n"/>
@@ -9419,6 +10055,7 @@
       <c r="J619" s="6" t="n"/>
       <c r="K619" s="6" t="n"/>
       <c r="L619" s="6" t="n"/>
+      <c r="M619" s="6" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="6" t="n"/>
@@ -9433,6 +10070,7 @@
       <c r="J620" s="6" t="n"/>
       <c r="K620" s="6" t="n"/>
       <c r="L620" s="6" t="n"/>
+      <c r="M620" s="6" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="6" t="n"/>
@@ -9447,6 +10085,7 @@
       <c r="J621" s="6" t="n"/>
       <c r="K621" s="6" t="n"/>
       <c r="L621" s="6" t="n"/>
+      <c r="M621" s="6" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="6" t="n"/>
@@ -9461,6 +10100,7 @@
       <c r="J622" s="6" t="n"/>
       <c r="K622" s="6" t="n"/>
       <c r="L622" s="6" t="n"/>
+      <c r="M622" s="6" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="6" t="n"/>
@@ -9475,6 +10115,7 @@
       <c r="J623" s="6" t="n"/>
       <c r="K623" s="6" t="n"/>
       <c r="L623" s="6" t="n"/>
+      <c r="M623" s="6" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="6" t="n"/>
@@ -9489,6 +10130,7 @@
       <c r="J624" s="6" t="n"/>
       <c r="K624" s="6" t="n"/>
       <c r="L624" s="6" t="n"/>
+      <c r="M624" s="6" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="6" t="n"/>
@@ -9503,6 +10145,7 @@
       <c r="J625" s="6" t="n"/>
       <c r="K625" s="6" t="n"/>
       <c r="L625" s="6" t="n"/>
+      <c r="M625" s="6" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="6" t="n"/>
@@ -9517,6 +10160,7 @@
       <c r="J626" s="6" t="n"/>
       <c r="K626" s="6" t="n"/>
       <c r="L626" s="6" t="n"/>
+      <c r="M626" s="6" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="6" t="n"/>
@@ -9531,6 +10175,7 @@
       <c r="J627" s="6" t="n"/>
       <c r="K627" s="6" t="n"/>
       <c r="L627" s="6" t="n"/>
+      <c r="M627" s="6" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="6" t="n"/>
@@ -9545,6 +10190,7 @@
       <c r="J628" s="6" t="n"/>
       <c r="K628" s="6" t="n"/>
       <c r="L628" s="6" t="n"/>
+      <c r="M628" s="6" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="6" t="n"/>
@@ -9559,6 +10205,7 @@
       <c r="J629" s="6" t="n"/>
       <c r="K629" s="6" t="n"/>
       <c r="L629" s="6" t="n"/>
+      <c r="M629" s="6" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="6" t="n"/>
@@ -9573,6 +10220,7 @@
       <c r="J630" s="6" t="n"/>
       <c r="K630" s="6" t="n"/>
       <c r="L630" s="6" t="n"/>
+      <c r="M630" s="6" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="6" t="n"/>
@@ -9587,6 +10235,7 @@
       <c r="J631" s="6" t="n"/>
       <c r="K631" s="6" t="n"/>
       <c r="L631" s="6" t="n"/>
+      <c r="M631" s="6" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="6" t="n"/>
@@ -9601,6 +10250,7 @@
       <c r="J632" s="6" t="n"/>
       <c r="K632" s="6" t="n"/>
       <c r="L632" s="6" t="n"/>
+      <c r="M632" s="6" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="6" t="n"/>
@@ -9615,6 +10265,7 @@
       <c r="J633" s="6" t="n"/>
       <c r="K633" s="6" t="n"/>
       <c r="L633" s="6" t="n"/>
+      <c r="M633" s="6" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="6" t="n"/>
@@ -9629,6 +10280,7 @@
       <c r="J634" s="6" t="n"/>
       <c r="K634" s="6" t="n"/>
       <c r="L634" s="6" t="n"/>
+      <c r="M634" s="6" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="6" t="n"/>
@@ -9643,6 +10295,7 @@
       <c r="J635" s="6" t="n"/>
       <c r="K635" s="6" t="n"/>
       <c r="L635" s="6" t="n"/>
+      <c r="M635" s="6" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="6" t="n"/>
@@ -9657,6 +10310,7 @@
       <c r="J636" s="6" t="n"/>
       <c r="K636" s="6" t="n"/>
       <c r="L636" s="6" t="n"/>
+      <c r="M636" s="6" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="6" t="n"/>
@@ -9671,6 +10325,7 @@
       <c r="J637" s="6" t="n"/>
       <c r="K637" s="6" t="n"/>
       <c r="L637" s="6" t="n"/>
+      <c r="M637" s="6" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="6" t="n"/>
@@ -9685,6 +10340,7 @@
       <c r="J638" s="6" t="n"/>
       <c r="K638" s="6" t="n"/>
       <c r="L638" s="6" t="n"/>
+      <c r="M638" s="6" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="6" t="n"/>
@@ -9699,6 +10355,7 @@
       <c r="J639" s="6" t="n"/>
       <c r="K639" s="6" t="n"/>
       <c r="L639" s="6" t="n"/>
+      <c r="M639" s="6" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="6" t="n"/>
@@ -9713,6 +10370,7 @@
       <c r="J640" s="6" t="n"/>
       <c r="K640" s="6" t="n"/>
       <c r="L640" s="6" t="n"/>
+      <c r="M640" s="6" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="6" t="n"/>
@@ -9727,6 +10385,7 @@
       <c r="J641" s="6" t="n"/>
       <c r="K641" s="6" t="n"/>
       <c r="L641" s="6" t="n"/>
+      <c r="M641" s="6" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="6" t="n"/>
@@ -9741,6 +10400,7 @@
       <c r="J642" s="6" t="n"/>
       <c r="K642" s="6" t="n"/>
       <c r="L642" s="6" t="n"/>
+      <c r="M642" s="6" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="6" t="n"/>
@@ -9755,6 +10415,7 @@
       <c r="J643" s="6" t="n"/>
       <c r="K643" s="6" t="n"/>
       <c r="L643" s="6" t="n"/>
+      <c r="M643" s="6" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="6" t="n"/>
@@ -9769,6 +10430,7 @@
       <c r="J644" s="6" t="n"/>
       <c r="K644" s="6" t="n"/>
       <c r="L644" s="6" t="n"/>
+      <c r="M644" s="6" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="6" t="n"/>
@@ -9783,6 +10445,7 @@
       <c r="J645" s="6" t="n"/>
       <c r="K645" s="6" t="n"/>
       <c r="L645" s="6" t="n"/>
+      <c r="M645" s="6" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="6" t="n"/>
@@ -9797,6 +10460,7 @@
       <c r="J646" s="6" t="n"/>
       <c r="K646" s="6" t="n"/>
       <c r="L646" s="6" t="n"/>
+      <c r="M646" s="6" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="6" t="n"/>
@@ -9811,6 +10475,7 @@
       <c r="J647" s="6" t="n"/>
       <c r="K647" s="6" t="n"/>
       <c r="L647" s="6" t="n"/>
+      <c r="M647" s="6" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="6" t="n"/>
@@ -9825,6 +10490,7 @@
       <c r="J648" s="6" t="n"/>
       <c r="K648" s="6" t="n"/>
       <c r="L648" s="6" t="n"/>
+      <c r="M648" s="6" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="6" t="n"/>
@@ -9839,6 +10505,7 @@
       <c r="J649" s="6" t="n"/>
       <c r="K649" s="6" t="n"/>
       <c r="L649" s="6" t="n"/>
+      <c r="M649" s="6" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="6" t="n"/>
@@ -9853,6 +10520,7 @@
       <c r="J650" s="6" t="n"/>
       <c r="K650" s="6" t="n"/>
       <c r="L650" s="6" t="n"/>
+      <c r="M650" s="6" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="6" t="n"/>
@@ -9867,6 +10535,7 @@
       <c r="J651" s="6" t="n"/>
       <c r="K651" s="6" t="n"/>
       <c r="L651" s="6" t="n"/>
+      <c r="M651" s="6" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="6" t="n"/>
@@ -9881,6 +10550,7 @@
       <c r="J652" s="6" t="n"/>
       <c r="K652" s="6" t="n"/>
       <c r="L652" s="6" t="n"/>
+      <c r="M652" s="6" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="6" t="n"/>
@@ -9895,6 +10565,7 @@
       <c r="J653" s="6" t="n"/>
       <c r="K653" s="6" t="n"/>
       <c r="L653" s="6" t="n"/>
+      <c r="M653" s="6" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="6" t="n"/>
@@ -9909,6 +10580,7 @@
       <c r="J654" s="6" t="n"/>
       <c r="K654" s="6" t="n"/>
       <c r="L654" s="6" t="n"/>
+      <c r="M654" s="6" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="6" t="n"/>
@@ -9923,6 +10595,7 @@
       <c r="J655" s="6" t="n"/>
       <c r="K655" s="6" t="n"/>
       <c r="L655" s="6" t="n"/>
+      <c r="M655" s="6" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="6" t="n"/>
@@ -9937,6 +10610,7 @@
       <c r="J656" s="6" t="n"/>
       <c r="K656" s="6" t="n"/>
       <c r="L656" s="6" t="n"/>
+      <c r="M656" s="6" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="6" t="n"/>
@@ -9951,6 +10625,7 @@
       <c r="J657" s="6" t="n"/>
       <c r="K657" s="6" t="n"/>
       <c r="L657" s="6" t="n"/>
+      <c r="M657" s="6" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="6" t="n"/>
@@ -9965,6 +10640,7 @@
       <c r="J658" s="6" t="n"/>
       <c r="K658" s="6" t="n"/>
       <c r="L658" s="6" t="n"/>
+      <c r="M658" s="6" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="6" t="n"/>
@@ -9979,6 +10655,7 @@
       <c r="J659" s="6" t="n"/>
       <c r="K659" s="6" t="n"/>
       <c r="L659" s="6" t="n"/>
+      <c r="M659" s="6" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="6" t="n"/>
@@ -9993,6 +10670,7 @@
       <c r="J660" s="6" t="n"/>
       <c r="K660" s="6" t="n"/>
       <c r="L660" s="6" t="n"/>
+      <c r="M660" s="6" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="6" t="n"/>
@@ -10007,6 +10685,7 @@
       <c r="J661" s="6" t="n"/>
       <c r="K661" s="6" t="n"/>
       <c r="L661" s="6" t="n"/>
+      <c r="M661" s="6" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="6" t="n"/>
@@ -10021,6 +10700,7 @@
       <c r="J662" s="6" t="n"/>
       <c r="K662" s="6" t="n"/>
       <c r="L662" s="6" t="n"/>
+      <c r="M662" s="6" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="6" t="n"/>
@@ -10035,6 +10715,7 @@
       <c r="J663" s="6" t="n"/>
       <c r="K663" s="6" t="n"/>
       <c r="L663" s="6" t="n"/>
+      <c r="M663" s="6" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="6" t="n"/>
@@ -10049,6 +10730,7 @@
       <c r="J664" s="6" t="n"/>
       <c r="K664" s="6" t="n"/>
       <c r="L664" s="6" t="n"/>
+      <c r="M664" s="6" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="6" t="n"/>
@@ -10063,6 +10745,7 @@
       <c r="J665" s="6" t="n"/>
       <c r="K665" s="6" t="n"/>
       <c r="L665" s="6" t="n"/>
+      <c r="M665" s="6" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="6" t="n"/>
@@ -10077,6 +10760,7 @@
       <c r="J666" s="6" t="n"/>
       <c r="K666" s="6" t="n"/>
       <c r="L666" s="6" t="n"/>
+      <c r="M666" s="6" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="6" t="n"/>
@@ -10091,6 +10775,7 @@
       <c r="J667" s="6" t="n"/>
       <c r="K667" s="6" t="n"/>
       <c r="L667" s="6" t="n"/>
+      <c r="M667" s="6" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="6" t="n"/>
@@ -10105,6 +10790,7 @@
       <c r="J668" s="6" t="n"/>
       <c r="K668" s="6" t="n"/>
       <c r="L668" s="6" t="n"/>
+      <c r="M668" s="6" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="6" t="n"/>
@@ -10119,6 +10805,7 @@
       <c r="J669" s="6" t="n"/>
       <c r="K669" s="6" t="n"/>
       <c r="L669" s="6" t="n"/>
+      <c r="M669" s="6" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="6" t="n"/>
@@ -10133,6 +10820,7 @@
       <c r="J670" s="6" t="n"/>
       <c r="K670" s="6" t="n"/>
       <c r="L670" s="6" t="n"/>
+      <c r="M670" s="6" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="6" t="n"/>
@@ -10147,6 +10835,7 @@
       <c r="J671" s="6" t="n"/>
       <c r="K671" s="6" t="n"/>
       <c r="L671" s="6" t="n"/>
+      <c r="M671" s="6" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="6" t="n"/>
@@ -10161,6 +10850,7 @@
       <c r="J672" s="6" t="n"/>
       <c r="K672" s="6" t="n"/>
       <c r="L672" s="6" t="n"/>
+      <c r="M672" s="6" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="6" t="n"/>
@@ -10175,6 +10865,7 @@
       <c r="J673" s="6" t="n"/>
       <c r="K673" s="6" t="n"/>
       <c r="L673" s="6" t="n"/>
+      <c r="M673" s="6" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="6" t="n"/>
@@ -10189,6 +10880,7 @@
       <c r="J674" s="6" t="n"/>
       <c r="K674" s="6" t="n"/>
       <c r="L674" s="6" t="n"/>
+      <c r="M674" s="6" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="6" t="n"/>
@@ -10203,6 +10895,7 @@
       <c r="J675" s="6" t="n"/>
       <c r="K675" s="6" t="n"/>
       <c r="L675" s="6" t="n"/>
+      <c r="M675" s="6" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="6" t="n"/>
@@ -10217,6 +10910,7 @@
       <c r="J676" s="6" t="n"/>
       <c r="K676" s="6" t="n"/>
       <c r="L676" s="6" t="n"/>
+      <c r="M676" s="6" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="6" t="n"/>
@@ -10231,6 +10925,7 @@
       <c r="J677" s="6" t="n"/>
       <c r="K677" s="6" t="n"/>
       <c r="L677" s="6" t="n"/>
+      <c r="M677" s="6" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="6" t="n"/>
@@ -10245,6 +10940,7 @@
       <c r="J678" s="6" t="n"/>
       <c r="K678" s="6" t="n"/>
       <c r="L678" s="6" t="n"/>
+      <c r="M678" s="6" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="6" t="n"/>
@@ -10259,6 +10955,7 @@
       <c r="J679" s="6" t="n"/>
       <c r="K679" s="6" t="n"/>
       <c r="L679" s="6" t="n"/>
+      <c r="M679" s="6" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="6" t="n"/>
@@ -10273,6 +10970,7 @@
       <c r="J680" s="6" t="n"/>
       <c r="K680" s="6" t="n"/>
       <c r="L680" s="6" t="n"/>
+      <c r="M680" s="6" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="6" t="n"/>
@@ -10287,6 +10985,7 @@
       <c r="J681" s="6" t="n"/>
       <c r="K681" s="6" t="n"/>
       <c r="L681" s="6" t="n"/>
+      <c r="M681" s="6" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="6" t="n"/>
@@ -10301,6 +11000,7 @@
       <c r="J682" s="6" t="n"/>
       <c r="K682" s="6" t="n"/>
       <c r="L682" s="6" t="n"/>
+      <c r="M682" s="6" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="6" t="n"/>
@@ -10315,6 +11015,7 @@
       <c r="J683" s="6" t="n"/>
       <c r="K683" s="6" t="n"/>
       <c r="L683" s="6" t="n"/>
+      <c r="M683" s="6" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="6" t="n"/>
@@ -10329,6 +11030,7 @@
       <c r="J684" s="6" t="n"/>
       <c r="K684" s="6" t="n"/>
       <c r="L684" s="6" t="n"/>
+      <c r="M684" s="6" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="6" t="n"/>
@@ -10343,6 +11045,7 @@
       <c r="J685" s="6" t="n"/>
       <c r="K685" s="6" t="n"/>
       <c r="L685" s="6" t="n"/>
+      <c r="M685" s="6" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="6" t="n"/>
@@ -10357,6 +11060,7 @@
       <c r="J686" s="6" t="n"/>
       <c r="K686" s="6" t="n"/>
       <c r="L686" s="6" t="n"/>
+      <c r="M686" s="6" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="6" t="n"/>
@@ -10371,6 +11075,7 @@
       <c r="J687" s="6" t="n"/>
       <c r="K687" s="6" t="n"/>
       <c r="L687" s="6" t="n"/>
+      <c r="M687" s="6" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="6" t="n"/>
@@ -10385,6 +11090,7 @@
       <c r="J688" s="6" t="n"/>
       <c r="K688" s="6" t="n"/>
       <c r="L688" s="6" t="n"/>
+      <c r="M688" s="6" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="6" t="n"/>
@@ -10399,6 +11105,7 @@
       <c r="J689" s="6" t="n"/>
       <c r="K689" s="6" t="n"/>
       <c r="L689" s="6" t="n"/>
+      <c r="M689" s="6" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="6" t="n"/>
@@ -10413,6 +11120,7 @@
       <c r="J690" s="6" t="n"/>
       <c r="K690" s="6" t="n"/>
       <c r="L690" s="6" t="n"/>
+      <c r="M690" s="6" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="6" t="n"/>
@@ -10427,6 +11135,7 @@
       <c r="J691" s="6" t="n"/>
       <c r="K691" s="6" t="n"/>
       <c r="L691" s="6" t="n"/>
+      <c r="M691" s="6" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="6" t="n"/>
@@ -10441,6 +11150,7 @@
       <c r="J692" s="6" t="n"/>
       <c r="K692" s="6" t="n"/>
       <c r="L692" s="6" t="n"/>
+      <c r="M692" s="6" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="6" t="n"/>
@@ -10455,6 +11165,7 @@
       <c r="J693" s="6" t="n"/>
       <c r="K693" s="6" t="n"/>
       <c r="L693" s="6" t="n"/>
+      <c r="M693" s="6" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="6" t="n"/>
@@ -10469,6 +11180,7 @@
       <c r="J694" s="6" t="n"/>
       <c r="K694" s="6" t="n"/>
       <c r="L694" s="6" t="n"/>
+      <c r="M694" s="6" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="6" t="n"/>
@@ -10483,6 +11195,7 @@
       <c r="J695" s="6" t="n"/>
       <c r="K695" s="6" t="n"/>
       <c r="L695" s="6" t="n"/>
+      <c r="M695" s="6" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="6" t="n"/>
@@ -10497,6 +11210,7 @@
       <c r="J696" s="6" t="n"/>
       <c r="K696" s="6" t="n"/>
       <c r="L696" s="6" t="n"/>
+      <c r="M696" s="6" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="6" t="n"/>
@@ -10511,6 +11225,7 @@
       <c r="J697" s="6" t="n"/>
       <c r="K697" s="6" t="n"/>
       <c r="L697" s="6" t="n"/>
+      <c r="M697" s="6" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="6" t="n"/>
@@ -10525,6 +11240,7 @@
       <c r="J698" s="6" t="n"/>
       <c r="K698" s="6" t="n"/>
       <c r="L698" s="6" t="n"/>
+      <c r="M698" s="6" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="6" t="n"/>
@@ -10539,6 +11255,7 @@
       <c r="J699" s="6" t="n"/>
       <c r="K699" s="6" t="n"/>
       <c r="L699" s="6" t="n"/>
+      <c r="M699" s="6" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="6" t="n"/>
@@ -10553,6 +11270,7 @@
       <c r="J700" s="6" t="n"/>
       <c r="K700" s="6" t="n"/>
       <c r="L700" s="6" t="n"/>
+      <c r="M700" s="6" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="6" t="n"/>
@@ -10567,6 +11285,7 @@
       <c r="J701" s="6" t="n"/>
       <c r="K701" s="6" t="n"/>
       <c r="L701" s="6" t="n"/>
+      <c r="M701" s="6" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="6" t="n"/>
@@ -10581,6 +11300,7 @@
       <c r="J702" s="6" t="n"/>
       <c r="K702" s="6" t="n"/>
       <c r="L702" s="6" t="n"/>
+      <c r="M702" s="6" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="6" t="n"/>
@@ -10595,6 +11315,7 @@
       <c r="J703" s="6" t="n"/>
       <c r="K703" s="6" t="n"/>
       <c r="L703" s="6" t="n"/>
+      <c r="M703" s="6" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="6" t="n"/>
@@ -10609,6 +11330,7 @@
       <c r="J704" s="6" t="n"/>
       <c r="K704" s="6" t="n"/>
       <c r="L704" s="6" t="n"/>
+      <c r="M704" s="6" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="6" t="n"/>
@@ -10623,6 +11345,7 @@
       <c r="J705" s="6" t="n"/>
       <c r="K705" s="6" t="n"/>
       <c r="L705" s="6" t="n"/>
+      <c r="M705" s="6" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="6" t="n"/>
@@ -10637,6 +11360,7 @@
       <c r="J706" s="6" t="n"/>
       <c r="K706" s="6" t="n"/>
       <c r="L706" s="6" t="n"/>
+      <c r="M706" s="6" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="6" t="n"/>
@@ -10651,6 +11375,7 @@
       <c r="J707" s="6" t="n"/>
       <c r="K707" s="6" t="n"/>
       <c r="L707" s="6" t="n"/>
+      <c r="M707" s="6" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="6" t="n"/>
@@ -10665,6 +11390,7 @@
       <c r="J708" s="6" t="n"/>
       <c r="K708" s="6" t="n"/>
       <c r="L708" s="6" t="n"/>
+      <c r="M708" s="6" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="6" t="n"/>
@@ -10679,6 +11405,7 @@
       <c r="J709" s="6" t="n"/>
       <c r="K709" s="6" t="n"/>
       <c r="L709" s="6" t="n"/>
+      <c r="M709" s="6" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="6" t="n"/>
@@ -10693,6 +11420,7 @@
       <c r="J710" s="6" t="n"/>
       <c r="K710" s="6" t="n"/>
       <c r="L710" s="6" t="n"/>
+      <c r="M710" s="6" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="6" t="n"/>
@@ -10707,6 +11435,7 @@
       <c r="J711" s="6" t="n"/>
       <c r="K711" s="6" t="n"/>
       <c r="L711" s="6" t="n"/>
+      <c r="M711" s="6" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="6" t="n"/>
@@ -10721,6 +11450,7 @@
       <c r="J712" s="6" t="n"/>
       <c r="K712" s="6" t="n"/>
       <c r="L712" s="6" t="n"/>
+      <c r="M712" s="6" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="6" t="n"/>
@@ -10735,6 +11465,7 @@
       <c r="J713" s="6" t="n"/>
       <c r="K713" s="6" t="n"/>
       <c r="L713" s="6" t="n"/>
+      <c r="M713" s="6" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="6" t="n"/>
@@ -10749,6 +11480,7 @@
       <c r="J714" s="6" t="n"/>
       <c r="K714" s="6" t="n"/>
       <c r="L714" s="6" t="n"/>
+      <c r="M714" s="6" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="6" t="n"/>
@@ -10763,6 +11495,7 @@
       <c r="J715" s="6" t="n"/>
       <c r="K715" s="6" t="n"/>
       <c r="L715" s="6" t="n"/>
+      <c r="M715" s="6" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="6" t="n"/>
@@ -10777,6 +11510,7 @@
       <c r="J716" s="6" t="n"/>
       <c r="K716" s="6" t="n"/>
       <c r="L716" s="6" t="n"/>
+      <c r="M716" s="6" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="6" t="n"/>
@@ -10791,6 +11525,7 @@
       <c r="J717" s="6" t="n"/>
       <c r="K717" s="6" t="n"/>
       <c r="L717" s="6" t="n"/>
+      <c r="M717" s="6" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="6" t="n"/>
@@ -10805,6 +11540,7 @@
       <c r="J718" s="6" t="n"/>
       <c r="K718" s="6" t="n"/>
       <c r="L718" s="6" t="n"/>
+      <c r="M718" s="6" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="6" t="n"/>
@@ -10819,6 +11555,7 @@
       <c r="J719" s="6" t="n"/>
       <c r="K719" s="6" t="n"/>
       <c r="L719" s="6" t="n"/>
+      <c r="M719" s="6" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="6" t="n"/>
@@ -10833,6 +11570,7 @@
       <c r="J720" s="6" t="n"/>
       <c r="K720" s="6" t="n"/>
       <c r="L720" s="6" t="n"/>
+      <c r="M720" s="6" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="6" t="n"/>
@@ -10847,6 +11585,7 @@
       <c r="J721" s="6" t="n"/>
       <c r="K721" s="6" t="n"/>
       <c r="L721" s="6" t="n"/>
+      <c r="M721" s="6" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="6" t="n"/>
@@ -10861,6 +11600,7 @@
       <c r="J722" s="6" t="n"/>
       <c r="K722" s="6" t="n"/>
       <c r="L722" s="6" t="n"/>
+      <c r="M722" s="6" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="6" t="n"/>
@@ -10875,6 +11615,7 @@
       <c r="J723" s="6" t="n"/>
       <c r="K723" s="6" t="n"/>
       <c r="L723" s="6" t="n"/>
+      <c r="M723" s="6" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="6" t="n"/>
@@ -10889,6 +11630,7 @@
       <c r="J724" s="6" t="n"/>
       <c r="K724" s="6" t="n"/>
       <c r="L724" s="6" t="n"/>
+      <c r="M724" s="6" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="6" t="n"/>
@@ -10903,6 +11645,7 @@
       <c r="J725" s="6" t="n"/>
       <c r="K725" s="6" t="n"/>
       <c r="L725" s="6" t="n"/>
+      <c r="M725" s="6" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="6" t="n"/>
@@ -10917,6 +11660,7 @@
       <c r="J726" s="6" t="n"/>
       <c r="K726" s="6" t="n"/>
       <c r="L726" s="6" t="n"/>
+      <c r="M726" s="6" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="6" t="n"/>
@@ -10931,6 +11675,7 @@
       <c r="J727" s="6" t="n"/>
       <c r="K727" s="6" t="n"/>
       <c r="L727" s="6" t="n"/>
+      <c r="M727" s="6" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="6" t="n"/>
@@ -10945,6 +11690,7 @@
       <c r="J728" s="6" t="n"/>
       <c r="K728" s="6" t="n"/>
       <c r="L728" s="6" t="n"/>
+      <c r="M728" s="6" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="6" t="n"/>
@@ -10959,6 +11705,7 @@
       <c r="J729" s="6" t="n"/>
       <c r="K729" s="6" t="n"/>
       <c r="L729" s="6" t="n"/>
+      <c r="M729" s="6" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="6" t="n"/>
@@ -10973,6 +11720,7 @@
       <c r="J730" s="6" t="n"/>
       <c r="K730" s="6" t="n"/>
       <c r="L730" s="6" t="n"/>
+      <c r="M730" s="6" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="6" t="n"/>
@@ -10987,6 +11735,7 @@
       <c r="J731" s="6" t="n"/>
       <c r="K731" s="6" t="n"/>
       <c r="L731" s="6" t="n"/>
+      <c r="M731" s="6" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="6" t="n"/>
@@ -11001,6 +11750,7 @@
       <c r="J732" s="6" t="n"/>
       <c r="K732" s="6" t="n"/>
       <c r="L732" s="6" t="n"/>
+      <c r="M732" s="6" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="6" t="n"/>
@@ -11015,6 +11765,7 @@
       <c r="J733" s="6" t="n"/>
       <c r="K733" s="6" t="n"/>
       <c r="L733" s="6" t="n"/>
+      <c r="M733" s="6" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="6" t="n"/>
@@ -11029,6 +11780,7 @@
       <c r="J734" s="6" t="n"/>
       <c r="K734" s="6" t="n"/>
       <c r="L734" s="6" t="n"/>
+      <c r="M734" s="6" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="6" t="n"/>
@@ -11043,6 +11795,7 @@
       <c r="J735" s="6" t="n"/>
       <c r="K735" s="6" t="n"/>
       <c r="L735" s="6" t="n"/>
+      <c r="M735" s="6" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="6" t="n"/>
@@ -11057,6 +11810,7 @@
       <c r="J736" s="6" t="n"/>
       <c r="K736" s="6" t="n"/>
       <c r="L736" s="6" t="n"/>
+      <c r="M736" s="6" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="6" t="n"/>
@@ -11071,6 +11825,7 @@
       <c r="J737" s="6" t="n"/>
       <c r="K737" s="6" t="n"/>
       <c r="L737" s="6" t="n"/>
+      <c r="M737" s="6" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="6" t="n"/>
@@ -11085,6 +11840,7 @@
       <c r="J738" s="6" t="n"/>
       <c r="K738" s="6" t="n"/>
       <c r="L738" s="6" t="n"/>
+      <c r="M738" s="6" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="6" t="n"/>
@@ -11099,6 +11855,7 @@
       <c r="J739" s="6" t="n"/>
       <c r="K739" s="6" t="n"/>
       <c r="L739" s="6" t="n"/>
+      <c r="M739" s="6" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="6" t="n"/>
@@ -11113,6 +11870,7 @@
       <c r="J740" s="6" t="n"/>
       <c r="K740" s="6" t="n"/>
       <c r="L740" s="6" t="n"/>
+      <c r="M740" s="6" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="6" t="n"/>
@@ -11127,6 +11885,7 @@
       <c r="J741" s="6" t="n"/>
       <c r="K741" s="6" t="n"/>
       <c r="L741" s="6" t="n"/>
+      <c r="M741" s="6" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="6" t="n"/>
@@ -11141,6 +11900,7 @@
       <c r="J742" s="6" t="n"/>
       <c r="K742" s="6" t="n"/>
       <c r="L742" s="6" t="n"/>
+      <c r="M742" s="6" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="6" t="n"/>
@@ -11155,6 +11915,7 @@
       <c r="J743" s="6" t="n"/>
       <c r="K743" s="6" t="n"/>
       <c r="L743" s="6" t="n"/>
+      <c r="M743" s="6" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="6" t="n"/>
@@ -11169,6 +11930,7 @@
       <c r="J744" s="6" t="n"/>
       <c r="K744" s="6" t="n"/>
       <c r="L744" s="6" t="n"/>
+      <c r="M744" s="6" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="6" t="n"/>
@@ -11183,6 +11945,7 @@
       <c r="J745" s="6" t="n"/>
       <c r="K745" s="6" t="n"/>
       <c r="L745" s="6" t="n"/>
+      <c r="M745" s="6" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="6" t="n"/>
@@ -11197,6 +11960,7 @@
       <c r="J746" s="6" t="n"/>
       <c r="K746" s="6" t="n"/>
       <c r="L746" s="6" t="n"/>
+      <c r="M746" s="6" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="6" t="n"/>
@@ -11211,6 +11975,7 @@
       <c r="J747" s="6" t="n"/>
       <c r="K747" s="6" t="n"/>
       <c r="L747" s="6" t="n"/>
+      <c r="M747" s="6" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="6" t="n"/>
@@ -11225,6 +11990,7 @@
       <c r="J748" s="6" t="n"/>
       <c r="K748" s="6" t="n"/>
       <c r="L748" s="6" t="n"/>
+      <c r="M748" s="6" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="6" t="n"/>
@@ -11239,6 +12005,7 @@
       <c r="J749" s="6" t="n"/>
       <c r="K749" s="6" t="n"/>
       <c r="L749" s="6" t="n"/>
+      <c r="M749" s="6" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="6" t="n"/>
@@ -11253,6 +12020,7 @@
       <c r="J750" s="6" t="n"/>
       <c r="K750" s="6" t="n"/>
       <c r="L750" s="6" t="n"/>
+      <c r="M750" s="6" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="6" t="n"/>
@@ -11267,6 +12035,7 @@
       <c r="J751" s="6" t="n"/>
       <c r="K751" s="6" t="n"/>
       <c r="L751" s="6" t="n"/>
+      <c r="M751" s="6" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="6" t="n"/>
@@ -11281,6 +12050,7 @@
       <c r="J752" s="6" t="n"/>
       <c r="K752" s="6" t="n"/>
       <c r="L752" s="6" t="n"/>
+      <c r="M752" s="6" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="6" t="n"/>
@@ -11295,6 +12065,7 @@
       <c r="J753" s="6" t="n"/>
       <c r="K753" s="6" t="n"/>
       <c r="L753" s="6" t="n"/>
+      <c r="M753" s="6" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="6" t="n"/>
@@ -11309,6 +12080,7 @@
       <c r="J754" s="6" t="n"/>
       <c r="K754" s="6" t="n"/>
       <c r="L754" s="6" t="n"/>
+      <c r="M754" s="6" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="6" t="n"/>
@@ -11323,6 +12095,7 @@
       <c r="J755" s="6" t="n"/>
       <c r="K755" s="6" t="n"/>
       <c r="L755" s="6" t="n"/>
+      <c r="M755" s="6" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="6" t="n"/>
@@ -11337,6 +12110,7 @@
       <c r="J756" s="6" t="n"/>
       <c r="K756" s="6" t="n"/>
       <c r="L756" s="6" t="n"/>
+      <c r="M756" s="6" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="6" t="n"/>
@@ -11351,6 +12125,7 @@
       <c r="J757" s="6" t="n"/>
       <c r="K757" s="6" t="n"/>
       <c r="L757" s="6" t="n"/>
+      <c r="M757" s="6" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="6" t="n"/>
@@ -11365,6 +12140,7 @@
       <c r="J758" s="6" t="n"/>
       <c r="K758" s="6" t="n"/>
       <c r="L758" s="6" t="n"/>
+      <c r="M758" s="6" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="6" t="n"/>
@@ -11379,6 +12155,7 @@
       <c r="J759" s="6" t="n"/>
       <c r="K759" s="6" t="n"/>
       <c r="L759" s="6" t="n"/>
+      <c r="M759" s="6" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="6" t="n"/>
@@ -11393,6 +12170,7 @@
       <c r="J760" s="6" t="n"/>
       <c r="K760" s="6" t="n"/>
       <c r="L760" s="6" t="n"/>
+      <c r="M760" s="6" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="6" t="n"/>
@@ -11407,6 +12185,7 @@
       <c r="J761" s="6" t="n"/>
       <c r="K761" s="6" t="n"/>
       <c r="L761" s="6" t="n"/>
+      <c r="M761" s="6" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="6" t="n"/>
@@ -11421,6 +12200,7 @@
       <c r="J762" s="6" t="n"/>
       <c r="K762" s="6" t="n"/>
       <c r="L762" s="6" t="n"/>
+      <c r="M762" s="6" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="6" t="n"/>
@@ -11435,6 +12215,7 @@
       <c r="J763" s="6" t="n"/>
       <c r="K763" s="6" t="n"/>
       <c r="L763" s="6" t="n"/>
+      <c r="M763" s="6" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="6" t="n"/>
@@ -11449,6 +12230,7 @@
       <c r="J764" s="6" t="n"/>
       <c r="K764" s="6" t="n"/>
       <c r="L764" s="6" t="n"/>
+      <c r="M764" s="6" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="6" t="n"/>
@@ -11463,6 +12245,7 @@
       <c r="J765" s="6" t="n"/>
       <c r="K765" s="6" t="n"/>
       <c r="L765" s="6" t="n"/>
+      <c r="M765" s="6" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="6" t="n"/>
@@ -11477,6 +12260,7 @@
       <c r="J766" s="6" t="n"/>
       <c r="K766" s="6" t="n"/>
       <c r="L766" s="6" t="n"/>
+      <c r="M766" s="6" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="6" t="n"/>
@@ -11491,6 +12275,7 @@
       <c r="J767" s="6" t="n"/>
       <c r="K767" s="6" t="n"/>
       <c r="L767" s="6" t="n"/>
+      <c r="M767" s="6" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="6" t="n"/>
@@ -11505,6 +12290,7 @@
       <c r="J768" s="6" t="n"/>
       <c r="K768" s="6" t="n"/>
       <c r="L768" s="6" t="n"/>
+      <c r="M768" s="6" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="6" t="n"/>
@@ -11519,6 +12305,7 @@
       <c r="J769" s="6" t="n"/>
       <c r="K769" s="6" t="n"/>
       <c r="L769" s="6" t="n"/>
+      <c r="M769" s="6" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="6" t="n"/>
@@ -11533,6 +12320,7 @@
       <c r="J770" s="6" t="n"/>
       <c r="K770" s="6" t="n"/>
       <c r="L770" s="6" t="n"/>
+      <c r="M770" s="6" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="6" t="n"/>
@@ -11547,6 +12335,7 @@
       <c r="J771" s="6" t="n"/>
       <c r="K771" s="6" t="n"/>
       <c r="L771" s="6" t="n"/>
+      <c r="M771" s="6" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="6" t="n"/>
@@ -11561,6 +12350,7 @@
       <c r="J772" s="6" t="n"/>
       <c r="K772" s="6" t="n"/>
       <c r="L772" s="6" t="n"/>
+      <c r="M772" s="6" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="6" t="n"/>
@@ -11575,6 +12365,7 @@
       <c r="J773" s="6" t="n"/>
       <c r="K773" s="6" t="n"/>
       <c r="L773" s="6" t="n"/>
+      <c r="M773" s="6" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="6" t="n"/>
@@ -11589,6 +12380,7 @@
       <c r="J774" s="6" t="n"/>
       <c r="K774" s="6" t="n"/>
       <c r="L774" s="6" t="n"/>
+      <c r="M774" s="6" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="6" t="n"/>
@@ -11603,6 +12395,7 @@
       <c r="J775" s="6" t="n"/>
       <c r="K775" s="6" t="n"/>
       <c r="L775" s="6" t="n"/>
+      <c r="M775" s="6" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="6" t="n"/>
@@ -11617,6 +12410,7 @@
       <c r="J776" s="6" t="n"/>
       <c r="K776" s="6" t="n"/>
       <c r="L776" s="6" t="n"/>
+      <c r="M776" s="6" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="6" t="n"/>
@@ -11631,6 +12425,7 @@
       <c r="J777" s="6" t="n"/>
       <c r="K777" s="6" t="n"/>
       <c r="L777" s="6" t="n"/>
+      <c r="M777" s="6" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="6" t="n"/>
@@ -11645,6 +12440,7 @@
       <c r="J778" s="6" t="n"/>
       <c r="K778" s="6" t="n"/>
       <c r="L778" s="6" t="n"/>
+      <c r="M778" s="6" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="6" t="n"/>
@@ -11659,6 +12455,7 @@
       <c r="J779" s="6" t="n"/>
       <c r="K779" s="6" t="n"/>
       <c r="L779" s="6" t="n"/>
+      <c r="M779" s="6" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="6" t="n"/>
@@ -11673,6 +12470,7 @@
       <c r="J780" s="6" t="n"/>
       <c r="K780" s="6" t="n"/>
       <c r="L780" s="6" t="n"/>
+      <c r="M780" s="6" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="6" t="n"/>
@@ -11687,6 +12485,7 @@
       <c r="J781" s="6" t="n"/>
       <c r="K781" s="6" t="n"/>
       <c r="L781" s="6" t="n"/>
+      <c r="M781" s="6" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="6" t="n"/>
@@ -11701,6 +12500,7 @@
       <c r="J782" s="6" t="n"/>
       <c r="K782" s="6" t="n"/>
       <c r="L782" s="6" t="n"/>
+      <c r="M782" s="6" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="6" t="n"/>
@@ -11715,6 +12515,7 @@
       <c r="J783" s="6" t="n"/>
       <c r="K783" s="6" t="n"/>
       <c r="L783" s="6" t="n"/>
+      <c r="M783" s="6" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="6" t="n"/>
@@ -11729,6 +12530,7 @@
       <c r="J784" s="6" t="n"/>
       <c r="K784" s="6" t="n"/>
       <c r="L784" s="6" t="n"/>
+      <c r="M784" s="6" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="6" t="n"/>
@@ -11743,6 +12545,7 @@
       <c r="J785" s="6" t="n"/>
       <c r="K785" s="6" t="n"/>
       <c r="L785" s="6" t="n"/>
+      <c r="M785" s="6" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="6" t="n"/>
@@ -11757,6 +12560,7 @@
       <c r="J786" s="6" t="n"/>
       <c r="K786" s="6" t="n"/>
       <c r="L786" s="6" t="n"/>
+      <c r="M786" s="6" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="6" t="n"/>
@@ -11771,6 +12575,7 @@
       <c r="J787" s="6" t="n"/>
       <c r="K787" s="6" t="n"/>
       <c r="L787" s="6" t="n"/>
+      <c r="M787" s="6" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="6" t="n"/>
@@ -11785,6 +12590,7 @@
       <c r="J788" s="6" t="n"/>
       <c r="K788" s="6" t="n"/>
       <c r="L788" s="6" t="n"/>
+      <c r="M788" s="6" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="6" t="n"/>
@@ -11799,6 +12605,7 @@
       <c r="J789" s="6" t="n"/>
       <c r="K789" s="6" t="n"/>
       <c r="L789" s="6" t="n"/>
+      <c r="M789" s="6" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="6" t="n"/>
@@ -11813,6 +12620,7 @@
       <c r="J790" s="6" t="n"/>
       <c r="K790" s="6" t="n"/>
       <c r="L790" s="6" t="n"/>
+      <c r="M790" s="6" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="6" t="n"/>
@@ -11827,6 +12635,7 @@
       <c r="J791" s="6" t="n"/>
       <c r="K791" s="6" t="n"/>
       <c r="L791" s="6" t="n"/>
+      <c r="M791" s="6" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="6" t="n"/>
@@ -11841,6 +12650,7 @@
       <c r="J792" s="6" t="n"/>
       <c r="K792" s="6" t="n"/>
       <c r="L792" s="6" t="n"/>
+      <c r="M792" s="6" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="6" t="n"/>
@@ -11855,6 +12665,7 @@
       <c r="J793" s="6" t="n"/>
       <c r="K793" s="6" t="n"/>
       <c r="L793" s="6" t="n"/>
+      <c r="M793" s="6" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="6" t="n"/>
@@ -11869,6 +12680,7 @@
       <c r="J794" s="6" t="n"/>
       <c r="K794" s="6" t="n"/>
       <c r="L794" s="6" t="n"/>
+      <c r="M794" s="6" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="6" t="n"/>
@@ -11883,6 +12695,7 @@
       <c r="J795" s="6" t="n"/>
       <c r="K795" s="6" t="n"/>
       <c r="L795" s="6" t="n"/>
+      <c r="M795" s="6" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="6" t="n"/>
@@ -11897,6 +12710,7 @@
       <c r="J796" s="6" t="n"/>
       <c r="K796" s="6" t="n"/>
       <c r="L796" s="6" t="n"/>
+      <c r="M796" s="6" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="6" t="n"/>
@@ -11911,6 +12725,7 @@
       <c r="J797" s="6" t="n"/>
       <c r="K797" s="6" t="n"/>
       <c r="L797" s="6" t="n"/>
+      <c r="M797" s="6" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="6" t="n"/>
@@ -11925,6 +12740,7 @@
       <c r="J798" s="6" t="n"/>
       <c r="K798" s="6" t="n"/>
       <c r="L798" s="6" t="n"/>
+      <c r="M798" s="6" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="6" t="n"/>
@@ -11939,6 +12755,7 @@
       <c r="J799" s="6" t="n"/>
       <c r="K799" s="6" t="n"/>
       <c r="L799" s="6" t="n"/>
+      <c r="M799" s="6" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="6" t="n"/>
@@ -11953,6 +12770,7 @@
       <c r="J800" s="6" t="n"/>
       <c r="K800" s="6" t="n"/>
       <c r="L800" s="6" t="n"/>
+      <c r="M800" s="6" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="6" t="n"/>
@@ -11967,6 +12785,7 @@
       <c r="J801" s="6" t="n"/>
       <c r="K801" s="6" t="n"/>
       <c r="L801" s="6" t="n"/>
+      <c r="M801" s="6" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="6" t="n"/>
@@ -11981,6 +12800,7 @@
       <c r="J802" s="6" t="n"/>
       <c r="K802" s="6" t="n"/>
       <c r="L802" s="6" t="n"/>
+      <c r="M802" s="6" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="6" t="n"/>
@@ -11995,6 +12815,7 @@
       <c r="J803" s="6" t="n"/>
       <c r="K803" s="6" t="n"/>
       <c r="L803" s="6" t="n"/>
+      <c r="M803" s="6" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="6" t="n"/>
@@ -12009,6 +12830,7 @@
       <c r="J804" s="6" t="n"/>
       <c r="K804" s="6" t="n"/>
       <c r="L804" s="6" t="n"/>
+      <c r="M804" s="6" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="6" t="n"/>
@@ -12023,6 +12845,7 @@
       <c r="J805" s="6" t="n"/>
       <c r="K805" s="6" t="n"/>
       <c r="L805" s="6" t="n"/>
+      <c r="M805" s="6" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="6" t="n"/>
@@ -12037,6 +12860,7 @@
       <c r="J806" s="6" t="n"/>
       <c r="K806" s="6" t="n"/>
       <c r="L806" s="6" t="n"/>
+      <c r="M806" s="6" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="6" t="n"/>
@@ -12051,6 +12875,7 @@
       <c r="J807" s="6" t="n"/>
       <c r="K807" s="6" t="n"/>
       <c r="L807" s="6" t="n"/>
+      <c r="M807" s="6" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="6" t="n"/>
@@ -12065,6 +12890,7 @@
       <c r="J808" s="6" t="n"/>
       <c r="K808" s="6" t="n"/>
       <c r="L808" s="6" t="n"/>
+      <c r="M808" s="6" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="6" t="n"/>
@@ -12079,6 +12905,7 @@
       <c r="J809" s="6" t="n"/>
       <c r="K809" s="6" t="n"/>
       <c r="L809" s="6" t="n"/>
+      <c r="M809" s="6" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="6" t="n"/>
@@ -12093,6 +12920,7 @@
       <c r="J810" s="6" t="n"/>
       <c r="K810" s="6" t="n"/>
       <c r="L810" s="6" t="n"/>
+      <c r="M810" s="6" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="6" t="n"/>
@@ -12107,6 +12935,7 @@
       <c r="J811" s="6" t="n"/>
       <c r="K811" s="6" t="n"/>
       <c r="L811" s="6" t="n"/>
+      <c r="M811" s="6" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="6" t="n"/>
@@ -12121,6 +12950,7 @@
       <c r="J812" s="6" t="n"/>
       <c r="K812" s="6" t="n"/>
       <c r="L812" s="6" t="n"/>
+      <c r="M812" s="6" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="6" t="n"/>
@@ -12135,6 +12965,7 @@
       <c r="J813" s="6" t="n"/>
       <c r="K813" s="6" t="n"/>
       <c r="L813" s="6" t="n"/>
+      <c r="M813" s="6" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="6" t="n"/>
@@ -12149,6 +12980,7 @@
       <c r="J814" s="6" t="n"/>
       <c r="K814" s="6" t="n"/>
       <c r="L814" s="6" t="n"/>
+      <c r="M814" s="6" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="6" t="n"/>
@@ -12163,6 +12995,7 @@
       <c r="J815" s="6" t="n"/>
       <c r="K815" s="6" t="n"/>
       <c r="L815" s="6" t="n"/>
+      <c r="M815" s="6" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="6" t="n"/>
@@ -12177,6 +13010,7 @@
       <c r="J816" s="6" t="n"/>
       <c r="K816" s="6" t="n"/>
       <c r="L816" s="6" t="n"/>
+      <c r="M816" s="6" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="6" t="n"/>
@@ -12191,6 +13025,7 @@
       <c r="J817" s="6" t="n"/>
       <c r="K817" s="6" t="n"/>
       <c r="L817" s="6" t="n"/>
+      <c r="M817" s="6" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="6" t="n"/>
@@ -12205,6 +13040,7 @@
       <c r="J818" s="6" t="n"/>
       <c r="K818" s="6" t="n"/>
       <c r="L818" s="6" t="n"/>
+      <c r="M818" s="6" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="6" t="n"/>
@@ -12219,6 +13055,7 @@
       <c r="J819" s="6" t="n"/>
       <c r="K819" s="6" t="n"/>
       <c r="L819" s="6" t="n"/>
+      <c r="M819" s="6" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="6" t="n"/>
@@ -12233,6 +13070,7 @@
       <c r="J820" s="6" t="n"/>
       <c r="K820" s="6" t="n"/>
       <c r="L820" s="6" t="n"/>
+      <c r="M820" s="6" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="6" t="n"/>
@@ -12247,6 +13085,7 @@
       <c r="J821" s="6" t="n"/>
       <c r="K821" s="6" t="n"/>
       <c r="L821" s="6" t="n"/>
+      <c r="M821" s="6" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="6" t="n"/>
@@ -12261,6 +13100,7 @@
       <c r="J822" s="6" t="n"/>
       <c r="K822" s="6" t="n"/>
       <c r="L822" s="6" t="n"/>
+      <c r="M822" s="6" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="6" t="n"/>
@@ -12275,6 +13115,7 @@
       <c r="J823" s="6" t="n"/>
       <c r="K823" s="6" t="n"/>
       <c r="L823" s="6" t="n"/>
+      <c r="M823" s="6" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="6" t="n"/>
@@ -12289,6 +13130,7 @@
       <c r="J824" s="6" t="n"/>
       <c r="K824" s="6" t="n"/>
       <c r="L824" s="6" t="n"/>
+      <c r="M824" s="6" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="6" t="n"/>
@@ -12303,6 +13145,7 @@
       <c r="J825" s="6" t="n"/>
       <c r="K825" s="6" t="n"/>
       <c r="L825" s="6" t="n"/>
+      <c r="M825" s="6" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="6" t="n"/>
@@ -12317,6 +13160,7 @@
       <c r="J826" s="6" t="n"/>
       <c r="K826" s="6" t="n"/>
       <c r="L826" s="6" t="n"/>
+      <c r="M826" s="6" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="6" t="n"/>
@@ -12331,6 +13175,7 @@
       <c r="J827" s="6" t="n"/>
       <c r="K827" s="6" t="n"/>
       <c r="L827" s="6" t="n"/>
+      <c r="M827" s="6" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="6" t="n"/>
@@ -12345,6 +13190,7 @@
       <c r="J828" s="6" t="n"/>
       <c r="K828" s="6" t="n"/>
       <c r="L828" s="6" t="n"/>
+      <c r="M828" s="6" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="6" t="n"/>
@@ -12359,6 +13205,7 @@
       <c r="J829" s="6" t="n"/>
       <c r="K829" s="6" t="n"/>
       <c r="L829" s="6" t="n"/>
+      <c r="M829" s="6" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="6" t="n"/>
@@ -12373,6 +13220,7 @@
       <c r="J830" s="6" t="n"/>
       <c r="K830" s="6" t="n"/>
       <c r="L830" s="6" t="n"/>
+      <c r="M830" s="6" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="6" t="n"/>
@@ -12387,6 +13235,7 @@
       <c r="J831" s="6" t="n"/>
       <c r="K831" s="6" t="n"/>
       <c r="L831" s="6" t="n"/>
+      <c r="M831" s="6" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="6" t="n"/>
@@ -12401,6 +13250,7 @@
       <c r="J832" s="6" t="n"/>
       <c r="K832" s="6" t="n"/>
       <c r="L832" s="6" t="n"/>
+      <c r="M832" s="6" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="6" t="n"/>
@@ -12415,6 +13265,7 @@
       <c r="J833" s="6" t="n"/>
       <c r="K833" s="6" t="n"/>
       <c r="L833" s="6" t="n"/>
+      <c r="M833" s="6" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="6" t="n"/>
@@ -12429,6 +13280,7 @@
       <c r="J834" s="6" t="n"/>
       <c r="K834" s="6" t="n"/>
       <c r="L834" s="6" t="n"/>
+      <c r="M834" s="6" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="6" t="n"/>
@@ -12443,6 +13295,7 @@
       <c r="J835" s="6" t="n"/>
       <c r="K835" s="6" t="n"/>
       <c r="L835" s="6" t="n"/>
+      <c r="M835" s="6" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="6" t="n"/>
@@ -12457,6 +13310,7 @@
       <c r="J836" s="6" t="n"/>
       <c r="K836" s="6" t="n"/>
       <c r="L836" s="6" t="n"/>
+      <c r="M836" s="6" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="6" t="n"/>
@@ -12471,6 +13325,7 @@
       <c r="J837" s="6" t="n"/>
       <c r="K837" s="6" t="n"/>
       <c r="L837" s="6" t="n"/>
+      <c r="M837" s="6" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="6" t="n"/>
@@ -12485,6 +13340,7 @@
       <c r="J838" s="6" t="n"/>
       <c r="K838" s="6" t="n"/>
       <c r="L838" s="6" t="n"/>
+      <c r="M838" s="6" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="6" t="n"/>
@@ -12499,6 +13355,7 @@
       <c r="J839" s="6" t="n"/>
       <c r="K839" s="6" t="n"/>
       <c r="L839" s="6" t="n"/>
+      <c r="M839" s="6" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="6" t="n"/>
@@ -12513,6 +13370,7 @@
       <c r="J840" s="6" t="n"/>
       <c r="K840" s="6" t="n"/>
       <c r="L840" s="6" t="n"/>
+      <c r="M840" s="6" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="6" t="n"/>
@@ -12527,6 +13385,7 @@
       <c r="J841" s="6" t="n"/>
       <c r="K841" s="6" t="n"/>
       <c r="L841" s="6" t="n"/>
+      <c r="M841" s="6" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="6" t="n"/>
@@ -12541,6 +13400,7 @@
       <c r="J842" s="6" t="n"/>
       <c r="K842" s="6" t="n"/>
       <c r="L842" s="6" t="n"/>
+      <c r="M842" s="6" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="6" t="n"/>
@@ -12555,6 +13415,7 @@
       <c r="J843" s="6" t="n"/>
       <c r="K843" s="6" t="n"/>
       <c r="L843" s="6" t="n"/>
+      <c r="M843" s="6" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="6" t="n"/>
@@ -12569,6 +13430,7 @@
       <c r="J844" s="6" t="n"/>
       <c r="K844" s="6" t="n"/>
       <c r="L844" s="6" t="n"/>
+      <c r="M844" s="6" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="6" t="n"/>
@@ -12583,6 +13445,7 @@
       <c r="J845" s="6" t="n"/>
       <c r="K845" s="6" t="n"/>
       <c r="L845" s="6" t="n"/>
+      <c r="M845" s="6" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="6" t="n"/>
@@ -12597,6 +13460,7 @@
       <c r="J846" s="6" t="n"/>
       <c r="K846" s="6" t="n"/>
       <c r="L846" s="6" t="n"/>
+      <c r="M846" s="6" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="6" t="n"/>
@@ -12611,6 +13475,7 @@
       <c r="J847" s="6" t="n"/>
       <c r="K847" s="6" t="n"/>
       <c r="L847" s="6" t="n"/>
+      <c r="M847" s="6" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="6" t="n"/>
@@ -12625,6 +13490,7 @@
       <c r="J848" s="6" t="n"/>
       <c r="K848" s="6" t="n"/>
       <c r="L848" s="6" t="n"/>
+      <c r="M848" s="6" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="6" t="n"/>
@@ -12639,6 +13505,7 @@
       <c r="J849" s="6" t="n"/>
       <c r="K849" s="6" t="n"/>
       <c r="L849" s="6" t="n"/>
+      <c r="M849" s="6" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="6" t="n"/>
@@ -12653,6 +13520,7 @@
       <c r="J850" s="6" t="n"/>
       <c r="K850" s="6" t="n"/>
       <c r="L850" s="6" t="n"/>
+      <c r="M850" s="6" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="6" t="n"/>
@@ -12667,6 +13535,7 @@
       <c r="J851" s="6" t="n"/>
       <c r="K851" s="6" t="n"/>
       <c r="L851" s="6" t="n"/>
+      <c r="M851" s="6" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="6" t="n"/>
@@ -12681,6 +13550,7 @@
       <c r="J852" s="6" t="n"/>
       <c r="K852" s="6" t="n"/>
       <c r="L852" s="6" t="n"/>
+      <c r="M852" s="6" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="6" t="n"/>
@@ -12695,6 +13565,7 @@
       <c r="J853" s="6" t="n"/>
       <c r="K853" s="6" t="n"/>
       <c r="L853" s="6" t="n"/>
+      <c r="M853" s="6" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="6" t="n"/>
@@ -12709,6 +13580,7 @@
       <c r="J854" s="6" t="n"/>
       <c r="K854" s="6" t="n"/>
       <c r="L854" s="6" t="n"/>
+      <c r="M854" s="6" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="6" t="n"/>
@@ -12723,6 +13595,7 @@
       <c r="J855" s="6" t="n"/>
       <c r="K855" s="6" t="n"/>
       <c r="L855" s="6" t="n"/>
+      <c r="M855" s="6" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="6" t="n"/>
@@ -12737,6 +13610,7 @@
       <c r="J856" s="6" t="n"/>
       <c r="K856" s="6" t="n"/>
       <c r="L856" s="6" t="n"/>
+      <c r="M856" s="6" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="6" t="n"/>
@@ -12751,6 +13625,7 @@
       <c r="J857" s="6" t="n"/>
       <c r="K857" s="6" t="n"/>
       <c r="L857" s="6" t="n"/>
+      <c r="M857" s="6" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="6" t="n"/>
@@ -12765,6 +13640,7 @@
       <c r="J858" s="6" t="n"/>
       <c r="K858" s="6" t="n"/>
       <c r="L858" s="6" t="n"/>
+      <c r="M858" s="6" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="6" t="n"/>
@@ -12779,6 +13655,7 @@
       <c r="J859" s="6" t="n"/>
       <c r="K859" s="6" t="n"/>
       <c r="L859" s="6" t="n"/>
+      <c r="M859" s="6" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="6" t="n"/>
@@ -12793,6 +13670,7 @@
       <c r="J860" s="6" t="n"/>
       <c r="K860" s="6" t="n"/>
       <c r="L860" s="6" t="n"/>
+      <c r="M860" s="6" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="6" t="n"/>
@@ -12807,6 +13685,7 @@
       <c r="J861" s="6" t="n"/>
       <c r="K861" s="6" t="n"/>
       <c r="L861" s="6" t="n"/>
+      <c r="M861" s="6" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="6" t="n"/>
@@ -12821,6 +13700,7 @@
       <c r="J862" s="6" t="n"/>
       <c r="K862" s="6" t="n"/>
       <c r="L862" s="6" t="n"/>
+      <c r="M862" s="6" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="6" t="n"/>
@@ -12835,6 +13715,7 @@
       <c r="J863" s="6" t="n"/>
       <c r="K863" s="6" t="n"/>
       <c r="L863" s="6" t="n"/>
+      <c r="M863" s="6" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="6" t="n"/>
@@ -12849,6 +13730,7 @@
       <c r="J864" s="6" t="n"/>
       <c r="K864" s="6" t="n"/>
       <c r="L864" s="6" t="n"/>
+      <c r="M864" s="6" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="6" t="n"/>
@@ -12863,6 +13745,7 @@
       <c r="J865" s="6" t="n"/>
       <c r="K865" s="6" t="n"/>
       <c r="L865" s="6" t="n"/>
+      <c r="M865" s="6" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="6" t="n"/>
@@ -12877,6 +13760,7 @@
       <c r="J866" s="6" t="n"/>
       <c r="K866" s="6" t="n"/>
       <c r="L866" s="6" t="n"/>
+      <c r="M866" s="6" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="6" t="n"/>
@@ -12891,6 +13775,7 @@
       <c r="J867" s="6" t="n"/>
       <c r="K867" s="6" t="n"/>
       <c r="L867" s="6" t="n"/>
+      <c r="M867" s="6" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="6" t="n"/>
@@ -12905,6 +13790,7 @@
       <c r="J868" s="6" t="n"/>
       <c r="K868" s="6" t="n"/>
       <c r="L868" s="6" t="n"/>
+      <c r="M868" s="6" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="6" t="n"/>
@@ -12919,6 +13805,7 @@
       <c r="J869" s="6" t="n"/>
       <c r="K869" s="6" t="n"/>
       <c r="L869" s="6" t="n"/>
+      <c r="M869" s="6" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="6" t="n"/>
@@ -12933,6 +13820,7 @@
       <c r="J870" s="6" t="n"/>
       <c r="K870" s="6" t="n"/>
       <c r="L870" s="6" t="n"/>
+      <c r="M870" s="6" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="6" t="n"/>
@@ -12947,6 +13835,7 @@
       <c r="J871" s="6" t="n"/>
       <c r="K871" s="6" t="n"/>
       <c r="L871" s="6" t="n"/>
+      <c r="M871" s="6" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="6" t="n"/>
@@ -12961,6 +13850,7 @@
       <c r="J872" s="6" t="n"/>
       <c r="K872" s="6" t="n"/>
       <c r="L872" s="6" t="n"/>
+      <c r="M872" s="6" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="6" t="n"/>
@@ -12975,6 +13865,7 @@
       <c r="J873" s="6" t="n"/>
       <c r="K873" s="6" t="n"/>
       <c r="L873" s="6" t="n"/>
+      <c r="M873" s="6" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="6" t="n"/>
@@ -12989,6 +13880,7 @@
       <c r="J874" s="6" t="n"/>
       <c r="K874" s="6" t="n"/>
       <c r="L874" s="6" t="n"/>
+      <c r="M874" s="6" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="6" t="n"/>
@@ -13003,6 +13895,7 @@
       <c r="J875" s="6" t="n"/>
       <c r="K875" s="6" t="n"/>
       <c r="L875" s="6" t="n"/>
+      <c r="M875" s="6" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="6" t="n"/>
@@ -13017,6 +13910,7 @@
       <c r="J876" s="6" t="n"/>
       <c r="K876" s="6" t="n"/>
       <c r="L876" s="6" t="n"/>
+      <c r="M876" s="6" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="6" t="n"/>
@@ -13031,6 +13925,7 @@
       <c r="J877" s="6" t="n"/>
       <c r="K877" s="6" t="n"/>
       <c r="L877" s="6" t="n"/>
+      <c r="M877" s="6" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="6" t="n"/>
@@ -13045,6 +13940,7 @@
       <c r="J878" s="6" t="n"/>
       <c r="K878" s="6" t="n"/>
       <c r="L878" s="6" t="n"/>
+      <c r="M878" s="6" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="6" t="n"/>
@@ -13059,6 +13955,7 @@
       <c r="J879" s="6" t="n"/>
       <c r="K879" s="6" t="n"/>
       <c r="L879" s="6" t="n"/>
+      <c r="M879" s="6" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="6" t="n"/>
@@ -13073,6 +13970,7 @@
       <c r="J880" s="6" t="n"/>
       <c r="K880" s="6" t="n"/>
       <c r="L880" s="6" t="n"/>
+      <c r="M880" s="6" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="6" t="n"/>
@@ -13087,6 +13985,7 @@
       <c r="J881" s="6" t="n"/>
       <c r="K881" s="6" t="n"/>
       <c r="L881" s="6" t="n"/>
+      <c r="M881" s="6" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="6" t="n"/>
@@ -13101,6 +14000,7 @@
       <c r="J882" s="6" t="n"/>
       <c r="K882" s="6" t="n"/>
       <c r="L882" s="6" t="n"/>
+      <c r="M882" s="6" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="6" t="n"/>
@@ -13115,6 +14015,7 @@
       <c r="J883" s="6" t="n"/>
       <c r="K883" s="6" t="n"/>
       <c r="L883" s="6" t="n"/>
+      <c r="M883" s="6" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="6" t="n"/>
@@ -13129,6 +14030,7 @@
       <c r="J884" s="6" t="n"/>
       <c r="K884" s="6" t="n"/>
       <c r="L884" s="6" t="n"/>
+      <c r="M884" s="6" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="6" t="n"/>
@@ -13143,6 +14045,7 @@
       <c r="J885" s="6" t="n"/>
       <c r="K885" s="6" t="n"/>
       <c r="L885" s="6" t="n"/>
+      <c r="M885" s="6" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="6" t="n"/>
@@ -13157,6 +14060,7 @@
       <c r="J886" s="6" t="n"/>
       <c r="K886" s="6" t="n"/>
       <c r="L886" s="6" t="n"/>
+      <c r="M886" s="6" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="6" t="n"/>
@@ -13171,6 +14075,7 @@
       <c r="J887" s="6" t="n"/>
       <c r="K887" s="6" t="n"/>
       <c r="L887" s="6" t="n"/>
+      <c r="M887" s="6" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="6" t="n"/>
@@ -13185,6 +14090,7 @@
       <c r="J888" s="6" t="n"/>
       <c r="K888" s="6" t="n"/>
       <c r="L888" s="6" t="n"/>
+      <c r="M888" s="6" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="6" t="n"/>
@@ -13199,6 +14105,7 @@
       <c r="J889" s="6" t="n"/>
       <c r="K889" s="6" t="n"/>
       <c r="L889" s="6" t="n"/>
+      <c r="M889" s="6" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="6" t="n"/>
@@ -13213,6 +14120,7 @@
       <c r="J890" s="6" t="n"/>
       <c r="K890" s="6" t="n"/>
       <c r="L890" s="6" t="n"/>
+      <c r="M890" s="6" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="6" t="n"/>
@@ -13227,6 +14135,7 @@
       <c r="J891" s="6" t="n"/>
       <c r="K891" s="6" t="n"/>
       <c r="L891" s="6" t="n"/>
+      <c r="M891" s="6" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="6" t="n"/>
@@ -13241,6 +14150,7 @@
       <c r="J892" s="6" t="n"/>
       <c r="K892" s="6" t="n"/>
       <c r="L892" s="6" t="n"/>
+      <c r="M892" s="6" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="6" t="n"/>
@@ -13255,6 +14165,7 @@
       <c r="J893" s="6" t="n"/>
       <c r="K893" s="6" t="n"/>
       <c r="L893" s="6" t="n"/>
+      <c r="M893" s="6" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="6" t="n"/>
@@ -13269,6 +14180,7 @@
       <c r="J894" s="6" t="n"/>
       <c r="K894" s="6" t="n"/>
       <c r="L894" s="6" t="n"/>
+      <c r="M894" s="6" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="6" t="n"/>
@@ -13283,6 +14195,7 @@
       <c r="J895" s="6" t="n"/>
       <c r="K895" s="6" t="n"/>
       <c r="L895" s="6" t="n"/>
+      <c r="M895" s="6" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="6" t="n"/>
@@ -13297,6 +14210,7 @@
       <c r="J896" s="6" t="n"/>
       <c r="K896" s="6" t="n"/>
       <c r="L896" s="6" t="n"/>
+      <c r="M896" s="6" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="6" t="n"/>
@@ -13311,6 +14225,7 @@
       <c r="J897" s="6" t="n"/>
       <c r="K897" s="6" t="n"/>
       <c r="L897" s="6" t="n"/>
+      <c r="M897" s="6" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="6" t="n"/>
@@ -13325,6 +14240,7 @@
       <c r="J898" s="6" t="n"/>
       <c r="K898" s="6" t="n"/>
       <c r="L898" s="6" t="n"/>
+      <c r="M898" s="6" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="6" t="n"/>
@@ -13339,6 +14255,7 @@
       <c r="J899" s="6" t="n"/>
       <c r="K899" s="6" t="n"/>
       <c r="L899" s="6" t="n"/>
+      <c r="M899" s="6" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="6" t="n"/>
@@ -13353,6 +14270,7 @@
       <c r="J900" s="6" t="n"/>
       <c r="K900" s="6" t="n"/>
       <c r="L900" s="6" t="n"/>
+      <c r="M900" s="6" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="6" t="n"/>
@@ -13367,6 +14285,7 @@
       <c r="J901" s="6" t="n"/>
       <c r="K901" s="6" t="n"/>
       <c r="L901" s="6" t="n"/>
+      <c r="M901" s="6" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="6" t="n"/>
@@ -13381,6 +14300,7 @@
       <c r="J902" s="6" t="n"/>
       <c r="K902" s="6" t="n"/>
       <c r="L902" s="6" t="n"/>
+      <c r="M902" s="6" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="6" t="n"/>
@@ -13395,6 +14315,7 @@
       <c r="J903" s="6" t="n"/>
       <c r="K903" s="6" t="n"/>
       <c r="L903" s="6" t="n"/>
+      <c r="M903" s="6" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="6" t="n"/>
@@ -13409,6 +14330,7 @@
       <c r="J904" s="6" t="n"/>
       <c r="K904" s="6" t="n"/>
       <c r="L904" s="6" t="n"/>
+      <c r="M904" s="6" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="6" t="n"/>
@@ -13423,6 +14345,7 @@
       <c r="J905" s="6" t="n"/>
       <c r="K905" s="6" t="n"/>
       <c r="L905" s="6" t="n"/>
+      <c r="M905" s="6" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="6" t="n"/>
@@ -13437,6 +14360,7 @@
       <c r="J906" s="6" t="n"/>
       <c r="K906" s="6" t="n"/>
       <c r="L906" s="6" t="n"/>
+      <c r="M906" s="6" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="6" t="n"/>
@@ -13451,6 +14375,7 @@
       <c r="J907" s="6" t="n"/>
       <c r="K907" s="6" t="n"/>
       <c r="L907" s="6" t="n"/>
+      <c r="M907" s="6" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="6" t="n"/>
@@ -13465,6 +14390,7 @@
       <c r="J908" s="6" t="n"/>
       <c r="K908" s="6" t="n"/>
       <c r="L908" s="6" t="n"/>
+      <c r="M908" s="6" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="6" t="n"/>
@@ -13479,6 +14405,7 @@
       <c r="J909" s="6" t="n"/>
       <c r="K909" s="6" t="n"/>
       <c r="L909" s="6" t="n"/>
+      <c r="M909" s="6" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="6" t="n"/>
@@ -13493,6 +14420,7 @@
       <c r="J910" s="6" t="n"/>
       <c r="K910" s="6" t="n"/>
       <c r="L910" s="6" t="n"/>
+      <c r="M910" s="6" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="6" t="n"/>
@@ -13507,6 +14435,7 @@
       <c r="J911" s="6" t="n"/>
       <c r="K911" s="6" t="n"/>
       <c r="L911" s="6" t="n"/>
+      <c r="M911" s="6" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="6" t="n"/>
@@ -13521,6 +14450,7 @@
       <c r="J912" s="6" t="n"/>
       <c r="K912" s="6" t="n"/>
       <c r="L912" s="6" t="n"/>
+      <c r="M912" s="6" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="6" t="n"/>
@@ -13535,6 +14465,7 @@
       <c r="J913" s="6" t="n"/>
       <c r="K913" s="6" t="n"/>
       <c r="L913" s="6" t="n"/>
+      <c r="M913" s="6" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="6" t="n"/>
@@ -13549,6 +14480,7 @@
       <c r="J914" s="6" t="n"/>
       <c r="K914" s="6" t="n"/>
       <c r="L914" s="6" t="n"/>
+      <c r="M914" s="6" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="6" t="n"/>
@@ -13563,6 +14495,7 @@
       <c r="J915" s="6" t="n"/>
       <c r="K915" s="6" t="n"/>
       <c r="L915" s="6" t="n"/>
+      <c r="M915" s="6" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="6" t="n"/>
@@ -13577,6 +14510,7 @@
       <c r="J916" s="6" t="n"/>
       <c r="K916" s="6" t="n"/>
       <c r="L916" s="6" t="n"/>
+      <c r="M916" s="6" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="6" t="n"/>
@@ -13591,6 +14525,7 @@
       <c r="J917" s="6" t="n"/>
       <c r="K917" s="6" t="n"/>
       <c r="L917" s="6" t="n"/>
+      <c r="M917" s="6" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="6" t="n"/>
@@ -13605,6 +14540,7 @@
       <c r="J918" s="6" t="n"/>
       <c r="K918" s="6" t="n"/>
       <c r="L918" s="6" t="n"/>
+      <c r="M918" s="6" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="6" t="n"/>
@@ -13619,6 +14555,7 @@
       <c r="J919" s="6" t="n"/>
       <c r="K919" s="6" t="n"/>
       <c r="L919" s="6" t="n"/>
+      <c r="M919" s="6" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="6" t="n"/>
@@ -13633,6 +14570,7 @@
       <c r="J920" s="6" t="n"/>
       <c r="K920" s="6" t="n"/>
       <c r="L920" s="6" t="n"/>
+      <c r="M920" s="6" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="6" t="n"/>
@@ -13647,6 +14585,7 @@
       <c r="J921" s="6" t="n"/>
       <c r="K921" s="6" t="n"/>
       <c r="L921" s="6" t="n"/>
+      <c r="M921" s="6" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="6" t="n"/>
@@ -13661,6 +14600,7 @@
       <c r="J922" s="6" t="n"/>
       <c r="K922" s="6" t="n"/>
       <c r="L922" s="6" t="n"/>
+      <c r="M922" s="6" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="6" t="n"/>
@@ -13675,6 +14615,7 @@
       <c r="J923" s="6" t="n"/>
       <c r="K923" s="6" t="n"/>
       <c r="L923" s="6" t="n"/>
+      <c r="M923" s="6" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="6" t="n"/>
@@ -13689,6 +14630,7 @@
       <c r="J924" s="6" t="n"/>
       <c r="K924" s="6" t="n"/>
       <c r="L924" s="6" t="n"/>
+      <c r="M924" s="6" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="6" t="n"/>
@@ -13703,6 +14645,7 @@
       <c r="J925" s="6" t="n"/>
       <c r="K925" s="6" t="n"/>
       <c r="L925" s="6" t="n"/>
+      <c r="M925" s="6" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="6" t="n"/>
@@ -13717,6 +14660,7 @@
       <c r="J926" s="6" t="n"/>
       <c r="K926" s="6" t="n"/>
       <c r="L926" s="6" t="n"/>
+      <c r="M926" s="6" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="6" t="n"/>
@@ -13731,6 +14675,7 @@
       <c r="J927" s="6" t="n"/>
       <c r="K927" s="6" t="n"/>
       <c r="L927" s="6" t="n"/>
+      <c r="M927" s="6" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="6" t="n"/>
@@ -13745,6 +14690,7 @@
       <c r="J928" s="6" t="n"/>
       <c r="K928" s="6" t="n"/>
       <c r="L928" s="6" t="n"/>
+      <c r="M928" s="6" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="6" t="n"/>
@@ -13759,6 +14705,7 @@
       <c r="J929" s="6" t="n"/>
       <c r="K929" s="6" t="n"/>
       <c r="L929" s="6" t="n"/>
+      <c r="M929" s="6" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="6" t="n"/>
@@ -13773,6 +14720,7 @@
       <c r="J930" s="6" t="n"/>
       <c r="K930" s="6" t="n"/>
       <c r="L930" s="6" t="n"/>
+      <c r="M930" s="6" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="6" t="n"/>
@@ -13787,6 +14735,7 @@
       <c r="J931" s="6" t="n"/>
       <c r="K931" s="6" t="n"/>
       <c r="L931" s="6" t="n"/>
+      <c r="M931" s="6" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="6" t="n"/>
@@ -13801,6 +14750,7 @@
       <c r="J932" s="6" t="n"/>
       <c r="K932" s="6" t="n"/>
       <c r="L932" s="6" t="n"/>
+      <c r="M932" s="6" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="6" t="n"/>
@@ -13815,6 +14765,7 @@
       <c r="J933" s="6" t="n"/>
       <c r="K933" s="6" t="n"/>
       <c r="L933" s="6" t="n"/>
+      <c r="M933" s="6" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="6" t="n"/>
@@ -13829,6 +14780,7 @@
       <c r="J934" s="6" t="n"/>
       <c r="K934" s="6" t="n"/>
       <c r="L934" s="6" t="n"/>
+      <c r="M934" s="6" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="6" t="n"/>
@@ -13843,6 +14795,7 @@
       <c r="J935" s="6" t="n"/>
       <c r="K935" s="6" t="n"/>
       <c r="L935" s="6" t="n"/>
+      <c r="M935" s="6" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="6" t="n"/>
@@ -13857,6 +14810,7 @@
       <c r="J936" s="6" t="n"/>
       <c r="K936" s="6" t="n"/>
       <c r="L936" s="6" t="n"/>
+      <c r="M936" s="6" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="6" t="n"/>
@@ -13871,6 +14825,7 @@
       <c r="J937" s="6" t="n"/>
       <c r="K937" s="6" t="n"/>
       <c r="L937" s="6" t="n"/>
+      <c r="M937" s="6" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="6" t="n"/>
@@ -13885,6 +14840,7 @@
       <c r="J938" s="6" t="n"/>
       <c r="K938" s="6" t="n"/>
       <c r="L938" s="6" t="n"/>
+      <c r="M938" s="6" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="6" t="n"/>
@@ -13899,6 +14855,7 @@
       <c r="J939" s="6" t="n"/>
       <c r="K939" s="6" t="n"/>
       <c r="L939" s="6" t="n"/>
+      <c r="M939" s="6" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="6" t="n"/>
@@ -13913,6 +14870,7 @@
       <c r="J940" s="6" t="n"/>
       <c r="K940" s="6" t="n"/>
       <c r="L940" s="6" t="n"/>
+      <c r="M940" s="6" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="6" t="n"/>
@@ -13927,6 +14885,7 @@
       <c r="J941" s="6" t="n"/>
       <c r="K941" s="6" t="n"/>
       <c r="L941" s="6" t="n"/>
+      <c r="M941" s="6" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="6" t="n"/>
@@ -13941,6 +14900,7 @@
       <c r="J942" s="6" t="n"/>
       <c r="K942" s="6" t="n"/>
       <c r="L942" s="6" t="n"/>
+      <c r="M942" s="6" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="6" t="n"/>
@@ -13955,6 +14915,7 @@
       <c r="J943" s="6" t="n"/>
       <c r="K943" s="6" t="n"/>
       <c r="L943" s="6" t="n"/>
+      <c r="M943" s="6" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="6" t="n"/>
@@ -13969,6 +14930,7 @@
       <c r="J944" s="6" t="n"/>
       <c r="K944" s="6" t="n"/>
       <c r="L944" s="6" t="n"/>
+      <c r="M944" s="6" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="6" t="n"/>
@@ -13983,6 +14945,7 @@
       <c r="J945" s="6" t="n"/>
       <c r="K945" s="6" t="n"/>
       <c r="L945" s="6" t="n"/>
+      <c r="M945" s="6" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="6" t="n"/>
@@ -13997,6 +14960,7 @@
       <c r="J946" s="6" t="n"/>
       <c r="K946" s="6" t="n"/>
       <c r="L946" s="6" t="n"/>
+      <c r="M946" s="6" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="6" t="n"/>
@@ -14011,6 +14975,7 @@
       <c r="J947" s="6" t="n"/>
       <c r="K947" s="6" t="n"/>
       <c r="L947" s="6" t="n"/>
+      <c r="M947" s="6" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="6" t="n"/>
@@ -14025,6 +14990,7 @@
       <c r="J948" s="6" t="n"/>
       <c r="K948" s="6" t="n"/>
       <c r="L948" s="6" t="n"/>
+      <c r="M948" s="6" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="6" t="n"/>
@@ -14039,6 +15005,7 @@
       <c r="J949" s="6" t="n"/>
       <c r="K949" s="6" t="n"/>
       <c r="L949" s="6" t="n"/>
+      <c r="M949" s="6" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="6" t="n"/>
@@ -14053,6 +15020,7 @@
       <c r="J950" s="6" t="n"/>
       <c r="K950" s="6" t="n"/>
       <c r="L950" s="6" t="n"/>
+      <c r="M950" s="6" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="6" t="n"/>
@@ -14067,6 +15035,7 @@
       <c r="J951" s="6" t="n"/>
       <c r="K951" s="6" t="n"/>
       <c r="L951" s="6" t="n"/>
+      <c r="M951" s="6" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="6" t="n"/>
@@ -14081,6 +15050,7 @@
       <c r="J952" s="6" t="n"/>
       <c r="K952" s="6" t="n"/>
       <c r="L952" s="6" t="n"/>
+      <c r="M952" s="6" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="6" t="n"/>
@@ -14095,6 +15065,7 @@
       <c r="J953" s="6" t="n"/>
       <c r="K953" s="6" t="n"/>
       <c r="L953" s="6" t="n"/>
+      <c r="M953" s="6" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="6" t="n"/>
@@ -14109,6 +15080,7 @@
       <c r="J954" s="6" t="n"/>
       <c r="K954" s="6" t="n"/>
       <c r="L954" s="6" t="n"/>
+      <c r="M954" s="6" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="6" t="n"/>
@@ -14123,6 +15095,7 @@
       <c r="J955" s="6" t="n"/>
       <c r="K955" s="6" t="n"/>
       <c r="L955" s="6" t="n"/>
+      <c r="M955" s="6" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="6" t="n"/>
@@ -14137,6 +15110,7 @@
       <c r="J956" s="6" t="n"/>
       <c r="K956" s="6" t="n"/>
       <c r="L956" s="6" t="n"/>
+      <c r="M956" s="6" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="6" t="n"/>
@@ -14151,6 +15125,7 @@
       <c r="J957" s="6" t="n"/>
       <c r="K957" s="6" t="n"/>
       <c r="L957" s="6" t="n"/>
+      <c r="M957" s="6" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="6" t="n"/>
@@ -14165,6 +15140,7 @@
       <c r="J958" s="6" t="n"/>
       <c r="K958" s="6" t="n"/>
       <c r="L958" s="6" t="n"/>
+      <c r="M958" s="6" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="6" t="n"/>
@@ -14179,6 +15155,7 @@
       <c r="J959" s="6" t="n"/>
       <c r="K959" s="6" t="n"/>
       <c r="L959" s="6" t="n"/>
+      <c r="M959" s="6" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="6" t="n"/>
@@ -14193,6 +15170,7 @@
       <c r="J960" s="6" t="n"/>
       <c r="K960" s="6" t="n"/>
       <c r="L960" s="6" t="n"/>
+      <c r="M960" s="6" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="6" t="n"/>
@@ -14207,6 +15185,7 @@
       <c r="J961" s="6" t="n"/>
       <c r="K961" s="6" t="n"/>
       <c r="L961" s="6" t="n"/>
+      <c r="M961" s="6" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="6" t="n"/>
@@ -14221,6 +15200,7 @@
       <c r="J962" s="6" t="n"/>
       <c r="K962" s="6" t="n"/>
       <c r="L962" s="6" t="n"/>
+      <c r="M962" s="6" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="6" t="n"/>
@@ -14235,6 +15215,7 @@
       <c r="J963" s="6" t="n"/>
       <c r="K963" s="6" t="n"/>
       <c r="L963" s="6" t="n"/>
+      <c r="M963" s="6" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="6" t="n"/>
@@ -14249,6 +15230,7 @@
       <c r="J964" s="6" t="n"/>
       <c r="K964" s="6" t="n"/>
       <c r="L964" s="6" t="n"/>
+      <c r="M964" s="6" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="6" t="n"/>
@@ -14263,6 +15245,7 @@
       <c r="J965" s="6" t="n"/>
       <c r="K965" s="6" t="n"/>
       <c r="L965" s="6" t="n"/>
+      <c r="M965" s="6" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="6" t="n"/>
@@ -14277,6 +15260,7 @@
       <c r="J966" s="6" t="n"/>
       <c r="K966" s="6" t="n"/>
       <c r="L966" s="6" t="n"/>
+      <c r="M966" s="6" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="6" t="n"/>
@@ -14291,6 +15275,7 @@
       <c r="J967" s="6" t="n"/>
       <c r="K967" s="6" t="n"/>
       <c r="L967" s="6" t="n"/>
+      <c r="M967" s="6" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="6" t="n"/>
@@ -14305,6 +15290,7 @@
       <c r="J968" s="6" t="n"/>
       <c r="K968" s="6" t="n"/>
       <c r="L968" s="6" t="n"/>
+      <c r="M968" s="6" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="6" t="n"/>
@@ -14319,6 +15305,7 @@
       <c r="J969" s="6" t="n"/>
       <c r="K969" s="6" t="n"/>
       <c r="L969" s="6" t="n"/>
+      <c r="M969" s="6" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="6" t="n"/>
@@ -14333,6 +15320,7 @@
       <c r="J970" s="6" t="n"/>
       <c r="K970" s="6" t="n"/>
       <c r="L970" s="6" t="n"/>
+      <c r="M970" s="6" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="6" t="n"/>
@@ -14347,6 +15335,7 @@
       <c r="J971" s="6" t="n"/>
       <c r="K971" s="6" t="n"/>
       <c r="L971" s="6" t="n"/>
+      <c r="M971" s="6" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="6" t="n"/>
@@ -14361,6 +15350,7 @@
       <c r="J972" s="6" t="n"/>
       <c r="K972" s="6" t="n"/>
       <c r="L972" s="6" t="n"/>
+      <c r="M972" s="6" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="6" t="n"/>
@@ -14375,6 +15365,7 @@
       <c r="J973" s="6" t="n"/>
       <c r="K973" s="6" t="n"/>
       <c r="L973" s="6" t="n"/>
+      <c r="M973" s="6" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="6" t="n"/>
@@ -14389,6 +15380,7 @@
       <c r="J974" s="6" t="n"/>
       <c r="K974" s="6" t="n"/>
       <c r="L974" s="6" t="n"/>
+      <c r="M974" s="6" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="6" t="n"/>
@@ -14403,6 +15395,7 @@
       <c r="J975" s="6" t="n"/>
       <c r="K975" s="6" t="n"/>
       <c r="L975" s="6" t="n"/>
+      <c r="M975" s="6" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="6" t="n"/>
@@ -14417,6 +15410,7 @@
       <c r="J976" s="6" t="n"/>
       <c r="K976" s="6" t="n"/>
       <c r="L976" s="6" t="n"/>
+      <c r="M976" s="6" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="6" t="n"/>
@@ -14431,6 +15425,7 @@
       <c r="J977" s="6" t="n"/>
       <c r="K977" s="6" t="n"/>
       <c r="L977" s="6" t="n"/>
+      <c r="M977" s="6" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="6" t="n"/>
@@ -14445,6 +15440,7 @@
       <c r="J978" s="6" t="n"/>
       <c r="K978" s="6" t="n"/>
       <c r="L978" s="6" t="n"/>
+      <c r="M978" s="6" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="6" t="n"/>
@@ -14459,6 +15455,7 @@
       <c r="J979" s="6" t="n"/>
       <c r="K979" s="6" t="n"/>
       <c r="L979" s="6" t="n"/>
+      <c r="M979" s="6" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="6" t="n"/>
@@ -14473,6 +15470,7 @@
       <c r="J980" s="6" t="n"/>
       <c r="K980" s="6" t="n"/>
       <c r="L980" s="6" t="n"/>
+      <c r="M980" s="6" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="6" t="n"/>
@@ -14487,6 +15485,7 @@
       <c r="J981" s="6" t="n"/>
       <c r="K981" s="6" t="n"/>
       <c r="L981" s="6" t="n"/>
+      <c r="M981" s="6" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="6" t="n"/>
@@ -14501,6 +15500,7 @@
       <c r="J982" s="6" t="n"/>
       <c r="K982" s="6" t="n"/>
       <c r="L982" s="6" t="n"/>
+      <c r="M982" s="6" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="6" t="n"/>
@@ -14515,6 +15515,7 @@
       <c r="J983" s="6" t="n"/>
       <c r="K983" s="6" t="n"/>
       <c r="L983" s="6" t="n"/>
+      <c r="M983" s="6" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="6" t="n"/>
@@ -14529,6 +15530,7 @@
       <c r="J984" s="6" t="n"/>
       <c r="K984" s="6" t="n"/>
       <c r="L984" s="6" t="n"/>
+      <c r="M984" s="6" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="6" t="n"/>
@@ -14543,6 +15545,7 @@
       <c r="J985" s="6" t="n"/>
       <c r="K985" s="6" t="n"/>
       <c r="L985" s="6" t="n"/>
+      <c r="M985" s="6" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="6" t="n"/>
@@ -14557,6 +15560,7 @@
       <c r="J986" s="6" t="n"/>
       <c r="K986" s="6" t="n"/>
       <c r="L986" s="6" t="n"/>
+      <c r="M986" s="6" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="6" t="n"/>
@@ -14571,6 +15575,7 @@
       <c r="J987" s="6" t="n"/>
       <c r="K987" s="6" t="n"/>
       <c r="L987" s="6" t="n"/>
+      <c r="M987" s="6" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="6" t="n"/>
@@ -14585,6 +15590,7 @@
       <c r="J988" s="6" t="n"/>
       <c r="K988" s="6" t="n"/>
       <c r="L988" s="6" t="n"/>
+      <c r="M988" s="6" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="6" t="n"/>
@@ -14599,6 +15605,7 @@
       <c r="J989" s="6" t="n"/>
       <c r="K989" s="6" t="n"/>
       <c r="L989" s="6" t="n"/>
+      <c r="M989" s="6" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="6" t="n"/>
@@ -14613,6 +15620,7 @@
       <c r="J990" s="6" t="n"/>
       <c r="K990" s="6" t="n"/>
       <c r="L990" s="6" t="n"/>
+      <c r="M990" s="6" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="6" t="n"/>
@@ -14627,6 +15635,7 @@
       <c r="J991" s="6" t="n"/>
       <c r="K991" s="6" t="n"/>
       <c r="L991" s="6" t="n"/>
+      <c r="M991" s="6" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="6" t="n"/>
@@ -14641,6 +15650,7 @@
       <c r="J992" s="6" t="n"/>
       <c r="K992" s="6" t="n"/>
       <c r="L992" s="6" t="n"/>
+      <c r="M992" s="6" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="6" t="n"/>
@@ -14655,6 +15665,7 @@
       <c r="J993" s="6" t="n"/>
       <c r="K993" s="6" t="n"/>
       <c r="L993" s="6" t="n"/>
+      <c r="M993" s="6" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="6" t="n"/>
@@ -14669,6 +15680,7 @@
       <c r="J994" s="6" t="n"/>
       <c r="K994" s="6" t="n"/>
       <c r="L994" s="6" t="n"/>
+      <c r="M994" s="6" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="6" t="n"/>
@@ -14683,6 +15695,7 @@
       <c r="J995" s="6" t="n"/>
       <c r="K995" s="6" t="n"/>
       <c r="L995" s="6" t="n"/>
+      <c r="M995" s="6" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="6" t="n"/>
@@ -14697,6 +15710,7 @@
       <c r="J996" s="6" t="n"/>
       <c r="K996" s="6" t="n"/>
       <c r="L996" s="6" t="n"/>
+      <c r="M996" s="6" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="6" t="n"/>
@@ -14711,6 +15725,7 @@
       <c r="J997" s="6" t="n"/>
       <c r="K997" s="6" t="n"/>
       <c r="L997" s="6" t="n"/>
+      <c r="M997" s="6" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="6" t="n"/>
@@ -14725,6 +15740,7 @@
       <c r="J998" s="6" t="n"/>
       <c r="K998" s="6" t="n"/>
       <c r="L998" s="6" t="n"/>
+      <c r="M998" s="6" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="6" t="n"/>
@@ -14739,6 +15755,7 @@
       <c r="J999" s="6" t="n"/>
       <c r="K999" s="6" t="n"/>
       <c r="L999" s="6" t="n"/>
+      <c r="M999" s="6" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="6" t="n"/>
@@ -14753,6 +15770,7 @@
       <c r="J1000" s="6" t="n"/>
       <c r="K1000" s="6" t="n"/>
       <c r="L1000" s="6" t="n"/>
+      <c r="M1000" s="6" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="6" t="n"/>
@@ -14767,9 +15785,10 @@
       <c r="J1001" s="6" t="n"/>
       <c r="K1001" s="6" t="n"/>
       <c r="L1001" s="6" t="n"/>
+      <c r="M1001" s="6" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="B2:B1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Naturaleza" error="Elige NATURAL o JURIDICA" type="list">
       <formula1>=LISTAS!$A$2:$A$3</formula1>
     </dataValidation>
@@ -14780,6 +15799,10 @@
       <formula1>=INDIRECT(VLOOKUP(I2,DEPTOS_RANGO,2,FALSE))</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Número de días entre 1 y 90 (vacío = 15)" type="whole" operator="between">
+      <formula1>1</formula1>
+      <formula2>90</formula2>
+    </dataValidation>
+    <dataValidation sqref="M2:M1001" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Número de días entre 1 y 90 (vacío = 15)" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>90</formula2>
     </dataValidation>
